--- a/templates/accounting-template.xlsx
+++ b/templates/accounting-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\school-substitution-sys\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A02DB0-5A17-45EA-ACA3-E9C8652FAFF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A351242B-66A3-4E93-8016-74149CBED496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="超鐘點" sheetId="5" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="61">
   <si>
     <t>編號</t>
   </si>
@@ -143,9 +143,6 @@
   </si>
   <si>
     <t>雙</t>
-  </si>
-  <si>
-    <t>合計</t>
   </si>
   <si>
     <t>出納組長</t>
@@ -523,7 +520,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -668,9 +665,6 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -692,9 +686,6 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -956,13 +947,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -983,14 +971,17 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1228,59 +1219,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.453125" style="112" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="67" customWidth="1"/>
-    <col min="3" max="3" width="15.08984375" style="96" customWidth="1"/>
-    <col min="4" max="4" width="9.36328125" style="96" customWidth="1"/>
-    <col min="5" max="5" width="25.90625" style="142" customWidth="1"/>
-    <col min="6" max="6" width="5.90625" style="118" customWidth="1"/>
-    <col min="7" max="7" width="6.453125" style="118" customWidth="1"/>
-    <col min="8" max="8" width="6.90625" style="88" customWidth="1"/>
-    <col min="9" max="9" width="9" style="78" customWidth="1"/>
-    <col min="10" max="10" width="8.08984375" style="88" customWidth="1"/>
-    <col min="11" max="11" width="17.08984375" style="88" customWidth="1"/>
-    <col min="12" max="13" width="0.26953125" style="96" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7265625" style="96" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="48.36328125" style="121" customWidth="1"/>
-    <col min="16" max="16" width="11.453125" style="96" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="96"/>
+    <col min="1" max="1" width="5.5" style="110" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="65" customWidth="1"/>
+    <col min="3" max="3" width="15.125" style="94" customWidth="1"/>
+    <col min="4" max="4" width="9.375" style="94" customWidth="1"/>
+    <col min="5" max="5" width="25.875" style="140" customWidth="1"/>
+    <col min="6" max="6" width="5.875" style="116" customWidth="1"/>
+    <col min="7" max="7" width="6.5" style="116" customWidth="1"/>
+    <col min="8" max="8" width="6.875" style="86" customWidth="1"/>
+    <col min="9" max="9" width="9" style="76" customWidth="1"/>
+    <col min="10" max="10" width="8.125" style="86" customWidth="1"/>
+    <col min="11" max="11" width="17.125" style="86" customWidth="1"/>
+    <col min="12" max="13" width="0.25" style="94" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="12.75" style="94" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="48.375" style="119" customWidth="1"/>
+    <col min="16" max="16" width="11.5" style="94" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="94"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="112" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="146" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
-      <c r="J1" s="146"/>
-      <c r="K1" s="146"/>
-      <c r="L1" s="146"/>
-      <c r="M1" s="146"/>
-      <c r="N1" s="146"/>
-      <c r="O1" s="146"/>
-      <c r="P1" s="121"/>
-    </row>
-    <row r="2" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="90" t="s">
+    <row r="1" spans="1:16" s="110" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="142" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="142"/>
+      <c r="K1" s="142"/>
+      <c r="L1" s="142"/>
+      <c r="M1" s="142"/>
+      <c r="N1" s="142"/>
+      <c r="O1" s="142"/>
+      <c r="P1" s="119"/>
+    </row>
+    <row r="2" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="88" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="122" t="s">
+      <c r="D2" s="120" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="123" t="s">
+      <c r="E2" s="121" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="42" t="s">
@@ -1295,10 +1286,10 @@
       <c r="I2" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="122" t="s">
+      <c r="J2" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="124" t="s">
+      <c r="K2" s="122" t="s">
         <v>10</v>
       </c>
       <c r="L2" s="42" t="s">
@@ -1307,618 +1298,618 @@
       <c r="M2" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="125" t="s">
+      <c r="N2" s="123" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="124" t="s">
+      <c r="O2" s="122" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="90"/>
-      <c r="B3" s="126"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="128"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="103"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="130"/>
-      <c r="N3" s="104"/>
-      <c r="O3" s="131"/>
-      <c r="P3" s="132"/>
-    </row>
-    <row r="4" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="90"/>
-      <c r="B4" s="126"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="103"/>
-      <c r="K4" s="103"/>
-      <c r="L4" s="129"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="104">
+    <row r="3" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="88"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="101"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="129"/>
+      <c r="P3" s="130"/>
+    </row>
+    <row r="4" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="88"/>
+      <c r="B4" s="124"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="100"/>
+      <c r="J4" s="101"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="127"/>
+      <c r="M4" s="128"/>
+      <c r="N4" s="102">
         <f t="shared" ref="N4:N26" si="0">K4</f>
         <v>0</v>
       </c>
-      <c r="O4" s="131"/>
-    </row>
-    <row r="5" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="90"/>
-      <c r="B5" s="126"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="127"/>
-      <c r="E5" s="128"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="100"/>
-      <c r="H5" s="101"/>
-      <c r="I5" s="102"/>
-      <c r="J5" s="103"/>
-      <c r="K5" s="103"/>
-      <c r="L5" s="129"/>
-      <c r="M5" s="130"/>
-      <c r="N5" s="104">
+      <c r="O4" s="129"/>
+    </row>
+    <row r="5" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="88"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="96"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="101"/>
+      <c r="K5" s="101"/>
+      <c r="L5" s="127"/>
+      <c r="M5" s="128"/>
+      <c r="N5" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O5" s="131"/>
-    </row>
-    <row r="6" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="90"/>
-      <c r="B6" s="126"/>
-      <c r="C6" s="98"/>
-      <c r="D6" s="127"/>
-      <c r="E6" s="128"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="100"/>
-      <c r="H6" s="101"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="103"/>
-      <c r="K6" s="103"/>
-      <c r="L6" s="129"/>
-      <c r="M6" s="130"/>
-      <c r="N6" s="104">
+      <c r="O5" s="129"/>
+    </row>
+    <row r="6" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="88"/>
+      <c r="B6" s="124"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="125"/>
+      <c r="E6" s="126"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="98"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="100"/>
+      <c r="J6" s="101"/>
+      <c r="K6" s="101"/>
+      <c r="L6" s="127"/>
+      <c r="M6" s="128"/>
+      <c r="N6" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O6" s="131"/>
-    </row>
-    <row r="7" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="90"/>
-      <c r="B7" s="126"/>
-      <c r="C7" s="98"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="128"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="100"/>
-      <c r="H7" s="101"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="103"/>
-      <c r="K7" s="103"/>
-      <c r="L7" s="129"/>
-      <c r="M7" s="129"/>
-      <c r="N7" s="104">
+      <c r="O6" s="129"/>
+    </row>
+    <row r="7" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="88"/>
+      <c r="B7" s="124"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="125"/>
+      <c r="E7" s="126"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="98"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="100"/>
+      <c r="J7" s="101"/>
+      <c r="K7" s="101"/>
+      <c r="L7" s="127"/>
+      <c r="M7" s="127"/>
+      <c r="N7" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O7" s="133"/>
-    </row>
-    <row r="8" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="90"/>
-      <c r="B8" s="126"/>
-      <c r="C8" s="98"/>
-      <c r="D8" s="127"/>
-      <c r="E8" s="128"/>
-      <c r="F8" s="102"/>
-      <c r="G8" s="100"/>
-      <c r="H8" s="101"/>
-      <c r="I8" s="102"/>
-      <c r="J8" s="103"/>
-      <c r="K8" s="103"/>
-      <c r="L8" s="129"/>
-      <c r="M8" s="129"/>
-      <c r="N8" s="104"/>
-      <c r="O8" s="134"/>
-    </row>
-    <row r="9" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="90"/>
-      <c r="B9" s="126"/>
-      <c r="C9" s="98"/>
-      <c r="D9" s="127"/>
-      <c r="E9" s="128"/>
-      <c r="F9" s="102"/>
-      <c r="G9" s="100"/>
-      <c r="H9" s="101"/>
-      <c r="I9" s="102"/>
-      <c r="J9" s="103"/>
-      <c r="K9" s="103"/>
-      <c r="L9" s="129"/>
-      <c r="M9" s="99"/>
-      <c r="N9" s="104">
+      <c r="O7" s="131"/>
+    </row>
+    <row r="8" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="88"/>
+      <c r="B8" s="124"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="125"/>
+      <c r="E8" s="126"/>
+      <c r="F8" s="100"/>
+      <c r="G8" s="98"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="100"/>
+      <c r="J8" s="101"/>
+      <c r="K8" s="101"/>
+      <c r="L8" s="127"/>
+      <c r="M8" s="127"/>
+      <c r="N8" s="102"/>
+      <c r="O8" s="132"/>
+    </row>
+    <row r="9" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="88"/>
+      <c r="B9" s="124"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="126"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="98"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="100"/>
+      <c r="J9" s="101"/>
+      <c r="K9" s="101"/>
+      <c r="L9" s="127"/>
+      <c r="M9" s="97"/>
+      <c r="N9" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O9" s="134"/>
-    </row>
-    <row r="10" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="90"/>
-      <c r="B10" s="126"/>
-      <c r="C10" s="98"/>
-      <c r="D10" s="127"/>
-      <c r="E10" s="128"/>
-      <c r="F10" s="102"/>
-      <c r="G10" s="100"/>
-      <c r="H10" s="101"/>
-      <c r="I10" s="102"/>
-      <c r="J10" s="103"/>
-      <c r="K10" s="103"/>
-      <c r="L10" s="129"/>
-      <c r="M10" s="99"/>
-      <c r="N10" s="104"/>
-      <c r="O10" s="134"/>
-    </row>
-    <row r="11" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="90"/>
-      <c r="B11" s="126"/>
-      <c r="C11" s="98"/>
-      <c r="D11" s="127"/>
-      <c r="E11" s="128"/>
-      <c r="F11" s="102"/>
-      <c r="G11" s="100"/>
-      <c r="H11" s="101"/>
-      <c r="I11" s="102"/>
-      <c r="J11" s="103"/>
-      <c r="K11" s="103"/>
-      <c r="L11" s="129"/>
-      <c r="M11" s="130"/>
-      <c r="N11" s="104">
+      <c r="O9" s="132"/>
+    </row>
+    <row r="10" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="88"/>
+      <c r="B10" s="124"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="126"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="98"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="100"/>
+      <c r="J10" s="101"/>
+      <c r="K10" s="101"/>
+      <c r="L10" s="127"/>
+      <c r="M10" s="97"/>
+      <c r="N10" s="102"/>
+      <c r="O10" s="132"/>
+    </row>
+    <row r="11" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="88"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="126"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="98"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="100"/>
+      <c r="J11" s="101"/>
+      <c r="K11" s="101"/>
+      <c r="L11" s="127"/>
+      <c r="M11" s="128"/>
+      <c r="N11" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O11" s="131"/>
-    </row>
-    <row r="12" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="90"/>
-      <c r="B12" s="126"/>
-      <c r="C12" s="98"/>
-      <c r="D12" s="127"/>
-      <c r="E12" s="128"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="100"/>
-      <c r="H12" s="101"/>
-      <c r="I12" s="102"/>
-      <c r="J12" s="103"/>
-      <c r="K12" s="103"/>
-      <c r="L12" s="129"/>
-      <c r="M12" s="130"/>
-      <c r="N12" s="104"/>
-      <c r="O12" s="131"/>
-    </row>
-    <row r="13" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="90"/>
-      <c r="B13" s="126"/>
-      <c r="C13" s="98"/>
-      <c r="D13" s="127"/>
-      <c r="E13" s="128"/>
-      <c r="F13" s="102"/>
-      <c r="G13" s="100"/>
-      <c r="H13" s="101"/>
-      <c r="I13" s="102"/>
-      <c r="J13" s="103"/>
-      <c r="K13" s="103"/>
-      <c r="L13" s="129"/>
-      <c r="M13" s="130"/>
-      <c r="N13" s="104"/>
-      <c r="O13" s="131"/>
-    </row>
-    <row r="14" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="90"/>
-      <c r="B14" s="126"/>
-      <c r="C14" s="98"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="128"/>
-      <c r="F14" s="102"/>
-      <c r="G14" s="100"/>
-      <c r="H14" s="101"/>
-      <c r="I14" s="102"/>
-      <c r="J14" s="103"/>
-      <c r="K14" s="103"/>
-      <c r="L14" s="129"/>
-      <c r="M14" s="129"/>
-      <c r="N14" s="104">
+      <c r="O11" s="129"/>
+    </row>
+    <row r="12" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="88"/>
+      <c r="B12" s="124"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="125"/>
+      <c r="E12" s="126"/>
+      <c r="F12" s="100"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="100"/>
+      <c r="J12" s="101"/>
+      <c r="K12" s="101"/>
+      <c r="L12" s="127"/>
+      <c r="M12" s="128"/>
+      <c r="N12" s="102"/>
+      <c r="O12" s="129"/>
+    </row>
+    <row r="13" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="88"/>
+      <c r="B13" s="124"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="125"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="100"/>
+      <c r="G13" s="98"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="100"/>
+      <c r="J13" s="101"/>
+      <c r="K13" s="101"/>
+      <c r="L13" s="127"/>
+      <c r="M13" s="128"/>
+      <c r="N13" s="102"/>
+      <c r="O13" s="129"/>
+    </row>
+    <row r="14" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="88"/>
+      <c r="B14" s="124"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="125"/>
+      <c r="E14" s="126"/>
+      <c r="F14" s="100"/>
+      <c r="G14" s="98"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="100"/>
+      <c r="J14" s="101"/>
+      <c r="K14" s="101"/>
+      <c r="L14" s="127"/>
+      <c r="M14" s="127"/>
+      <c r="N14" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O14" s="133"/>
-    </row>
-    <row r="15" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="90"/>
-      <c r="B15" s="126"/>
-      <c r="C15" s="98"/>
-      <c r="D15" s="127"/>
-      <c r="E15" s="128"/>
-      <c r="F15" s="102"/>
-      <c r="G15" s="100"/>
-      <c r="H15" s="101"/>
-      <c r="I15" s="102"/>
-      <c r="J15" s="103"/>
-      <c r="K15" s="103"/>
-      <c r="L15" s="129"/>
-      <c r="M15" s="129"/>
-      <c r="N15" s="104"/>
-      <c r="O15" s="133"/>
-    </row>
-    <row r="16" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="90"/>
-      <c r="B16" s="126"/>
-      <c r="C16" s="98"/>
-      <c r="D16" s="127"/>
-      <c r="E16" s="128"/>
-      <c r="F16" s="102"/>
-      <c r="G16" s="100"/>
-      <c r="H16" s="101"/>
-      <c r="I16" s="102"/>
-      <c r="J16" s="103"/>
-      <c r="K16" s="101"/>
-      <c r="L16" s="99"/>
-      <c r="M16" s="99"/>
-      <c r="N16" s="135">
+      <c r="O14" s="131"/>
+    </row>
+    <row r="15" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="88"/>
+      <c r="B15" s="124"/>
+      <c r="C15" s="96"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="126"/>
+      <c r="F15" s="100"/>
+      <c r="G15" s="98"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="100"/>
+      <c r="J15" s="101"/>
+      <c r="K15" s="101"/>
+      <c r="L15" s="127"/>
+      <c r="M15" s="127"/>
+      <c r="N15" s="102"/>
+      <c r="O15" s="131"/>
+    </row>
+    <row r="16" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="88"/>
+      <c r="B16" s="124"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="125"/>
+      <c r="E16" s="126"/>
+      <c r="F16" s="100"/>
+      <c r="G16" s="98"/>
+      <c r="H16" s="99"/>
+      <c r="I16" s="100"/>
+      <c r="J16" s="101"/>
+      <c r="K16" s="99"/>
+      <c r="L16" s="97"/>
+      <c r="M16" s="97"/>
+      <c r="N16" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O16" s="136"/>
-    </row>
-    <row r="17" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="90"/>
-      <c r="B17" s="126"/>
-      <c r="C17" s="98"/>
-      <c r="D17" s="127"/>
-      <c r="E17" s="128"/>
-      <c r="F17" s="102"/>
-      <c r="G17" s="100"/>
-      <c r="H17" s="101"/>
-      <c r="I17" s="102"/>
-      <c r="J17" s="103"/>
-      <c r="K17" s="103"/>
-      <c r="L17" s="129"/>
-      <c r="M17" s="130"/>
-      <c r="N17" s="104">
+      <c r="O16" s="134"/>
+    </row>
+    <row r="17" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="88"/>
+      <c r="B17" s="124"/>
+      <c r="C17" s="96"/>
+      <c r="D17" s="125"/>
+      <c r="E17" s="126"/>
+      <c r="F17" s="100"/>
+      <c r="G17" s="98"/>
+      <c r="H17" s="99"/>
+      <c r="I17" s="100"/>
+      <c r="J17" s="101"/>
+      <c r="K17" s="101"/>
+      <c r="L17" s="127"/>
+      <c r="M17" s="128"/>
+      <c r="N17" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O17" s="131"/>
-    </row>
-    <row r="18" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="90"/>
-      <c r="B18" s="126"/>
-      <c r="C18" s="98"/>
-      <c r="D18" s="127"/>
-      <c r="E18" s="128"/>
-      <c r="F18" s="102"/>
-      <c r="G18" s="100"/>
-      <c r="H18" s="101"/>
-      <c r="I18" s="102"/>
-      <c r="J18" s="103"/>
-      <c r="K18" s="103"/>
-      <c r="L18" s="129"/>
-      <c r="M18" s="130"/>
-      <c r="N18" s="104">
+      <c r="O17" s="129"/>
+    </row>
+    <row r="18" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="88"/>
+      <c r="B18" s="124"/>
+      <c r="C18" s="96"/>
+      <c r="D18" s="125"/>
+      <c r="E18" s="126"/>
+      <c r="F18" s="100"/>
+      <c r="G18" s="98"/>
+      <c r="H18" s="99"/>
+      <c r="I18" s="100"/>
+      <c r="J18" s="101"/>
+      <c r="K18" s="101"/>
+      <c r="L18" s="127"/>
+      <c r="M18" s="128"/>
+      <c r="N18" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O18" s="131"/>
-    </row>
-    <row r="19" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="90"/>
-      <c r="B19" s="126"/>
-      <c r="C19" s="98"/>
-      <c r="D19" s="127"/>
-      <c r="E19" s="128"/>
-      <c r="F19" s="102"/>
-      <c r="G19" s="100"/>
-      <c r="H19" s="101"/>
-      <c r="I19" s="102"/>
-      <c r="J19" s="103"/>
-      <c r="K19" s="103"/>
-      <c r="L19" s="129"/>
-      <c r="M19" s="129"/>
-      <c r="N19" s="104">
+      <c r="O18" s="129"/>
+    </row>
+    <row r="19" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="88"/>
+      <c r="B19" s="124"/>
+      <c r="C19" s="96"/>
+      <c r="D19" s="125"/>
+      <c r="E19" s="126"/>
+      <c r="F19" s="100"/>
+      <c r="G19" s="98"/>
+      <c r="H19" s="99"/>
+      <c r="I19" s="100"/>
+      <c r="J19" s="101"/>
+      <c r="K19" s="101"/>
+      <c r="L19" s="127"/>
+      <c r="M19" s="127"/>
+      <c r="N19" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O19" s="133"/>
-    </row>
-    <row r="20" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="90"/>
-      <c r="B20" s="126"/>
-      <c r="C20" s="98"/>
-      <c r="D20" s="127"/>
-      <c r="E20" s="128"/>
-      <c r="F20" s="102"/>
-      <c r="G20" s="100"/>
-      <c r="H20" s="101"/>
-      <c r="I20" s="102"/>
-      <c r="J20" s="103"/>
-      <c r="K20" s="103"/>
-      <c r="L20" s="129"/>
-      <c r="M20" s="130"/>
-      <c r="N20" s="104">
+      <c r="O19" s="131"/>
+    </row>
+    <row r="20" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="88"/>
+      <c r="B20" s="124"/>
+      <c r="C20" s="96"/>
+      <c r="D20" s="125"/>
+      <c r="E20" s="126"/>
+      <c r="F20" s="100"/>
+      <c r="G20" s="98"/>
+      <c r="H20" s="99"/>
+      <c r="I20" s="100"/>
+      <c r="J20" s="101"/>
+      <c r="K20" s="101"/>
+      <c r="L20" s="127"/>
+      <c r="M20" s="128"/>
+      <c r="N20" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O20" s="131"/>
-    </row>
-    <row r="21" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="90"/>
-      <c r="B21" s="126"/>
-      <c r="C21" s="98"/>
-      <c r="D21" s="127"/>
-      <c r="E21" s="128"/>
-      <c r="F21" s="102"/>
-      <c r="G21" s="100"/>
-      <c r="H21" s="101"/>
-      <c r="I21" s="102"/>
-      <c r="J21" s="103"/>
-      <c r="K21" s="103"/>
-      <c r="L21" s="129"/>
-      <c r="M21" s="137"/>
-      <c r="N21" s="104">
+      <c r="O20" s="129"/>
+    </row>
+    <row r="21" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="88"/>
+      <c r="B21" s="124"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="125"/>
+      <c r="E21" s="126"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="98"/>
+      <c r="H21" s="99"/>
+      <c r="I21" s="100"/>
+      <c r="J21" s="101"/>
+      <c r="K21" s="101"/>
+      <c r="L21" s="127"/>
+      <c r="M21" s="135"/>
+      <c r="N21" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O21" s="133"/>
-    </row>
-    <row r="22" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="90"/>
-      <c r="B22" s="126"/>
-      <c r="C22" s="98"/>
-      <c r="D22" s="127"/>
-      <c r="E22" s="128"/>
-      <c r="F22" s="102"/>
-      <c r="G22" s="100"/>
-      <c r="H22" s="101"/>
-      <c r="I22" s="102"/>
-      <c r="J22" s="103"/>
-      <c r="K22" s="103"/>
-      <c r="L22" s="129"/>
-      <c r="M22" s="137"/>
-      <c r="N22" s="104"/>
-      <c r="O22" s="131"/>
-    </row>
-    <row r="23" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="90"/>
-      <c r="B23" s="126"/>
-      <c r="C23" s="98"/>
-      <c r="D23" s="127"/>
-      <c r="E23" s="128"/>
-      <c r="F23" s="102"/>
-      <c r="G23" s="100"/>
-      <c r="H23" s="101"/>
-      <c r="I23" s="102"/>
-      <c r="J23" s="103"/>
-      <c r="K23" s="103"/>
-      <c r="L23" s="129"/>
-      <c r="M23" s="129"/>
-      <c r="N23" s="104">
+      <c r="O21" s="131"/>
+    </row>
+    <row r="22" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="88"/>
+      <c r="B22" s="124"/>
+      <c r="C22" s="96"/>
+      <c r="D22" s="125"/>
+      <c r="E22" s="126"/>
+      <c r="F22" s="100"/>
+      <c r="G22" s="98"/>
+      <c r="H22" s="99"/>
+      <c r="I22" s="100"/>
+      <c r="J22" s="101"/>
+      <c r="K22" s="101"/>
+      <c r="L22" s="127"/>
+      <c r="M22" s="135"/>
+      <c r="N22" s="102"/>
+      <c r="O22" s="129"/>
+    </row>
+    <row r="23" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="88"/>
+      <c r="B23" s="124"/>
+      <c r="C23" s="96"/>
+      <c r="D23" s="125"/>
+      <c r="E23" s="126"/>
+      <c r="F23" s="100"/>
+      <c r="G23" s="98"/>
+      <c r="H23" s="99"/>
+      <c r="I23" s="100"/>
+      <c r="J23" s="101"/>
+      <c r="K23" s="101"/>
+      <c r="L23" s="127"/>
+      <c r="M23" s="127"/>
+      <c r="N23" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O23" s="138"/>
-    </row>
-    <row r="24" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="90"/>
-      <c r="B24" s="126"/>
-      <c r="C24" s="98"/>
-      <c r="D24" s="127"/>
-      <c r="E24" s="128"/>
-      <c r="F24" s="102"/>
-      <c r="G24" s="100"/>
-      <c r="H24" s="101"/>
-      <c r="I24" s="102"/>
-      <c r="J24" s="103"/>
-      <c r="K24" s="103"/>
-      <c r="L24" s="129"/>
-      <c r="M24" s="129"/>
-      <c r="N24" s="104">
+      <c r="O23" s="136"/>
+    </row>
+    <row r="24" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="88"/>
+      <c r="B24" s="124"/>
+      <c r="C24" s="96"/>
+      <c r="D24" s="125"/>
+      <c r="E24" s="126"/>
+      <c r="F24" s="100"/>
+      <c r="G24" s="98"/>
+      <c r="H24" s="99"/>
+      <c r="I24" s="100"/>
+      <c r="J24" s="101"/>
+      <c r="K24" s="101"/>
+      <c r="L24" s="127"/>
+      <c r="M24" s="127"/>
+      <c r="N24" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O24" s="131"/>
-    </row>
-    <row r="25" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="90"/>
-      <c r="B25" s="126"/>
-      <c r="C25" s="98"/>
-      <c r="D25" s="127"/>
-      <c r="E25" s="128"/>
-      <c r="F25" s="102"/>
-      <c r="G25" s="100"/>
-      <c r="H25" s="101"/>
-      <c r="I25" s="102"/>
-      <c r="J25" s="103"/>
-      <c r="K25" s="103"/>
-      <c r="L25" s="129"/>
-      <c r="M25" s="129"/>
-      <c r="N25" s="104"/>
-      <c r="O25" s="131"/>
-    </row>
-    <row r="26" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="90"/>
-      <c r="B26" s="126"/>
-      <c r="C26" s="98"/>
-      <c r="D26" s="127"/>
-      <c r="E26" s="128"/>
-      <c r="F26" s="102"/>
-      <c r="G26" s="100"/>
-      <c r="H26" s="101"/>
-      <c r="I26" s="102"/>
-      <c r="J26" s="103"/>
-      <c r="K26" s="103"/>
-      <c r="L26" s="129"/>
-      <c r="M26" s="137"/>
-      <c r="N26" s="104">
+      <c r="O24" s="129"/>
+    </row>
+    <row r="25" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="88"/>
+      <c r="B25" s="124"/>
+      <c r="C25" s="96"/>
+      <c r="D25" s="125"/>
+      <c r="E25" s="126"/>
+      <c r="F25" s="100"/>
+      <c r="G25" s="98"/>
+      <c r="H25" s="99"/>
+      <c r="I25" s="100"/>
+      <c r="J25" s="101"/>
+      <c r="K25" s="101"/>
+      <c r="L25" s="127"/>
+      <c r="M25" s="127"/>
+      <c r="N25" s="102"/>
+      <c r="O25" s="129"/>
+    </row>
+    <row r="26" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="88"/>
+      <c r="B26" s="124"/>
+      <c r="C26" s="96"/>
+      <c r="D26" s="125"/>
+      <c r="E26" s="126"/>
+      <c r="F26" s="100"/>
+      <c r="G26" s="98"/>
+      <c r="H26" s="99"/>
+      <c r="I26" s="100"/>
+      <c r="J26" s="101"/>
+      <c r="K26" s="101"/>
+      <c r="L26" s="127"/>
+      <c r="M26" s="135"/>
+      <c r="N26" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O26" s="131"/>
-    </row>
-    <row r="27" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="90"/>
-      <c r="B27" s="126"/>
-      <c r="C27" s="98"/>
-      <c r="D27" s="127"/>
-      <c r="E27" s="128"/>
-      <c r="F27" s="102"/>
-      <c r="G27" s="100"/>
-      <c r="H27" s="101"/>
-      <c r="I27" s="102"/>
-      <c r="J27" s="103"/>
-      <c r="K27" s="103"/>
-      <c r="L27" s="129"/>
-      <c r="M27" s="137"/>
-      <c r="N27" s="104"/>
-      <c r="O27" s="131"/>
-    </row>
-    <row r="28" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="139"/>
-      <c r="C28" s="100"/>
-      <c r="D28" s="91">
+      <c r="O26" s="129"/>
+    </row>
+    <row r="27" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="88"/>
+      <c r="B27" s="124"/>
+      <c r="C27" s="96"/>
+      <c r="D27" s="125"/>
+      <c r="E27" s="126"/>
+      <c r="F27" s="100"/>
+      <c r="G27" s="98"/>
+      <c r="H27" s="99"/>
+      <c r="I27" s="100"/>
+      <c r="J27" s="101"/>
+      <c r="K27" s="101"/>
+      <c r="L27" s="127"/>
+      <c r="M27" s="135"/>
+      <c r="N27" s="102"/>
+      <c r="O27" s="129"/>
+    </row>
+    <row r="28" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="137"/>
+      <c r="C28" s="98"/>
+      <c r="D28" s="89">
         <f>SUM(D3:D27)</f>
         <v>0</v>
       </c>
-      <c r="E28" s="140"/>
-      <c r="F28" s="100" t="s">
+      <c r="E28" s="138"/>
+      <c r="F28" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="G28" s="100"/>
-      <c r="H28" s="101"/>
-      <c r="I28" s="100"/>
-      <c r="J28" s="103"/>
-      <c r="K28" s="135"/>
-      <c r="L28" s="99"/>
-      <c r="M28" s="99"/>
-      <c r="N28" s="135">
+      <c r="G28" s="98"/>
+      <c r="H28" s="99"/>
+      <c r="I28" s="98"/>
+      <c r="J28" s="101"/>
+      <c r="K28" s="133"/>
+      <c r="L28" s="97"/>
+      <c r="M28" s="97"/>
+      <c r="N28" s="133">
         <f>SUM(N3:N27)</f>
         <v>0</v>
       </c>
-      <c r="O28" s="115"/>
-    </row>
-    <row r="29" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="147" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="148"/>
-      <c r="D29" s="148"/>
-      <c r="E29" s="148"/>
-      <c r="F29" s="148"/>
-      <c r="G29" s="148"/>
-      <c r="H29" s="148"/>
-      <c r="I29" s="148"/>
-      <c r="J29" s="148"/>
-      <c r="K29" s="148"/>
-      <c r="L29" s="148"/>
-      <c r="M29" s="148"/>
-      <c r="N29" s="148"/>
-      <c r="O29" s="149"/>
-    </row>
-    <row r="30" spans="1:15" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="141" t="s">
+      <c r="O28" s="113"/>
+    </row>
+    <row r="29" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="144" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="145"/>
+      <c r="D29" s="145"/>
+      <c r="E29" s="145"/>
+      <c r="F29" s="145"/>
+      <c r="G29" s="145"/>
+      <c r="H29" s="145"/>
+      <c r="I29" s="145"/>
+      <c r="J29" s="145"/>
+      <c r="K29" s="145"/>
+      <c r="L29" s="145"/>
+      <c r="M29" s="145"/>
+      <c r="N29" s="145"/>
+      <c r="O29" s="146"/>
+    </row>
+    <row r="30" spans="1:15" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="74"/>
-      <c r="D30" s="75" t="s">
+      <c r="C30" s="72"/>
+      <c r="D30" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="E30" s="80"/>
-      <c r="F30" s="78"/>
-      <c r="G30" s="75" t="s">
+      <c r="E30" s="78"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="H30" s="72"/>
-      <c r="J30" s="78"/>
-      <c r="K30" s="116" t="s">
+      <c r="H30" s="70"/>
+      <c r="J30" s="76"/>
+      <c r="K30" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="L30" s="78"/>
-      <c r="M30" s="72"/>
-      <c r="N30" s="72" t="s">
+      <c r="L30" s="76"/>
+      <c r="M30" s="70"/>
+      <c r="N30" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="O30" s="117" t="s">
+      <c r="O30" s="115" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="88" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="64"/>
-      <c r="C31" s="74"/>
-      <c r="D31" s="75" t="s">
+    <row r="31" spans="1:15" ht="87.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="62"/>
+      <c r="C31" s="72"/>
+      <c r="D31" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="80"/>
-      <c r="F31" s="78"/>
-      <c r="G31" s="75" t="s">
+      <c r="E31" s="78"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="H31" s="72"/>
-      <c r="J31" s="78"/>
-      <c r="K31" s="116" t="s">
+      <c r="H31" s="70"/>
+      <c r="J31" s="76"/>
+      <c r="K31" s="114" t="s">
         <v>24</v>
       </c>
-      <c r="L31" s="78"/>
-      <c r="M31" s="72"/>
-      <c r="N31" s="72" t="s">
+      <c r="L31" s="76"/>
+      <c r="M31" s="70"/>
+      <c r="N31" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="O31" s="82"/>
-    </row>
-    <row r="32" spans="1:15" ht="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="K32" s="143" t="s">
+      <c r="O31" s="80"/>
+    </row>
+    <row r="32" spans="1:15" ht="0.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K32" s="141" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="2:16" ht="23.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="34" spans="2:16" s="112" customFormat="1" ht="33.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="67"/>
-      <c r="C34" s="96"/>
-      <c r="D34" s="96"/>
-      <c r="E34" s="142"/>
-      <c r="F34" s="118"/>
-      <c r="G34" s="118"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="78"/>
-      <c r="J34" s="88"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="96"/>
-      <c r="M34" s="96"/>
-      <c r="N34" s="96"/>
-      <c r="O34" s="121"/>
-      <c r="P34" s="96"/>
-    </row>
-    <row r="35" spans="2:16" s="112" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="67"/>
-      <c r="C35" s="96"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="142"/>
-      <c r="F35" s="118"/>
-      <c r="G35" s="118"/>
-      <c r="H35" s="88"/>
-      <c r="I35" s="78"/>
-      <c r="J35" s="88"/>
-      <c r="K35" s="88"/>
-      <c r="L35" s="96"/>
-      <c r="M35" s="96"/>
-      <c r="N35" s="96"/>
-      <c r="O35" s="121"/>
-      <c r="P35" s="96"/>
+    <row r="33" spans="2:16" ht="23.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="2:16" s="110" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="65"/>
+      <c r="C34" s="94"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="140"/>
+      <c r="F34" s="116"/>
+      <c r="G34" s="116"/>
+      <c r="H34" s="86"/>
+      <c r="I34" s="76"/>
+      <c r="J34" s="86"/>
+      <c r="K34" s="86"/>
+      <c r="L34" s="94"/>
+      <c r="M34" s="94"/>
+      <c r="N34" s="94"/>
+      <c r="O34" s="119"/>
+      <c r="P34" s="94"/>
+    </row>
+    <row r="35" spans="2:16" s="110" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="65"/>
+      <c r="C35" s="94"/>
+      <c r="D35" s="94"/>
+      <c r="E35" s="140"/>
+      <c r="F35" s="116"/>
+      <c r="G35" s="116"/>
+      <c r="H35" s="86"/>
+      <c r="I35" s="76"/>
+      <c r="J35" s="86"/>
+      <c r="K35" s="86"/>
+      <c r="L35" s="94"/>
+      <c r="M35" s="94"/>
+      <c r="N35" s="94"/>
+      <c r="O35" s="119"/>
+      <c r="P35" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1936,611 +1927,611 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:BY14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0" style="112" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="10.1796875" style="112" customWidth="1"/>
-    <col min="3" max="3" width="14.1796875" style="96" customWidth="1"/>
-    <col min="4" max="4" width="10.54296875" style="96" customWidth="1"/>
-    <col min="5" max="5" width="0" style="96" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="5" style="118" customWidth="1"/>
-    <col min="7" max="7" width="5.453125" style="118" customWidth="1"/>
-    <col min="8" max="8" width="8.90625" style="112" customWidth="1"/>
-    <col min="9" max="9" width="6.453125" style="78" customWidth="1"/>
-    <col min="10" max="10" width="6.453125" style="88" customWidth="1"/>
-    <col min="11" max="11" width="10.36328125" style="88" customWidth="1"/>
-    <col min="12" max="12" width="9" style="119" customWidth="1"/>
-    <col min="13" max="13" width="11.90625" style="88" customWidth="1"/>
-    <col min="14" max="14" width="23.453125" style="120" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="96"/>
+    <col min="1" max="1" width="0" style="110" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="10.125" style="110" customWidth="1"/>
+    <col min="3" max="3" width="14.125" style="94" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="94" customWidth="1"/>
+    <col min="5" max="5" width="0" style="94" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="5" style="116" customWidth="1"/>
+    <col min="7" max="7" width="5.5" style="116" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="110" customWidth="1"/>
+    <col min="9" max="9" width="6.5" style="76" customWidth="1"/>
+    <col min="10" max="10" width="6.5" style="86" customWidth="1"/>
+    <col min="11" max="11" width="10.375" style="86" customWidth="1"/>
+    <col min="12" max="12" width="9" style="117" customWidth="1"/>
+    <col min="13" max="13" width="11.875" style="86" customWidth="1"/>
+    <col min="14" max="14" width="23.5" style="118" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="94"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77" s="88" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="150" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-    </row>
-    <row r="2" spans="1:77" ht="28.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="89" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="90" t="s">
+    <row r="1" spans="1:77" s="86" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="147" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+    </row>
+    <row r="2" spans="1:77" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="87" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="91" t="s">
+      <c r="C2" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="92" t="s">
+      <c r="D2" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="93" t="s">
+      <c r="E2" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="92" t="s">
+      <c r="F2" s="90" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="92" t="s">
+      <c r="G2" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="92" t="s">
+      <c r="H2" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="92" t="s">
+      <c r="I2" s="90" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="92" t="s">
+      <c r="J2" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="94" t="s">
+      <c r="K2" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="95" t="s">
+      <c r="L2" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="94" t="s">
+      <c r="M2" s="92" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="91" t="s">
+      <c r="N2" s="89" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:77" s="109" customFormat="1" ht="30.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="97"/>
-      <c r="B3" s="90"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="104"/>
-      <c r="L3" s="105"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="107"/>
-      <c r="O3" s="108"/>
-      <c r="P3" s="108"/>
-    </row>
-    <row r="4" spans="1:77" s="109" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="110"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="98"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="103"/>
-      <c r="K4" s="104"/>
-      <c r="L4" s="105"/>
-      <c r="M4" s="106"/>
-      <c r="N4" s="107"/>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108"/>
-    </row>
-    <row r="5" spans="1:77" s="109" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="110"/>
-      <c r="B5" s="90"/>
-      <c r="C5" s="91"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="100"/>
-      <c r="H5" s="101"/>
-      <c r="I5" s="102"/>
-      <c r="J5" s="103"/>
-      <c r="K5" s="104"/>
-      <c r="L5" s="105"/>
-      <c r="M5" s="106"/>
-      <c r="N5" s="107"/>
-      <c r="O5" s="108"/>
-      <c r="P5" s="108"/>
-    </row>
-    <row r="6" spans="1:77" s="109" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="110"/>
-      <c r="B6" s="90"/>
-      <c r="C6" s="91"/>
-      <c r="D6" s="98"/>
-      <c r="E6" s="99"/>
-      <c r="F6" s="100"/>
-      <c r="G6" s="100"/>
-      <c r="H6" s="101"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="103"/>
-      <c r="K6" s="104"/>
-      <c r="L6" s="105"/>
-      <c r="M6" s="106"/>
-      <c r="N6" s="107"/>
-      <c r="O6" s="108"/>
-      <c r="P6" s="108"/>
-    </row>
-    <row r="7" spans="1:77" s="109" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="110"/>
-      <c r="B7" s="90"/>
-      <c r="C7" s="91"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="99"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="100"/>
-      <c r="H7" s="101"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="103"/>
-      <c r="K7" s="104"/>
-      <c r="L7" s="105"/>
-      <c r="M7" s="106"/>
-      <c r="N7" s="107"/>
-      <c r="O7" s="108"/>
-      <c r="P7" s="108"/>
-    </row>
-    <row r="8" spans="1:77" s="109" customFormat="1" ht="32.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="110"/>
-      <c r="B8" s="90"/>
-      <c r="C8" s="91"/>
-      <c r="D8" s="98"/>
-      <c r="E8" s="99"/>
-      <c r="F8" s="100"/>
-      <c r="G8" s="100"/>
-      <c r="H8" s="101"/>
-      <c r="I8" s="102"/>
-      <c r="J8" s="103"/>
-      <c r="K8" s="104"/>
-      <c r="L8" s="105"/>
-      <c r="M8" s="106"/>
-      <c r="N8" s="111"/>
-      <c r="O8" s="108"/>
-      <c r="P8" s="108"/>
-    </row>
-    <row r="9" spans="1:77" s="109" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="110"/>
-      <c r="B9" s="90"/>
-      <c r="C9" s="91"/>
-      <c r="D9" s="98"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="100"/>
-      <c r="G9" s="100"/>
-      <c r="H9" s="101"/>
-      <c r="I9" s="102"/>
-      <c r="J9" s="103"/>
-      <c r="K9" s="104"/>
-      <c r="L9" s="105"/>
-      <c r="M9" s="106"/>
-      <c r="N9" s="107"/>
-      <c r="O9" s="108"/>
-      <c r="P9" s="108"/>
-    </row>
-    <row r="10" spans="1:77" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="101"/>
-      <c r="C10" s="100"/>
-      <c r="D10" s="100"/>
-      <c r="E10" s="100"/>
-      <c r="F10" s="100"/>
-      <c r="G10" s="100"/>
-      <c r="H10" s="100"/>
-      <c r="I10" s="102"/>
-      <c r="J10" s="100"/>
-      <c r="K10" s="113"/>
-      <c r="L10" s="114"/>
-      <c r="M10" s="113"/>
-      <c r="N10" s="115"/>
-      <c r="O10" s="80"/>
-      <c r="P10" s="80"/>
-      <c r="Q10" s="80"/>
-      <c r="R10" s="80"/>
-      <c r="S10" s="80"/>
-      <c r="T10" s="80"/>
-      <c r="U10" s="80"/>
-      <c r="V10" s="80"/>
-      <c r="W10" s="80"/>
-      <c r="X10" s="80"/>
-      <c r="Y10" s="80"/>
-      <c r="Z10" s="80"/>
-      <c r="AA10" s="80"/>
-      <c r="AB10" s="80"/>
-      <c r="AC10" s="80"/>
-      <c r="AD10" s="80"/>
-      <c r="AE10" s="80"/>
-      <c r="AF10" s="80"/>
-      <c r="AG10" s="80"/>
-      <c r="AH10" s="80"/>
-      <c r="AI10" s="80"/>
-      <c r="AJ10" s="80"/>
-      <c r="AK10" s="80"/>
-      <c r="AL10" s="80"/>
-      <c r="AM10" s="80"/>
-      <c r="AN10" s="80"/>
-      <c r="AO10" s="80"/>
-      <c r="AP10" s="80"/>
-      <c r="AQ10" s="80"/>
-      <c r="AR10" s="80"/>
-      <c r="AS10" s="80"/>
-      <c r="AT10" s="80"/>
-      <c r="AU10" s="80"/>
-      <c r="AV10" s="80"/>
-      <c r="AW10" s="80"/>
-      <c r="AX10" s="80"/>
-      <c r="AY10" s="80"/>
-      <c r="AZ10" s="80"/>
-      <c r="BA10" s="80"/>
-      <c r="BB10" s="80"/>
-      <c r="BC10" s="80"/>
-      <c r="BD10" s="80"/>
-      <c r="BE10" s="80"/>
-      <c r="BF10" s="80"/>
-      <c r="BG10" s="80"/>
-      <c r="BH10" s="80"/>
-      <c r="BI10" s="80"/>
-      <c r="BJ10" s="80"/>
-      <c r="BK10" s="80"/>
-      <c r="BL10" s="80"/>
-      <c r="BM10" s="80"/>
-      <c r="BN10" s="80"/>
-      <c r="BO10" s="80"/>
-      <c r="BP10" s="80"/>
-      <c r="BQ10" s="80"/>
-      <c r="BR10" s="80"/>
-      <c r="BS10" s="80"/>
-      <c r="BT10" s="80"/>
-      <c r="BU10" s="80"/>
-      <c r="BV10" s="80"/>
-      <c r="BW10" s="80"/>
-      <c r="BX10" s="80"/>
-      <c r="BY10" s="80"/>
-    </row>
-    <row r="11" spans="1:77" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="151"/>
-      <c r="C11" s="152"/>
-      <c r="D11" s="152"/>
-      <c r="E11" s="152"/>
-      <c r="F11" s="152"/>
-      <c r="G11" s="152"/>
-      <c r="H11" s="152"/>
-      <c r="I11" s="152"/>
-      <c r="J11" s="152"/>
-      <c r="K11" s="152"/>
-      <c r="L11" s="152"/>
-      <c r="M11" s="152"/>
-      <c r="N11" s="152"/>
-      <c r="O11" s="80"/>
-      <c r="P11" s="80"/>
-      <c r="Q11" s="80"/>
-      <c r="R11" s="80"/>
-      <c r="S11" s="80"/>
-      <c r="T11" s="80"/>
-      <c r="U11" s="80"/>
-      <c r="V11" s="80"/>
-      <c r="W11" s="80"/>
-      <c r="X11" s="80"/>
-      <c r="Y11" s="80"/>
-      <c r="Z11" s="80"/>
-      <c r="AA11" s="80"/>
-      <c r="AB11" s="80"/>
-      <c r="AC11" s="80"/>
-      <c r="AD11" s="80"/>
-      <c r="AE11" s="80"/>
-      <c r="AF11" s="80"/>
-      <c r="AG11" s="80"/>
-      <c r="AH11" s="80"/>
-      <c r="AI11" s="80"/>
-      <c r="AJ11" s="80"/>
-      <c r="AK11" s="80"/>
-      <c r="AL11" s="80"/>
-      <c r="AM11" s="80"/>
-      <c r="AN11" s="80"/>
-      <c r="AO11" s="80"/>
-      <c r="AP11" s="80"/>
-      <c r="AQ11" s="80"/>
-      <c r="AR11" s="80"/>
-      <c r="AS11" s="80"/>
-      <c r="AT11" s="80"/>
-      <c r="AU11" s="80"/>
-      <c r="AV11" s="80"/>
-      <c r="AW11" s="80"/>
-      <c r="AX11" s="80"/>
-      <c r="AY11" s="80"/>
-      <c r="AZ11" s="80"/>
-      <c r="BA11" s="80"/>
-      <c r="BB11" s="80"/>
-      <c r="BC11" s="80"/>
-      <c r="BD11" s="80"/>
-      <c r="BE11" s="80"/>
-      <c r="BF11" s="80"/>
-      <c r="BG11" s="80"/>
-      <c r="BH11" s="80"/>
-      <c r="BI11" s="80"/>
-      <c r="BJ11" s="80"/>
-      <c r="BK11" s="80"/>
-      <c r="BL11" s="80"/>
-      <c r="BM11" s="80"/>
-      <c r="BN11" s="80"/>
-      <c r="BO11" s="80"/>
-      <c r="BP11" s="80"/>
-      <c r="BQ11" s="80"/>
-      <c r="BR11" s="80"/>
-      <c r="BS11" s="80"/>
-      <c r="BT11" s="80"/>
-      <c r="BU11" s="80"/>
-      <c r="BV11" s="80"/>
-      <c r="BW11" s="80"/>
-      <c r="BX11" s="80"/>
-      <c r="BY11" s="80"/>
-    </row>
-    <row r="12" spans="1:77" s="80" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="116" t="s">
+    <row r="3" spans="1:77" s="107" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="95"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="104"/>
+      <c r="N3" s="105"/>
+      <c r="O3" s="106"/>
+      <c r="P3" s="106"/>
+    </row>
+    <row r="4" spans="1:77" s="107" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="108"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="100"/>
+      <c r="J4" s="101"/>
+      <c r="K4" s="102"/>
+      <c r="L4" s="103"/>
+      <c r="M4" s="104"/>
+      <c r="N4" s="105"/>
+      <c r="O4" s="106"/>
+      <c r="P4" s="106"/>
+    </row>
+    <row r="5" spans="1:77" s="107" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="108"/>
+      <c r="B5" s="88"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="101"/>
+      <c r="K5" s="102"/>
+      <c r="L5" s="103"/>
+      <c r="M5" s="104"/>
+      <c r="N5" s="105"/>
+      <c r="O5" s="106"/>
+      <c r="P5" s="106"/>
+    </row>
+    <row r="6" spans="1:77" s="107" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="108"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="96"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="98"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="100"/>
+      <c r="J6" s="101"/>
+      <c r="K6" s="102"/>
+      <c r="L6" s="103"/>
+      <c r="M6" s="104"/>
+      <c r="N6" s="105"/>
+      <c r="O6" s="106"/>
+      <c r="P6" s="106"/>
+    </row>
+    <row r="7" spans="1:77" s="107" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="108"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="89"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="97"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="98"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="100"/>
+      <c r="J7" s="101"/>
+      <c r="K7" s="102"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="104"/>
+      <c r="N7" s="105"/>
+      <c r="O7" s="106"/>
+      <c r="P7" s="106"/>
+    </row>
+    <row r="8" spans="1:77" s="107" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="108"/>
+      <c r="B8" s="88"/>
+      <c r="C8" s="89"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="98"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="100"/>
+      <c r="J8" s="101"/>
+      <c r="K8" s="102"/>
+      <c r="L8" s="103"/>
+      <c r="M8" s="104"/>
+      <c r="N8" s="109"/>
+      <c r="O8" s="106"/>
+      <c r="P8" s="106"/>
+    </row>
+    <row r="9" spans="1:77" s="107" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="108"/>
+      <c r="B9" s="88"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="97"/>
+      <c r="F9" s="98"/>
+      <c r="G9" s="98"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="100"/>
+      <c r="J9" s="101"/>
+      <c r="K9" s="102"/>
+      <c r="L9" s="103"/>
+      <c r="M9" s="104"/>
+      <c r="N9" s="105"/>
+      <c r="O9" s="106"/>
+      <c r="P9" s="106"/>
+    </row>
+    <row r="10" spans="1:77" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="99"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="98"/>
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98"/>
+      <c r="H10" s="98"/>
+      <c r="I10" s="100"/>
+      <c r="J10" s="98"/>
+      <c r="K10" s="111"/>
+      <c r="L10" s="112"/>
+      <c r="M10" s="111"/>
+      <c r="N10" s="113"/>
+      <c r="O10" s="78"/>
+      <c r="P10" s="78"/>
+      <c r="Q10" s="78"/>
+      <c r="R10" s="78"/>
+      <c r="S10" s="78"/>
+      <c r="T10" s="78"/>
+      <c r="U10" s="78"/>
+      <c r="V10" s="78"/>
+      <c r="W10" s="78"/>
+      <c r="X10" s="78"/>
+      <c r="Y10" s="78"/>
+      <c r="Z10" s="78"/>
+      <c r="AA10" s="78"/>
+      <c r="AB10" s="78"/>
+      <c r="AC10" s="78"/>
+      <c r="AD10" s="78"/>
+      <c r="AE10" s="78"/>
+      <c r="AF10" s="78"/>
+      <c r="AG10" s="78"/>
+      <c r="AH10" s="78"/>
+      <c r="AI10" s="78"/>
+      <c r="AJ10" s="78"/>
+      <c r="AK10" s="78"/>
+      <c r="AL10" s="78"/>
+      <c r="AM10" s="78"/>
+      <c r="AN10" s="78"/>
+      <c r="AO10" s="78"/>
+      <c r="AP10" s="78"/>
+      <c r="AQ10" s="78"/>
+      <c r="AR10" s="78"/>
+      <c r="AS10" s="78"/>
+      <c r="AT10" s="78"/>
+      <c r="AU10" s="78"/>
+      <c r="AV10" s="78"/>
+      <c r="AW10" s="78"/>
+      <c r="AX10" s="78"/>
+      <c r="AY10" s="78"/>
+      <c r="AZ10" s="78"/>
+      <c r="BA10" s="78"/>
+      <c r="BB10" s="78"/>
+      <c r="BC10" s="78"/>
+      <c r="BD10" s="78"/>
+      <c r="BE10" s="78"/>
+      <c r="BF10" s="78"/>
+      <c r="BG10" s="78"/>
+      <c r="BH10" s="78"/>
+      <c r="BI10" s="78"/>
+      <c r="BJ10" s="78"/>
+      <c r="BK10" s="78"/>
+      <c r="BL10" s="78"/>
+      <c r="BM10" s="78"/>
+      <c r="BN10" s="78"/>
+      <c r="BO10" s="78"/>
+      <c r="BP10" s="78"/>
+      <c r="BQ10" s="78"/>
+      <c r="BR10" s="78"/>
+      <c r="BS10" s="78"/>
+      <c r="BT10" s="78"/>
+      <c r="BU10" s="78"/>
+      <c r="BV10" s="78"/>
+      <c r="BW10" s="78"/>
+      <c r="BX10" s="78"/>
+      <c r="BY10" s="78"/>
+    </row>
+    <row r="11" spans="1:77" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="148"/>
+      <c r="C11" s="149"/>
+      <c r="D11" s="149"/>
+      <c r="E11" s="149"/>
+      <c r="F11" s="149"/>
+      <c r="G11" s="149"/>
+      <c r="H11" s="149"/>
+      <c r="I11" s="149"/>
+      <c r="J11" s="149"/>
+      <c r="K11" s="149"/>
+      <c r="L11" s="149"/>
+      <c r="M11" s="149"/>
+      <c r="N11" s="149"/>
+      <c r="O11" s="78"/>
+      <c r="P11" s="78"/>
+      <c r="Q11" s="78"/>
+      <c r="R11" s="78"/>
+      <c r="S11" s="78"/>
+      <c r="T11" s="78"/>
+      <c r="U11" s="78"/>
+      <c r="V11" s="78"/>
+      <c r="W11" s="78"/>
+      <c r="X11" s="78"/>
+      <c r="Y11" s="78"/>
+      <c r="Z11" s="78"/>
+      <c r="AA11" s="78"/>
+      <c r="AB11" s="78"/>
+      <c r="AC11" s="78"/>
+      <c r="AD11" s="78"/>
+      <c r="AE11" s="78"/>
+      <c r="AF11" s="78"/>
+      <c r="AG11" s="78"/>
+      <c r="AH11" s="78"/>
+      <c r="AI11" s="78"/>
+      <c r="AJ11" s="78"/>
+      <c r="AK11" s="78"/>
+      <c r="AL11" s="78"/>
+      <c r="AM11" s="78"/>
+      <c r="AN11" s="78"/>
+      <c r="AO11" s="78"/>
+      <c r="AP11" s="78"/>
+      <c r="AQ11" s="78"/>
+      <c r="AR11" s="78"/>
+      <c r="AS11" s="78"/>
+      <c r="AT11" s="78"/>
+      <c r="AU11" s="78"/>
+      <c r="AV11" s="78"/>
+      <c r="AW11" s="78"/>
+      <c r="AX11" s="78"/>
+      <c r="AY11" s="78"/>
+      <c r="AZ11" s="78"/>
+      <c r="BA11" s="78"/>
+      <c r="BB11" s="78"/>
+      <c r="BC11" s="78"/>
+      <c r="BD11" s="78"/>
+      <c r="BE11" s="78"/>
+      <c r="BF11" s="78"/>
+      <c r="BG11" s="78"/>
+      <c r="BH11" s="78"/>
+      <c r="BI11" s="78"/>
+      <c r="BJ11" s="78"/>
+      <c r="BK11" s="78"/>
+      <c r="BL11" s="78"/>
+      <c r="BM11" s="78"/>
+      <c r="BN11" s="78"/>
+      <c r="BO11" s="78"/>
+      <c r="BP11" s="78"/>
+      <c r="BQ11" s="78"/>
+      <c r="BR11" s="78"/>
+      <c r="BS11" s="78"/>
+      <c r="BT11" s="78"/>
+      <c r="BU11" s="78"/>
+      <c r="BV11" s="78"/>
+      <c r="BW11" s="78"/>
+      <c r="BX11" s="78"/>
+      <c r="BY11" s="78"/>
+    </row>
+    <row r="12" spans="1:77" s="78" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="114" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="81" t="s">
+      <c r="C12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="G12" s="78"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="81" t="s">
+      <c r="G12" s="76"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="79" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="78"/>
-      <c r="L12" s="72" t="s">
+      <c r="K12" s="76"/>
+      <c r="L12" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="M12" s="78"/>
-      <c r="N12" s="116" t="s">
+      <c r="M12" s="76"/>
+      <c r="N12" s="114" t="s">
         <v>21</v>
       </c>
-      <c r="O12" s="96"/>
-      <c r="P12" s="96"/>
-      <c r="Q12" s="96"/>
-      <c r="R12" s="96"/>
-      <c r="S12" s="96"/>
-      <c r="T12" s="96"/>
-      <c r="U12" s="96"/>
-      <c r="V12" s="96"/>
-      <c r="W12" s="96"/>
-      <c r="X12" s="96"/>
-      <c r="Y12" s="96"/>
-      <c r="Z12" s="96"/>
-      <c r="AA12" s="96"/>
-      <c r="AB12" s="96"/>
-      <c r="AC12" s="96"/>
-      <c r="AD12" s="96"/>
-      <c r="AE12" s="96"/>
-      <c r="AF12" s="96"/>
-      <c r="AG12" s="96"/>
-      <c r="AH12" s="96"/>
-      <c r="AI12" s="96"/>
-      <c r="AJ12" s="96"/>
-      <c r="AK12" s="96"/>
-      <c r="AL12" s="96"/>
-      <c r="AM12" s="96"/>
-      <c r="AN12" s="96"/>
-      <c r="AO12" s="96"/>
-      <c r="AP12" s="96"/>
-      <c r="AQ12" s="96"/>
-      <c r="AR12" s="96"/>
-      <c r="AS12" s="96"/>
-      <c r="AT12" s="96"/>
-      <c r="AU12" s="96"/>
-      <c r="AV12" s="96"/>
-      <c r="AW12" s="96"/>
-      <c r="AX12" s="96"/>
-      <c r="AY12" s="96"/>
-      <c r="AZ12" s="96"/>
-      <c r="BA12" s="96"/>
-      <c r="BB12" s="96"/>
-      <c r="BC12" s="96"/>
-      <c r="BD12" s="96"/>
-      <c r="BE12" s="96"/>
-      <c r="BF12" s="96"/>
-      <c r="BG12" s="96"/>
-      <c r="BH12" s="96"/>
-      <c r="BI12" s="96"/>
-      <c r="BJ12" s="96"/>
-      <c r="BK12" s="96"/>
-      <c r="BL12" s="96"/>
-      <c r="BM12" s="96"/>
-      <c r="BN12" s="96"/>
-      <c r="BO12" s="96"/>
-      <c r="BP12" s="96"/>
-      <c r="BQ12" s="96"/>
-      <c r="BR12" s="96"/>
-      <c r="BS12" s="96"/>
-      <c r="BT12" s="96"/>
-      <c r="BU12" s="96"/>
-      <c r="BV12" s="96"/>
-      <c r="BW12" s="96"/>
-      <c r="BX12" s="96"/>
-      <c r="BY12" s="96"/>
-    </row>
-    <row r="13" spans="1:77" s="80" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="78"/>
-      <c r="C13" s="78"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="81"/>
-      <c r="G13" s="78"/>
-      <c r="I13" s="79"/>
-      <c r="J13" s="81"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="72"/>
-      <c r="M13" s="78"/>
-      <c r="N13" s="117"/>
-      <c r="O13" s="96"/>
-      <c r="P13" s="96"/>
-      <c r="Q13" s="96"/>
-      <c r="R13" s="96"/>
-      <c r="S13" s="96"/>
-      <c r="T13" s="96"/>
-      <c r="U13" s="96"/>
-      <c r="V13" s="96"/>
-      <c r="W13" s="96"/>
-      <c r="X13" s="96"/>
-      <c r="Y13" s="96"/>
-      <c r="Z13" s="96"/>
-      <c r="AA13" s="96"/>
-      <c r="AB13" s="96"/>
-      <c r="AC13" s="96"/>
-      <c r="AD13" s="96"/>
-      <c r="AE13" s="96"/>
-      <c r="AF13" s="96"/>
-      <c r="AG13" s="96"/>
-      <c r="AH13" s="96"/>
-      <c r="AI13" s="96"/>
-      <c r="AJ13" s="96"/>
-      <c r="AK13" s="96"/>
-      <c r="AL13" s="96"/>
-      <c r="AM13" s="96"/>
-      <c r="AN13" s="96"/>
-      <c r="AO13" s="96"/>
-      <c r="AP13" s="96"/>
-      <c r="AQ13" s="96"/>
-      <c r="AR13" s="96"/>
-      <c r="AS13" s="96"/>
-      <c r="AT13" s="96"/>
-      <c r="AU13" s="96"/>
-      <c r="AV13" s="96"/>
-      <c r="AW13" s="96"/>
-      <c r="AX13" s="96"/>
-      <c r="AY13" s="96"/>
-      <c r="AZ13" s="96"/>
-      <c r="BA13" s="96"/>
-      <c r="BB13" s="96"/>
-      <c r="BC13" s="96"/>
-      <c r="BD13" s="96"/>
-      <c r="BE13" s="96"/>
-      <c r="BF13" s="96"/>
-      <c r="BG13" s="96"/>
-      <c r="BH13" s="96"/>
-      <c r="BI13" s="96"/>
-      <c r="BJ13" s="96"/>
-      <c r="BK13" s="96"/>
-      <c r="BL13" s="96"/>
-      <c r="BM13" s="96"/>
-      <c r="BN13" s="96"/>
-      <c r="BO13" s="96"/>
-      <c r="BP13" s="96"/>
-      <c r="BQ13" s="96"/>
-      <c r="BR13" s="96"/>
-      <c r="BS13" s="96"/>
-      <c r="BT13" s="96"/>
-      <c r="BU13" s="96"/>
-      <c r="BV13" s="96"/>
-      <c r="BW13" s="96"/>
-      <c r="BX13" s="96"/>
-      <c r="BY13" s="96"/>
-    </row>
-    <row r="14" spans="1:77" s="80" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="81" t="s">
+      <c r="O12" s="94"/>
+      <c r="P12" s="94"/>
+      <c r="Q12" s="94"/>
+      <c r="R12" s="94"/>
+      <c r="S12" s="94"/>
+      <c r="T12" s="94"/>
+      <c r="U12" s="94"/>
+      <c r="V12" s="94"/>
+      <c r="W12" s="94"/>
+      <c r="X12" s="94"/>
+      <c r="Y12" s="94"/>
+      <c r="Z12" s="94"/>
+      <c r="AA12" s="94"/>
+      <c r="AB12" s="94"/>
+      <c r="AC12" s="94"/>
+      <c r="AD12" s="94"/>
+      <c r="AE12" s="94"/>
+      <c r="AF12" s="94"/>
+      <c r="AG12" s="94"/>
+      <c r="AH12" s="94"/>
+      <c r="AI12" s="94"/>
+      <c r="AJ12" s="94"/>
+      <c r="AK12" s="94"/>
+      <c r="AL12" s="94"/>
+      <c r="AM12" s="94"/>
+      <c r="AN12" s="94"/>
+      <c r="AO12" s="94"/>
+      <c r="AP12" s="94"/>
+      <c r="AQ12" s="94"/>
+      <c r="AR12" s="94"/>
+      <c r="AS12" s="94"/>
+      <c r="AT12" s="94"/>
+      <c r="AU12" s="94"/>
+      <c r="AV12" s="94"/>
+      <c r="AW12" s="94"/>
+      <c r="AX12" s="94"/>
+      <c r="AY12" s="94"/>
+      <c r="AZ12" s="94"/>
+      <c r="BA12" s="94"/>
+      <c r="BB12" s="94"/>
+      <c r="BC12" s="94"/>
+      <c r="BD12" s="94"/>
+      <c r="BE12" s="94"/>
+      <c r="BF12" s="94"/>
+      <c r="BG12" s="94"/>
+      <c r="BH12" s="94"/>
+      <c r="BI12" s="94"/>
+      <c r="BJ12" s="94"/>
+      <c r="BK12" s="94"/>
+      <c r="BL12" s="94"/>
+      <c r="BM12" s="94"/>
+      <c r="BN12" s="94"/>
+      <c r="BO12" s="94"/>
+      <c r="BP12" s="94"/>
+      <c r="BQ12" s="94"/>
+      <c r="BR12" s="94"/>
+      <c r="BS12" s="94"/>
+      <c r="BT12" s="94"/>
+      <c r="BU12" s="94"/>
+      <c r="BV12" s="94"/>
+      <c r="BW12" s="94"/>
+      <c r="BX12" s="94"/>
+      <c r="BY12" s="94"/>
+    </row>
+    <row r="13" spans="1:77" s="78" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="76"/>
+      <c r="C13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="79"/>
+      <c r="G13" s="76"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="76"/>
+      <c r="L13" s="70"/>
+      <c r="M13" s="76"/>
+      <c r="N13" s="115"/>
+      <c r="O13" s="94"/>
+      <c r="P13" s="94"/>
+      <c r="Q13" s="94"/>
+      <c r="R13" s="94"/>
+      <c r="S13" s="94"/>
+      <c r="T13" s="94"/>
+      <c r="U13" s="94"/>
+      <c r="V13" s="94"/>
+      <c r="W13" s="94"/>
+      <c r="X13" s="94"/>
+      <c r="Y13" s="94"/>
+      <c r="Z13" s="94"/>
+      <c r="AA13" s="94"/>
+      <c r="AB13" s="94"/>
+      <c r="AC13" s="94"/>
+      <c r="AD13" s="94"/>
+      <c r="AE13" s="94"/>
+      <c r="AF13" s="94"/>
+      <c r="AG13" s="94"/>
+      <c r="AH13" s="94"/>
+      <c r="AI13" s="94"/>
+      <c r="AJ13" s="94"/>
+      <c r="AK13" s="94"/>
+      <c r="AL13" s="94"/>
+      <c r="AM13" s="94"/>
+      <c r="AN13" s="94"/>
+      <c r="AO13" s="94"/>
+      <c r="AP13" s="94"/>
+      <c r="AQ13" s="94"/>
+      <c r="AR13" s="94"/>
+      <c r="AS13" s="94"/>
+      <c r="AT13" s="94"/>
+      <c r="AU13" s="94"/>
+      <c r="AV13" s="94"/>
+      <c r="AW13" s="94"/>
+      <c r="AX13" s="94"/>
+      <c r="AY13" s="94"/>
+      <c r="AZ13" s="94"/>
+      <c r="BA13" s="94"/>
+      <c r="BB13" s="94"/>
+      <c r="BC13" s="94"/>
+      <c r="BD13" s="94"/>
+      <c r="BE13" s="94"/>
+      <c r="BF13" s="94"/>
+      <c r="BG13" s="94"/>
+      <c r="BH13" s="94"/>
+      <c r="BI13" s="94"/>
+      <c r="BJ13" s="94"/>
+      <c r="BK13" s="94"/>
+      <c r="BL13" s="94"/>
+      <c r="BM13" s="94"/>
+      <c r="BN13" s="94"/>
+      <c r="BO13" s="94"/>
+      <c r="BP13" s="94"/>
+      <c r="BQ13" s="94"/>
+      <c r="BR13" s="94"/>
+      <c r="BS13" s="94"/>
+      <c r="BT13" s="94"/>
+      <c r="BU13" s="94"/>
+      <c r="BV13" s="94"/>
+      <c r="BW13" s="94"/>
+      <c r="BX13" s="94"/>
+      <c r="BY13" s="94"/>
+    </row>
+    <row r="14" spans="1:77" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="76"/>
+      <c r="C14" s="76"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="78"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="81" t="s">
+      <c r="G14" s="76"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="K14" s="78"/>
-      <c r="L14" s="72" t="s">
+      <c r="K14" s="76"/>
+      <c r="L14" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="M14" s="78"/>
-      <c r="N14" s="117"/>
-      <c r="O14" s="96"/>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="96"/>
-      <c r="R14" s="96"/>
-      <c r="S14" s="96"/>
-      <c r="T14" s="96"/>
-      <c r="U14" s="96"/>
-      <c r="V14" s="96"/>
-      <c r="W14" s="96"/>
-      <c r="X14" s="96"/>
-      <c r="Y14" s="96"/>
-      <c r="Z14" s="96"/>
-      <c r="AA14" s="96"/>
-      <c r="AB14" s="96"/>
-      <c r="AC14" s="96"/>
-      <c r="AD14" s="96"/>
-      <c r="AE14" s="96"/>
-      <c r="AF14" s="96"/>
-      <c r="AG14" s="96"/>
-      <c r="AH14" s="96"/>
-      <c r="AI14" s="96"/>
-      <c r="AJ14" s="96"/>
-      <c r="AK14" s="96"/>
-      <c r="AL14" s="96"/>
-      <c r="AM14" s="96"/>
-      <c r="AN14" s="96"/>
-      <c r="AO14" s="96"/>
-      <c r="AP14" s="96"/>
-      <c r="AQ14" s="96"/>
-      <c r="AR14" s="96"/>
-      <c r="AS14" s="96"/>
-      <c r="AT14" s="96"/>
-      <c r="AU14" s="96"/>
-      <c r="AV14" s="96"/>
-      <c r="AW14" s="96"/>
-      <c r="AX14" s="96"/>
-      <c r="AY14" s="96"/>
-      <c r="AZ14" s="96"/>
-      <c r="BA14" s="96"/>
-      <c r="BB14" s="96"/>
-      <c r="BC14" s="96"/>
-      <c r="BD14" s="96"/>
-      <c r="BE14" s="96"/>
-      <c r="BF14" s="96"/>
-      <c r="BG14" s="96"/>
-      <c r="BH14" s="96"/>
-      <c r="BI14" s="96"/>
-      <c r="BJ14" s="96"/>
-      <c r="BK14" s="96"/>
-      <c r="BL14" s="96"/>
-      <c r="BM14" s="96"/>
-      <c r="BN14" s="96"/>
-      <c r="BO14" s="96"/>
-      <c r="BP14" s="96"/>
-      <c r="BQ14" s="96"/>
-      <c r="BR14" s="96"/>
-      <c r="BS14" s="96"/>
-      <c r="BT14" s="96"/>
-      <c r="BU14" s="96"/>
-      <c r="BV14" s="96"/>
-      <c r="BW14" s="96"/>
-      <c r="BX14" s="96"/>
-      <c r="BY14" s="96"/>
+      <c r="M14" s="76"/>
+      <c r="N14" s="115"/>
+      <c r="O14" s="94"/>
+      <c r="P14" s="94"/>
+      <c r="Q14" s="94"/>
+      <c r="R14" s="94"/>
+      <c r="S14" s="94"/>
+      <c r="T14" s="94"/>
+      <c r="U14" s="94"/>
+      <c r="V14" s="94"/>
+      <c r="W14" s="94"/>
+      <c r="X14" s="94"/>
+      <c r="Y14" s="94"/>
+      <c r="Z14" s="94"/>
+      <c r="AA14" s="94"/>
+      <c r="AB14" s="94"/>
+      <c r="AC14" s="94"/>
+      <c r="AD14" s="94"/>
+      <c r="AE14" s="94"/>
+      <c r="AF14" s="94"/>
+      <c r="AG14" s="94"/>
+      <c r="AH14" s="94"/>
+      <c r="AI14" s="94"/>
+      <c r="AJ14" s="94"/>
+      <c r="AK14" s="94"/>
+      <c r="AL14" s="94"/>
+      <c r="AM14" s="94"/>
+      <c r="AN14" s="94"/>
+      <c r="AO14" s="94"/>
+      <c r="AP14" s="94"/>
+      <c r="AQ14" s="94"/>
+      <c r="AR14" s="94"/>
+      <c r="AS14" s="94"/>
+      <c r="AT14" s="94"/>
+      <c r="AU14" s="94"/>
+      <c r="AV14" s="94"/>
+      <c r="AW14" s="94"/>
+      <c r="AX14" s="94"/>
+      <c r="AY14" s="94"/>
+      <c r="AZ14" s="94"/>
+      <c r="BA14" s="94"/>
+      <c r="BB14" s="94"/>
+      <c r="BC14" s="94"/>
+      <c r="BD14" s="94"/>
+      <c r="BE14" s="94"/>
+      <c r="BF14" s="94"/>
+      <c r="BG14" s="94"/>
+      <c r="BH14" s="94"/>
+      <c r="BI14" s="94"/>
+      <c r="BJ14" s="94"/>
+      <c r="BK14" s="94"/>
+      <c r="BL14" s="94"/>
+      <c r="BM14" s="94"/>
+      <c r="BN14" s="94"/>
+      <c r="BO14" s="94"/>
+      <c r="BP14" s="94"/>
+      <c r="BQ14" s="94"/>
+      <c r="BR14" s="94"/>
+      <c r="BS14" s="94"/>
+      <c r="BT14" s="94"/>
+      <c r="BU14" s="94"/>
+      <c r="BV14" s="94"/>
+      <c r="BW14" s="94"/>
+      <c r="BX14" s="94"/>
+      <c r="BY14" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2554,44 +2545,43 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:V25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21.5" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:U25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.453125" style="37" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" style="83" customWidth="1"/>
-    <col min="3" max="3" width="9.6328125" style="84" customWidth="1"/>
-    <col min="4" max="4" width="6.453125" style="85" customWidth="1"/>
-    <col min="5" max="5" width="6.453125" style="37" customWidth="1"/>
-    <col min="6" max="6" width="13.36328125" style="37" customWidth="1"/>
-    <col min="7" max="7" width="5.08984375" style="37" customWidth="1"/>
-    <col min="8" max="8" width="19.08984375" style="86" customWidth="1"/>
-    <col min="9" max="9" width="52.36328125" style="87" customWidth="1"/>
-    <col min="10" max="10" width="5.453125" style="38" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.08984375" style="38" hidden="1" customWidth="1"/>
-    <col min="12" max="13" width="5.08984375" style="38" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="1.7265625" style="38" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="0.453125" style="38" customWidth="1"/>
-    <col min="16" max="16" width="2.6328125" style="38" customWidth="1"/>
-    <col min="17" max="17" width="1" style="38" customWidth="1"/>
-    <col min="18" max="18" width="6.453125" style="38" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="38"/>
+    <col min="1" max="1" width="5.5" style="37" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="10.25" style="81" customWidth="1"/>
+    <col min="3" max="3" width="9.625" style="82" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="83" customWidth="1"/>
+    <col min="5" max="5" width="6.5" style="37" customWidth="1"/>
+    <col min="6" max="6" width="13.375" style="37" customWidth="1"/>
+    <col min="7" max="7" width="5.125" style="37" customWidth="1"/>
+    <col min="8" max="8" width="19.125" style="84" customWidth="1"/>
+    <col min="9" max="9" width="61.25" style="85" customWidth="1"/>
+    <col min="10" max="10" width="5.5" style="38" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.125" style="38" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="5.125" style="38" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="1.75" style="38" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="2.625" style="38" customWidth="1"/>
+    <col min="16" max="16" width="1" style="38" customWidth="1"/>
+    <col min="17" max="17" width="6.5" style="38" hidden="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="37" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="146" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="153"/>
-      <c r="G1" s="153"/>
-      <c r="H1" s="153"/>
-      <c r="I1" s="153"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="39"/>
-    </row>
-    <row r="2" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:21" s="37" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="142" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="39"/>
+    </row>
+    <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
         <v>0</v>
       </c>
@@ -2610,7 +2600,7 @@
       <c r="F2" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="125" t="s">
+      <c r="G2" s="123" t="s">
         <v>31</v>
       </c>
       <c r="H2" s="43" t="s">
@@ -2631,328 +2621,314 @@
       <c r="N2" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="O2" s="48" t="s">
+    </row>
+    <row r="3" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="48"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="51"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="53"/>
+    </row>
+    <row r="4" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="48"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="50">
+        <f t="shared" ref="F4:F13" si="0">D4*E4</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50">
+        <f t="shared" ref="H4:H13" si="1">F4</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="51"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="53"/>
+    </row>
+    <row r="5" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="48"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="51"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="53"/>
+    </row>
+    <row r="6" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="48"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="50"/>
+      <c r="H6" s="50">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I6" s="51"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="53"/>
+    </row>
+    <row r="7" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="48"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="51"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="53"/>
+      <c r="M7" s="54"/>
+      <c r="N7" s="53"/>
+    </row>
+    <row r="8" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="48"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="51"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="54"/>
+      <c r="N8" s="53"/>
+    </row>
+    <row r="9" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="48"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="50">
+        <f t="shared" ref="F9:F12" si="2">D9*E9</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="50"/>
+      <c r="H9" s="50">
+        <f t="shared" ref="H9:H12" si="3">F9</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="51"/>
+      <c r="K9" s="52"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="54"/>
+      <c r="N9" s="53"/>
+    </row>
+    <row r="10" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="48"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="50"/>
+      <c r="H10" s="50">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="51"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="53"/>
+    </row>
+    <row r="11" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="51"/>
+      <c r="K11" s="52"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="54"/>
+      <c r="N11" s="53"/>
+    </row>
+    <row r="12" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="48"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="51"/>
+      <c r="K12" s="52"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="54"/>
+      <c r="N12" s="53"/>
+    </row>
+    <row r="13" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="48"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="51"/>
+      <c r="K13" s="52"/>
+      <c r="L13" s="53"/>
+      <c r="M13" s="54"/>
+      <c r="N13" s="53"/>
+    </row>
+    <row r="14" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="55"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="51"/>
+    </row>
+    <row r="15" spans="1:21" s="60" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="62"/>
+      <c r="D15" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="64"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="64" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="49"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="52"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="56"/>
-    </row>
-    <row r="4" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="49"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="51">
-        <f t="shared" ref="F4:F13" si="0">D4*E4</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51">
-        <f t="shared" ref="H4:H13" si="1">F4</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="52"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="56"/>
-    </row>
-    <row r="5" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="49"/>
-      <c r="B5" s="42"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="51">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I5" s="52"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="55"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="56"/>
-    </row>
-    <row r="6" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="49"/>
-      <c r="B6" s="42"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="51">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I6" s="52"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="54"/>
-      <c r="M6" s="55"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="56"/>
-    </row>
-    <row r="7" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="49"/>
-      <c r="B7" s="42"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="51">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="52"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="54"/>
-      <c r="M7" s="55"/>
-      <c r="N7" s="54"/>
-      <c r="O7" s="56"/>
-    </row>
-    <row r="8" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="49"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="52"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="54"/>
-      <c r="M8" s="55"/>
-      <c r="N8" s="54"/>
-      <c r="O8" s="56"/>
-    </row>
-    <row r="9" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="49"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="51">
-        <f t="shared" ref="F9:F12" si="2">D9*E9</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51">
-        <f t="shared" ref="H9:H12" si="3">F9</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="52"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="54"/>
-      <c r="M9" s="55"/>
-      <c r="N9" s="54"/>
-      <c r="O9" s="56"/>
-    </row>
-    <row r="10" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="49"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="51">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="52"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="54"/>
-      <c r="M10" s="55"/>
-      <c r="N10" s="54"/>
-      <c r="O10" s="56"/>
-    </row>
-    <row r="11" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="49"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="51">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="52"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="55"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="56"/>
-    </row>
-    <row r="12" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="49"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="51">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="52"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="54"/>
-      <c r="M12" s="55"/>
-      <c r="N12" s="54"/>
-      <c r="O12" s="56"/>
-    </row>
-    <row r="13" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="49"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="51">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="52"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="54"/>
-      <c r="M13" s="55"/>
-      <c r="N13" s="54"/>
-      <c r="O13" s="56"/>
-    </row>
-    <row r="14" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="57"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="52"/>
-    </row>
-    <row r="15" spans="1:22" s="62" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="64"/>
-      <c r="D15" s="65" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="66"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="66" t="s">
+      <c r="H15" s="63"/>
+      <c r="I15" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="65"/>
-      <c r="I15" s="68" t="s">
+    </row>
+    <row r="16" spans="1:21" s="60" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="61"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="64"/>
+      <c r="H16" s="63"/>
+      <c r="I16" s="66"/>
+    </row>
+    <row r="17" spans="2:9" s="60" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="61"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="64"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="67"/>
+    </row>
+    <row r="18" spans="2:9" s="60" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="68"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="64"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="64" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="63"/>
+      <c r="I18" s="66" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:22" s="62" customFormat="1" ht="9.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="63"/>
-      <c r="C16" s="64"/>
-      <c r="D16" s="65"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="67"/>
-      <c r="G16" s="66"/>
-      <c r="H16" s="65"/>
-      <c r="I16" s="68"/>
-    </row>
-    <row r="17" spans="2:9" s="62" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="63"/>
-      <c r="C17" s="64"/>
-      <c r="D17" s="65"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="66"/>
-      <c r="H17" s="65"/>
-      <c r="I17" s="69"/>
-    </row>
-    <row r="18" spans="2:9" s="62" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="70"/>
-      <c r="C18" s="64"/>
-      <c r="D18" s="65" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="66"/>
-      <c r="F18" s="67"/>
-      <c r="G18" s="66" t="s">
-        <v>29</v>
-      </c>
-      <c r="H18" s="65"/>
-      <c r="I18" s="68" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="71"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="75"/>
-      <c r="I19" s="76"/>
-    </row>
-    <row r="20" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="77"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="80"/>
-      <c r="G20" s="80"/>
-      <c r="H20" s="81"/>
-      <c r="I20" s="82"/>
-    </row>
-    <row r="21" spans="2:9" ht="11.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="23" spans="2:9" ht="28" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="24" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="25" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="19" spans="2:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="69"/>
+      <c r="C19" s="70"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="74"/>
+    </row>
+    <row r="20" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="75"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="78"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="79"/>
+      <c r="I20" s="80"/>
+    </row>
+    <row r="21" spans="2:9" ht="11.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:I1"/>
@@ -2965,53 +2941,53 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="30" customWidth="1"/>
-    <col min="2" max="2" width="18.36328125" style="30" customWidth="1"/>
-    <col min="3" max="3" width="17.6328125" style="22" customWidth="1"/>
+    <col min="2" max="2" width="18.375" style="30" customWidth="1"/>
+    <col min="3" max="3" width="17.625" style="22" customWidth="1"/>
     <col min="4" max="4" width="20" style="32" customWidth="1"/>
-    <col min="5" max="5" width="5.36328125" style="30" customWidth="1"/>
-    <col min="6" max="6" width="9.26953125" style="17" customWidth="1"/>
-    <col min="7" max="7" width="8.7265625" style="17" customWidth="1"/>
-    <col min="8" max="8" width="13.7265625" style="18" customWidth="1"/>
-    <col min="9" max="9" width="18.26953125" style="30" customWidth="1"/>
-    <col min="10" max="10" width="17.6328125" style="22" customWidth="1"/>
+    <col min="5" max="5" width="5.375" style="30" customWidth="1"/>
+    <col min="6" max="6" width="9.25" style="17" customWidth="1"/>
+    <col min="7" max="7" width="8.75" style="17" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="18" customWidth="1"/>
+    <col min="9" max="9" width="18.25" style="30" customWidth="1"/>
+    <col min="10" max="10" width="17.625" style="22" customWidth="1"/>
     <col min="11" max="16384" width="9" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="154" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
-      <c r="J1" s="155"/>
-    </row>
-    <row r="2" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="150" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="151"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="151"/>
+    </row>
+    <row r="2" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="F2" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>9</v>
@@ -3020,13 +2996,13 @@
         <v>10</v>
       </c>
       <c r="I2" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="25" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -3038,7 +3014,7 @@
       <c r="I3" s="14"/>
       <c r="J3" s="14"/>
     </row>
-    <row r="4" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14"/>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -3050,7 +3026,7 @@
       <c r="I4" s="14"/>
       <c r="J4" s="14"/>
     </row>
-    <row r="5" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14"/>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
@@ -3062,7 +3038,7 @@
       <c r="I5" s="14"/>
       <c r="J5" s="14"/>
     </row>
-    <row r="6" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14"/>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -3074,7 +3050,7 @@
       <c r="I6" s="14"/>
       <c r="J6" s="14"/>
     </row>
-    <row r="7" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
@@ -3086,7 +3062,7 @@
       <c r="I7" s="14"/>
       <c r="J7" s="14"/>
     </row>
-    <row r="8" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
@@ -3098,7 +3074,7 @@
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
     </row>
-    <row r="9" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -3110,7 +3086,7 @@
       <c r="I9" s="14"/>
       <c r="J9" s="14"/>
     </row>
-    <row r="10" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14"/>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -3122,7 +3098,7 @@
       <c r="I10" s="14"/>
       <c r="J10" s="14"/>
     </row>
-    <row r="11" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -3134,7 +3110,7 @@
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
     </row>
-    <row r="12" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14"/>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -3146,7 +3122,7 @@
       <c r="I12" s="14"/>
       <c r="J12" s="14"/>
     </row>
-    <row r="13" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -3158,7 +3134,7 @@
       <c r="I13" s="14"/>
       <c r="J13" s="14"/>
     </row>
-    <row r="14" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -3170,26 +3146,26 @@
       <c r="I14" s="29"/>
       <c r="J14" s="29"/>
     </row>
-    <row r="15" spans="1:10" ht="19.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="30"/>
       <c r="D15" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G15" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="I15" s="30" t="s">
-        <v>48</v>
-      </c>
       <c r="J15" s="19"/>
     </row>
-    <row r="16" spans="1:10" ht="11" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19"/>
       <c r="B16" s="19"/>
       <c r="C16" s="30"/>
@@ -3198,13 +3174,13 @@
       <c r="I16" s="31"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="31"/>
       <c r="C17" s="30"/>
       <c r="D17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="1:10" ht="75.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="19" t="s">
         <v>22</v>
       </c>
@@ -3213,12 +3189,12 @@
         <v>29</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I18" s="17"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="1:10" ht="19.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="22"/>
       <c r="B19" s="22"/>
       <c r="E19" s="22"/>
@@ -3227,7 +3203,7 @@
       <c r="H19" s="34"/>
       <c r="I19" s="22"/>
     </row>
-    <row r="20" spans="1:10" ht="19.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="22"/>
       <c r="B20" s="22"/>
       <c r="E20" s="22"/>
@@ -3236,25 +3212,25 @@
       <c r="H20" s="35"/>
       <c r="I20" s="22"/>
     </row>
-    <row r="21" spans="1:10" s="30" customFormat="1" ht="19.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" s="30" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="22"/>
       <c r="D21" s="32"/>
       <c r="H21" s="36"/>
       <c r="J21" s="22"/>
     </row>
-    <row r="22" spans="1:10" s="30" customFormat="1" ht="19.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" s="30" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="22"/>
       <c r="D22" s="32"/>
       <c r="H22" s="36"/>
       <c r="J22" s="22"/>
     </row>
-    <row r="23" spans="1:10" s="30" customFormat="1" ht="19.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" s="30" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="22"/>
       <c r="D23" s="32"/>
       <c r="H23" s="36"/>
       <c r="J23" s="22"/>
     </row>
-    <row r="24" spans="1:10" s="30" customFormat="1" ht="19.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" s="30" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="22"/>
       <c r="D24" s="32"/>
       <c r="H24" s="36"/>
@@ -3272,53 +3248,53 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" style="8" customWidth="1"/>
-    <col min="2" max="2" width="18.36328125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="18.375" style="8" customWidth="1"/>
     <col min="3" max="3" width="14" style="8" customWidth="1"/>
-    <col min="4" max="4" width="6.08984375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="6.125" style="8" customWidth="1"/>
     <col min="5" max="5" width="8" style="8" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" style="8" customWidth="1"/>
-    <col min="7" max="7" width="7.36328125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="9.6328125" style="21" customWidth="1"/>
-    <col min="9" max="9" width="12.453125" style="8" customWidth="1"/>
-    <col min="10" max="10" width="17.453125" style="8" customWidth="1"/>
+    <col min="6" max="6" width="11.875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="7.375" style="8" customWidth="1"/>
+    <col min="8" max="8" width="9.625" style="21" customWidth="1"/>
+    <col min="9" max="9" width="12.5" style="8" customWidth="1"/>
+    <col min="10" max="10" width="17.5" style="8" customWidth="1"/>
     <col min="11" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="144" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-    </row>
-    <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="152" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="153"/>
+      <c r="C1" s="153"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="153"/>
+      <c r="F1" s="153"/>
+      <c r="G1" s="153"/>
+      <c r="H1" s="153"/>
+      <c r="I1" s="153"/>
+      <c r="J1" s="153"/>
+    </row>
+    <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="D2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>9</v>
@@ -3327,13 +3303,13 @@
         <v>10</v>
       </c>
       <c r="I2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -3345,7 +3321,7 @@
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
     </row>
-    <row r="4" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -3357,7 +3333,7 @@
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9"/>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -3369,7 +3345,7 @@
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
     </row>
-    <row r="6" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -3381,7 +3357,7 @@
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -3393,7 +3369,7 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -3405,7 +3381,7 @@
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
     </row>
-    <row r="9" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -3417,7 +3393,7 @@
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -3429,7 +3405,7 @@
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
     </row>
-    <row r="11" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -3441,28 +3417,28 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
     </row>
-    <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" s="17"/>
       <c r="E12" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F12" s="17"/>
       <c r="G12" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H12" s="18"/>
       <c r="I12" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J12" s="20"/>
     </row>
-    <row r="13" spans="1:10" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>
       <c r="B13" s="17"/>
       <c r="D13" s="17"/>
@@ -3473,10 +3449,10 @@
       <c r="I13" s="17"/>
       <c r="J13" s="20"/>
     </row>
-    <row r="14" spans="1:10" ht="46" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17"/>
       <c r="B14" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" s="17"/>
       <c r="E14" s="17" t="s">
@@ -3484,7 +3460,7 @@
       </c>
       <c r="F14" s="17"/>
       <c r="G14" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H14" s="18"/>
       <c r="I14" s="17"/>

--- a/templates/accounting-template.xlsx
+++ b/templates/accounting-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\school-substitution-sys\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A351242B-66A3-4E93-8016-74149CBED496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1916690-A9CB-44DF-B12B-0EDDC72242FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -520,7 +520,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -923,14 +923,8 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="8" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1218,14 +1212,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5" style="110" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="65" customWidth="1"/>
     <col min="3" max="3" width="15.125" style="94" customWidth="1"/>
     <col min="4" max="4" width="9.375" style="94" customWidth="1"/>
-    <col min="5" max="5" width="25.875" style="140" customWidth="1"/>
+    <col min="5" max="5" width="25.875" style="138" customWidth="1"/>
     <col min="6" max="6" width="5.875" style="116" customWidth="1"/>
     <col min="7" max="7" width="6.5" style="116" customWidth="1"/>
     <col min="8" max="8" width="6.875" style="86" customWidth="1"/>
@@ -1240,22 +1234,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="110" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="142" t="s">
+      <c r="B1" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="142"/>
-      <c r="H1" s="142"/>
-      <c r="I1" s="142"/>
-      <c r="J1" s="142"/>
-      <c r="K1" s="142"/>
-      <c r="L1" s="142"/>
-      <c r="M1" s="142"/>
-      <c r="N1" s="142"/>
-      <c r="O1" s="142"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="140"/>
+      <c r="M1" s="140"/>
+      <c r="N1" s="140"/>
+      <c r="O1" s="140"/>
       <c r="P1" s="119"/>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1338,7 +1332,7 @@
       <c r="L4" s="127"/>
       <c r="M4" s="128"/>
       <c r="N4" s="102">
-        <f t="shared" ref="N4:N26" si="0">K4</f>
+        <f t="shared" ref="N4:N13" si="0">K4</f>
         <v>0</v>
       </c>
       <c r="O4" s="129"/>
@@ -1471,10 +1465,7 @@
       <c r="K11" s="101"/>
       <c r="L11" s="127"/>
       <c r="M11" s="128"/>
-      <c r="N11" s="102">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="N11" s="102"/>
       <c r="O11" s="129"/>
     </row>
     <row r="12" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -1490,9 +1481,12 @@
       <c r="J12" s="101"/>
       <c r="K12" s="101"/>
       <c r="L12" s="127"/>
-      <c r="M12" s="128"/>
-      <c r="N12" s="102"/>
-      <c r="O12" s="129"/>
+      <c r="M12" s="127"/>
+      <c r="N12" s="102">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O12" s="131"/>
     </row>
     <row r="13" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="88"/>
@@ -1507,8 +1501,11 @@
       <c r="J13" s="101"/>
       <c r="K13" s="101"/>
       <c r="L13" s="127"/>
-      <c r="M13" s="128"/>
-      <c r="N13" s="102"/>
+      <c r="M13" s="134"/>
+      <c r="N13" s="102">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="O13" s="129"/>
     </row>
     <row r="14" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -1524,397 +1521,146 @@
       <c r="J14" s="101"/>
       <c r="K14" s="101"/>
       <c r="L14" s="127"/>
-      <c r="M14" s="127"/>
-      <c r="N14" s="102">
-        <f t="shared" si="0"/>
+      <c r="M14" s="134"/>
+      <c r="N14" s="102"/>
+      <c r="O14" s="129"/>
+    </row>
+    <row r="15" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="135"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="89">
+        <f>SUM(D3:D14)</f>
         <v>0</v>
       </c>
-      <c r="O14" s="131"/>
-    </row>
-    <row r="15" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="88"/>
-      <c r="B15" s="124"/>
-      <c r="C15" s="96"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="126"/>
-      <c r="F15" s="100"/>
+      <c r="E15" s="136"/>
+      <c r="F15" s="98" t="s">
+        <v>15</v>
+      </c>
       <c r="G15" s="98"/>
       <c r="H15" s="99"/>
-      <c r="I15" s="100"/>
+      <c r="I15" s="98"/>
       <c r="J15" s="101"/>
-      <c r="K15" s="101"/>
-      <c r="L15" s="127"/>
-      <c r="M15" s="127"/>
-      <c r="N15" s="102"/>
-      <c r="O15" s="131"/>
-    </row>
-    <row r="16" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="88"/>
-      <c r="B16" s="124"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="125"/>
-      <c r="E16" s="126"/>
-      <c r="F16" s="100"/>
-      <c r="G16" s="98"/>
-      <c r="H16" s="99"/>
-      <c r="I16" s="100"/>
-      <c r="J16" s="101"/>
-      <c r="K16" s="99"/>
-      <c r="L16" s="97"/>
-      <c r="M16" s="97"/>
-      <c r="N16" s="133">
-        <f t="shared" si="0"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="97"/>
+      <c r="M15" s="97"/>
+      <c r="N15" s="133">
+        <f>SUM(N3:N14)</f>
         <v>0</v>
       </c>
-      <c r="O16" s="134"/>
-    </row>
-    <row r="17" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="88"/>
-      <c r="B17" s="124"/>
-      <c r="C17" s="96"/>
-      <c r="D17" s="125"/>
-      <c r="E17" s="126"/>
-      <c r="F17" s="100"/>
-      <c r="G17" s="98"/>
-      <c r="H17" s="99"/>
-      <c r="I17" s="100"/>
-      <c r="J17" s="101"/>
-      <c r="K17" s="101"/>
-      <c r="L17" s="127"/>
-      <c r="M17" s="128"/>
-      <c r="N17" s="102">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O17" s="129"/>
-    </row>
-    <row r="18" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="88"/>
-      <c r="B18" s="124"/>
-      <c r="C18" s="96"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="126"/>
-      <c r="F18" s="100"/>
-      <c r="G18" s="98"/>
-      <c r="H18" s="99"/>
-      <c r="I18" s="100"/>
-      <c r="J18" s="101"/>
-      <c r="K18" s="101"/>
-      <c r="L18" s="127"/>
-      <c r="M18" s="128"/>
-      <c r="N18" s="102">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="129"/>
-    </row>
-    <row r="19" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="88"/>
-      <c r="B19" s="124"/>
-      <c r="C19" s="96"/>
-      <c r="D19" s="125"/>
-      <c r="E19" s="126"/>
-      <c r="F19" s="100"/>
-      <c r="G19" s="98"/>
-      <c r="H19" s="99"/>
-      <c r="I19" s="100"/>
-      <c r="J19" s="101"/>
-      <c r="K19" s="101"/>
-      <c r="L19" s="127"/>
-      <c r="M19" s="127"/>
-      <c r="N19" s="102">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="131"/>
-    </row>
-    <row r="20" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="88"/>
-      <c r="B20" s="124"/>
-      <c r="C20" s="96"/>
-      <c r="D20" s="125"/>
-      <c r="E20" s="126"/>
-      <c r="F20" s="100"/>
-      <c r="G20" s="98"/>
-      <c r="H20" s="99"/>
-      <c r="I20" s="100"/>
-      <c r="J20" s="101"/>
-      <c r="K20" s="101"/>
-      <c r="L20" s="127"/>
-      <c r="M20" s="128"/>
-      <c r="N20" s="102">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="129"/>
-    </row>
-    <row r="21" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="88"/>
-      <c r="B21" s="124"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="125"/>
-      <c r="E21" s="126"/>
-      <c r="F21" s="100"/>
-      <c r="G21" s="98"/>
-      <c r="H21" s="99"/>
-      <c r="I21" s="100"/>
-      <c r="J21" s="101"/>
-      <c r="K21" s="101"/>
-      <c r="L21" s="127"/>
-      <c r="M21" s="135"/>
-      <c r="N21" s="102">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="131"/>
-    </row>
-    <row r="22" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="88"/>
-      <c r="B22" s="124"/>
-      <c r="C22" s="96"/>
-      <c r="D22" s="125"/>
-      <c r="E22" s="126"/>
-      <c r="F22" s="100"/>
-      <c r="G22" s="98"/>
-      <c r="H22" s="99"/>
-      <c r="I22" s="100"/>
-      <c r="J22" s="101"/>
-      <c r="K22" s="101"/>
-      <c r="L22" s="127"/>
-      <c r="M22" s="135"/>
-      <c r="N22" s="102"/>
-      <c r="O22" s="129"/>
-    </row>
-    <row r="23" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="88"/>
-      <c r="B23" s="124"/>
-      <c r="C23" s="96"/>
-      <c r="D23" s="125"/>
-      <c r="E23" s="126"/>
-      <c r="F23" s="100"/>
-      <c r="G23" s="98"/>
-      <c r="H23" s="99"/>
-      <c r="I23" s="100"/>
-      <c r="J23" s="101"/>
-      <c r="K23" s="101"/>
-      <c r="L23" s="127"/>
-      <c r="M23" s="127"/>
-      <c r="N23" s="102">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O23" s="136"/>
-    </row>
-    <row r="24" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="88"/>
-      <c r="B24" s="124"/>
-      <c r="C24" s="96"/>
-      <c r="D24" s="125"/>
-      <c r="E24" s="126"/>
-      <c r="F24" s="100"/>
-      <c r="G24" s="98"/>
-      <c r="H24" s="99"/>
-      <c r="I24" s="100"/>
-      <c r="J24" s="101"/>
-      <c r="K24" s="101"/>
-      <c r="L24" s="127"/>
-      <c r="M24" s="127"/>
-      <c r="N24" s="102">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O24" s="129"/>
-    </row>
-    <row r="25" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="88"/>
-      <c r="B25" s="124"/>
-      <c r="C25" s="96"/>
-      <c r="D25" s="125"/>
-      <c r="E25" s="126"/>
-      <c r="F25" s="100"/>
-      <c r="G25" s="98"/>
-      <c r="H25" s="99"/>
-      <c r="I25" s="100"/>
-      <c r="J25" s="101"/>
-      <c r="K25" s="101"/>
-      <c r="L25" s="127"/>
-      <c r="M25" s="127"/>
-      <c r="N25" s="102"/>
-      <c r="O25" s="129"/>
-    </row>
-    <row r="26" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="88"/>
-      <c r="B26" s="124"/>
-      <c r="C26" s="96"/>
-      <c r="D26" s="125"/>
-      <c r="E26" s="126"/>
-      <c r="F26" s="100"/>
-      <c r="G26" s="98"/>
-      <c r="H26" s="99"/>
-      <c r="I26" s="100"/>
-      <c r="J26" s="101"/>
-      <c r="K26" s="101"/>
-      <c r="L26" s="127"/>
-      <c r="M26" s="135"/>
-      <c r="N26" s="102">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O26" s="129"/>
-    </row>
-    <row r="27" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="88"/>
-      <c r="B27" s="124"/>
-      <c r="C27" s="96"/>
-      <c r="D27" s="125"/>
-      <c r="E27" s="126"/>
-      <c r="F27" s="100"/>
-      <c r="G27" s="98"/>
-      <c r="H27" s="99"/>
-      <c r="I27" s="100"/>
-      <c r="J27" s="101"/>
-      <c r="K27" s="101"/>
-      <c r="L27" s="127"/>
-      <c r="M27" s="135"/>
-      <c r="N27" s="102"/>
-      <c r="O27" s="129"/>
-    </row>
-    <row r="28" spans="1:15" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="137"/>
-      <c r="C28" s="98"/>
-      <c r="D28" s="89">
-        <f>SUM(D3:D27)</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="138"/>
-      <c r="F28" s="98" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" s="98"/>
-      <c r="H28" s="99"/>
-      <c r="I28" s="98"/>
-      <c r="J28" s="101"/>
-      <c r="K28" s="133"/>
-      <c r="L28" s="97"/>
-      <c r="M28" s="97"/>
-      <c r="N28" s="133">
-        <f>SUM(N3:N27)</f>
-        <v>0</v>
-      </c>
-      <c r="O28" s="113"/>
-    </row>
-    <row r="29" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="144" t="s">
+      <c r="O15" s="113"/>
+    </row>
+    <row r="16" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="142" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="145"/>
-      <c r="D29" s="145"/>
-      <c r="E29" s="145"/>
-      <c r="F29" s="145"/>
-      <c r="G29" s="145"/>
-      <c r="H29" s="145"/>
-      <c r="I29" s="145"/>
-      <c r="J29" s="145"/>
-      <c r="K29" s="145"/>
-      <c r="L29" s="145"/>
-      <c r="M29" s="145"/>
-      <c r="N29" s="145"/>
-      <c r="O29" s="146"/>
-    </row>
-    <row r="30" spans="1:15" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="139" t="s">
+      <c r="C16" s="143"/>
+      <c r="D16" s="143"/>
+      <c r="E16" s="143"/>
+      <c r="F16" s="143"/>
+      <c r="G16" s="143"/>
+      <c r="H16" s="143"/>
+      <c r="I16" s="143"/>
+      <c r="J16" s="143"/>
+      <c r="K16" s="143"/>
+      <c r="L16" s="143"/>
+      <c r="M16" s="143"/>
+      <c r="N16" s="143"/>
+      <c r="O16" s="144"/>
+    </row>
+    <row r="17" spans="2:16" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="137" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="72"/>
-      <c r="D30" s="73" t="s">
+      <c r="C17" s="72"/>
+      <c r="D17" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="E30" s="78"/>
-      <c r="F30" s="76"/>
-      <c r="G30" s="73" t="s">
+      <c r="E17" s="78"/>
+      <c r="F17" s="76"/>
+      <c r="G17" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="H30" s="70"/>
-      <c r="J30" s="76"/>
-      <c r="K30" s="114" t="s">
+      <c r="H17" s="70"/>
+      <c r="J17" s="76"/>
+      <c r="K17" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="L30" s="76"/>
-      <c r="M30" s="70"/>
-      <c r="N30" s="70" t="s">
+      <c r="L17" s="76"/>
+      <c r="M17" s="70"/>
+      <c r="N17" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="O30" s="115" t="s">
+      <c r="O17" s="115" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="87.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="62"/>
-      <c r="C31" s="72"/>
-      <c r="D31" s="73" t="s">
+    <row r="18" spans="2:16" ht="87.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="62"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="78"/>
-      <c r="F31" s="76"/>
-      <c r="G31" s="73" t="s">
+      <c r="E18" s="78"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="H31" s="70"/>
-      <c r="J31" s="76"/>
-      <c r="K31" s="114" t="s">
+      <c r="H18" s="70"/>
+      <c r="J18" s="76"/>
+      <c r="K18" s="114" t="s">
         <v>24</v>
       </c>
-      <c r="L31" s="76"/>
-      <c r="M31" s="70"/>
-      <c r="N31" s="70" t="s">
+      <c r="L18" s="76"/>
+      <c r="M18" s="70"/>
+      <c r="N18" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="O31" s="80"/>
-    </row>
-    <row r="32" spans="1:15" ht="0.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K32" s="141" t="s">
+      <c r="O18" s="80"/>
+    </row>
+    <row r="19" spans="2:16" ht="0.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K19" s="139" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="2:16" ht="23.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="2:16" s="110" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="65"/>
-      <c r="C34" s="94"/>
-      <c r="D34" s="94"/>
-      <c r="E34" s="140"/>
-      <c r="F34" s="116"/>
-      <c r="G34" s="116"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="76"/>
-      <c r="J34" s="86"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="94"/>
-      <c r="M34" s="94"/>
-      <c r="N34" s="94"/>
-      <c r="O34" s="119"/>
-      <c r="P34" s="94"/>
-    </row>
-    <row r="35" spans="2:16" s="110" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="65"/>
-      <c r="C35" s="94"/>
-      <c r="D35" s="94"/>
-      <c r="E35" s="140"/>
-      <c r="F35" s="116"/>
-      <c r="G35" s="116"/>
-      <c r="H35" s="86"/>
-      <c r="I35" s="76"/>
-      <c r="J35" s="86"/>
-      <c r="K35" s="86"/>
-      <c r="L35" s="94"/>
-      <c r="M35" s="94"/>
-      <c r="N35" s="94"/>
-      <c r="O35" s="119"/>
-      <c r="P35" s="94"/>
+    <row r="20" spans="2:16" ht="23.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="2:16" s="110" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="65"/>
+      <c r="C21" s="94"/>
+      <c r="D21" s="94"/>
+      <c r="E21" s="138"/>
+      <c r="F21" s="116"/>
+      <c r="G21" s="116"/>
+      <c r="H21" s="86"/>
+      <c r="I21" s="76"/>
+      <c r="J21" s="86"/>
+      <c r="K21" s="86"/>
+      <c r="L21" s="94"/>
+      <c r="M21" s="94"/>
+      <c r="N21" s="94"/>
+      <c r="O21" s="119"/>
+      <c r="P21" s="94"/>
+    </row>
+    <row r="22" spans="2:16" s="110" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="65"/>
+      <c r="C22" s="94"/>
+      <c r="D22" s="94"/>
+      <c r="E22" s="138"/>
+      <c r="F22" s="116"/>
+      <c r="G22" s="116"/>
+      <c r="H22" s="86"/>
+      <c r="I22" s="76"/>
+      <c r="J22" s="86"/>
+      <c r="K22" s="86"/>
+      <c r="L22" s="94"/>
+      <c r="M22" s="94"/>
+      <c r="N22" s="94"/>
+      <c r="O22" s="119"/>
+      <c r="P22" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:O1"/>
-    <mergeCell ref="B29:O29"/>
+    <mergeCell ref="B16:O16"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1947,21 +1693,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:77" s="86" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="147" t="s">
+      <c r="B1" s="145" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="145"/>
+      <c r="K1" s="145"/>
+      <c r="L1" s="145"/>
+      <c r="M1" s="145"/>
+      <c r="N1" s="145"/>
     </row>
     <row r="2" spans="1:77" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="87" t="s">
@@ -2212,19 +1958,19 @@
       <c r="BY10" s="78"/>
     </row>
     <row r="11" spans="1:77" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="148"/>
-      <c r="C11" s="149"/>
-      <c r="D11" s="149"/>
-      <c r="E11" s="149"/>
-      <c r="F11" s="149"/>
-      <c r="G11" s="149"/>
-      <c r="H11" s="149"/>
-      <c r="I11" s="149"/>
-      <c r="J11" s="149"/>
-      <c r="K11" s="149"/>
-      <c r="L11" s="149"/>
-      <c r="M11" s="149"/>
-      <c r="N11" s="149"/>
+      <c r="B11" s="146"/>
+      <c r="C11" s="147"/>
+      <c r="D11" s="147"/>
+      <c r="E11" s="147"/>
+      <c r="F11" s="147"/>
+      <c r="G11" s="147"/>
+      <c r="H11" s="147"/>
+      <c r="I11" s="147"/>
+      <c r="J11" s="147"/>
+      <c r="K11" s="147"/>
+      <c r="L11" s="147"/>
+      <c r="M11" s="147"/>
+      <c r="N11" s="147"/>
       <c r="O11" s="78"/>
       <c r="P11" s="78"/>
       <c r="Q11" s="78"/>
@@ -2545,7 +2291,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5" style="37" hidden="1" customWidth="1"/>
@@ -2561,27 +2307,24 @@
     <col min="11" max="11" width="15.125" style="38" hidden="1" customWidth="1"/>
     <col min="12" max="13" width="5.125" style="38" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="1.75" style="38" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="2.625" style="38" customWidth="1"/>
-    <col min="16" max="16" width="1" style="38" customWidth="1"/>
-    <col min="17" max="17" width="6.5" style="38" hidden="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="38"/>
+    <col min="15" max="16384" width="9" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="37" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="142" t="s">
+    <row r="1" spans="1:17" s="37" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="140" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="39"/>
-    </row>
-    <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="39"/>
+    </row>
+    <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
         <v>0</v>
       </c>
@@ -2622,7 +2365,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="48"/>
       <c r="B3" s="42"/>
       <c r="C3" s="49"/>
@@ -2637,7 +2380,7 @@
       <c r="M3" s="54"/>
       <c r="N3" s="53"/>
     </row>
-    <row r="4" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="48"/>
       <c r="B4" s="42"/>
       <c r="C4" s="49"/>
@@ -2658,7 +2401,7 @@
       <c r="M4" s="54"/>
       <c r="N4" s="53"/>
     </row>
-    <row r="5" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="48"/>
       <c r="B5" s="42"/>
       <c r="C5" s="49"/>
@@ -2679,7 +2422,7 @@
       <c r="M5" s="54"/>
       <c r="N5" s="53"/>
     </row>
-    <row r="6" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="48"/>
       <c r="B6" s="42"/>
       <c r="C6" s="49"/>
@@ -2700,7 +2443,7 @@
       <c r="M6" s="54"/>
       <c r="N6" s="53"/>
     </row>
-    <row r="7" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="48"/>
       <c r="B7" s="42"/>
       <c r="C7" s="49"/>
@@ -2721,7 +2464,7 @@
       <c r="M7" s="54"/>
       <c r="N7" s="53"/>
     </row>
-    <row r="8" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="48"/>
       <c r="B8" s="42"/>
       <c r="C8" s="49"/>
@@ -2736,7 +2479,7 @@
       <c r="M8" s="54"/>
       <c r="N8" s="53"/>
     </row>
-    <row r="9" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="48"/>
       <c r="B9" s="42"/>
       <c r="C9" s="49"/>
@@ -2757,7 +2500,7 @@
       <c r="M9" s="54"/>
       <c r="N9" s="53"/>
     </row>
-    <row r="10" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="48"/>
       <c r="B10" s="42"/>
       <c r="C10" s="49"/>
@@ -2778,7 +2521,7 @@
       <c r="M10" s="54"/>
       <c r="N10" s="53"/>
     </row>
-    <row r="11" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="48"/>
       <c r="B11" s="42"/>
       <c r="C11" s="49"/>
@@ -2799,7 +2542,7 @@
       <c r="M11" s="54"/>
       <c r="N11" s="53"/>
     </row>
-    <row r="12" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="48"/>
       <c r="B12" s="42"/>
       <c r="C12" s="49"/>
@@ -2820,7 +2563,7 @@
       <c r="M12" s="54"/>
       <c r="N12" s="53"/>
     </row>
-    <row r="13" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="48"/>
       <c r="B13" s="42"/>
       <c r="C13" s="49"/>
@@ -2841,7 +2584,7 @@
       <c r="M13" s="54"/>
       <c r="N13" s="53"/>
     </row>
-    <row r="14" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="55"/>
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
@@ -2851,7 +2594,7 @@
       <c r="H14" s="59"/>
       <c r="I14" s="51"/>
     </row>
-    <row r="15" spans="1:21" s="60" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" s="60" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="61" t="s">
         <v>16</v>
       </c>
@@ -2869,7 +2612,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:21" s="60" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" s="60" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="61"/>
       <c r="C16" s="62"/>
       <c r="D16" s="63"/>
@@ -2957,18 +2700,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="148" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="151"/>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
-      <c r="F1" s="151"/>
-      <c r="G1" s="151"/>
-      <c r="H1" s="151"/>
-      <c r="I1" s="151"/>
-      <c r="J1" s="151"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
     </row>
     <row r="2" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -3264,18 +3007,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="150" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="153"/>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="153"/>
-      <c r="G1" s="153"/>
-      <c r="H1" s="153"/>
-      <c r="I1" s="153"/>
-      <c r="J1" s="153"/>
+      <c r="B1" s="151"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="151"/>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">

--- a/templates/accounting-template.xlsx
+++ b/templates/accounting-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\school-substitution-sys\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1916690-A9CB-44DF-B12B-0EDDC72242FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67050C1-FD27-48C9-A081-E413E81FB69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="超鐘點" sheetId="5" r:id="rId1"/>
@@ -1680,12 +1680,12 @@
     <col min="3" max="3" width="14.125" style="94" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="94" customWidth="1"/>
     <col min="5" max="5" width="0" style="94" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="5" style="116" customWidth="1"/>
-    <col min="7" max="7" width="5.5" style="116" customWidth="1"/>
+    <col min="6" max="6" width="6.75" style="116" customWidth="1"/>
+    <col min="7" max="7" width="6.875" style="116" customWidth="1"/>
     <col min="8" max="8" width="8.875" style="110" customWidth="1"/>
     <col min="9" max="9" width="6.5" style="76" customWidth="1"/>
     <col min="10" max="10" width="6.5" style="86" customWidth="1"/>
-    <col min="11" max="11" width="10.375" style="86" customWidth="1"/>
+    <col min="11" max="11" width="14.5" style="86" customWidth="1"/>
     <col min="12" max="12" width="9" style="117" customWidth="1"/>
     <col min="13" max="13" width="11.875" style="86" customWidth="1"/>
     <col min="14" max="14" width="23.5" style="118" customWidth="1"/>

--- a/templates/accounting-template.xlsx
+++ b/templates/accounting-template.xlsx
@@ -15,9 +15,10 @@
   <sheets>
     <sheet name="超鐘點" sheetId="5" r:id="rId1"/>
     <sheet name="兼課" sheetId="4" r:id="rId2"/>
-    <sheet name="公假代課" sheetId="3" r:id="rId3"/>
+    <sheet name="公付代課" sheetId="3" r:id="rId3"/>
     <sheet name=" 自付代課" sheetId="2" r:id="rId4"/>
     <sheet name="代導鐘點" sheetId="1" r:id="rId5"/>
+    <sheet name="115.6.1-6.30公付代課-身心調適假" sheetId="6" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="62">
   <si>
     <t>編號</t>
   </si>
@@ -222,7 +223,7 @@
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">臺北市立建成國中[[年]]年[[月]]月([[日期]])公假代課鐘點費印領清冊 </t>
+    <t xml:space="preserve">臺北市立建成國中[[年]]年[[月]]月([[日期]])公付代課鐘點費印領清冊 </t>
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
@@ -232,6 +233,9 @@
   <si>
     <t>臺北市立建成國民中學[[年]]年[[月]]月([[日期]])公付代導師鐘點費</t>
     <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>臺北市立建成國中[[年]]年[[月]]月([[日期]])公付代課-身心調適假鐘點費印領清冊 </t>
   </si>
 </sst>
 </file>
@@ -3216,4 +3220,396 @@
   <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:Q25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.5" style="37" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="10.25" style="81" customWidth="1"/>
+    <col min="3" max="3" width="9.625" style="82" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="83" customWidth="1"/>
+    <col min="5" max="5" width="6.5" style="37" customWidth="1"/>
+    <col min="6" max="6" width="13.375" style="37" customWidth="1"/>
+    <col min="7" max="7" width="5.125" style="37" customWidth="1"/>
+    <col min="8" max="8" width="19.125" style="84" customWidth="1"/>
+    <col min="9" max="9" width="61.25" style="85" customWidth="1"/>
+    <col min="10" max="10" width="5.5" style="38" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.125" style="38" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="5.125" style="38" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="1.75" style="38" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="38"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" s="37" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="140" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="39"/>
+    </row>
+    <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="123" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="N2" s="46" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="48"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="51"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="53"/>
+    </row>
+    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="48"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="50">
+        <f t="shared" ref="F4:F13" si="0">D4*E4</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50">
+        <f t="shared" ref="H4:H13" si="1">F4</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="51"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="53"/>
+    </row>
+    <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="48"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="51"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="53"/>
+    </row>
+    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="48"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="50"/>
+      <c r="H6" s="50">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I6" s="51"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="53"/>
+    </row>
+    <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="48"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="51"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="53"/>
+      <c r="M7" s="54"/>
+      <c r="N7" s="53"/>
+    </row>
+    <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="48"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="51"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="54"/>
+      <c r="N8" s="53"/>
+    </row>
+    <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="48"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="50">
+        <f t="shared" ref="F9:F12" si="2">D9*E9</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="50"/>
+      <c r="H9" s="50">
+        <f t="shared" ref="H9:H12" si="3">F9</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="51"/>
+      <c r="K9" s="52"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="54"/>
+      <c r="N9" s="53"/>
+    </row>
+    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="48"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="50"/>
+      <c r="H10" s="50">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="51"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="53"/>
+    </row>
+    <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="51"/>
+      <c r="K11" s="52"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="54"/>
+      <c r="N11" s="53"/>
+    </row>
+    <row r="12" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="48"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="51"/>
+      <c r="K12" s="52"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="54"/>
+      <c r="N12" s="53"/>
+    </row>
+    <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="48"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="51"/>
+      <c r="K13" s="52"/>
+      <c r="L13" s="53"/>
+      <c r="M13" s="54"/>
+      <c r="N13" s="53"/>
+    </row>
+    <row r="14" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="55"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="51"/>
+    </row>
+    <row r="15" spans="1:17" s="60" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="62"/>
+      <c r="D15" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="64"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="63"/>
+      <c r="I15" s="66" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" s="60" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="61"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="64"/>
+      <c r="H16" s="63"/>
+      <c r="I16" s="66"/>
+    </row>
+    <row r="17" spans="2:9" s="60" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="61"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="64"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="67"/>
+    </row>
+    <row r="18" spans="2:9" s="60" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="68"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="64"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="64" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="63"/>
+      <c r="I18" s="66" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="69"/>
+      <c r="C19" s="70"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="74"/>
+    </row>
+    <row r="20" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="75"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="78"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="79"/>
+      <c r="I20" s="80"/>
+    </row>
+    <row r="21" spans="2:9" ht="11.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:I1"/>
+  </mergeCells>
+  <phoneticPr fontId="25" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/templates/accounting-template.xlsx
+++ b/templates/accounting-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\school-substitution-sys\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67050C1-FD27-48C9-A081-E413E81FB69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8DC7B6D-9294-4E82-B343-FB192CDB826F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="超鐘點" sheetId="5" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="公付代課" sheetId="3" r:id="rId3"/>
     <sheet name=" 自付代課" sheetId="2" r:id="rId4"/>
     <sheet name="代導鐘點" sheetId="1" r:id="rId5"/>
-    <sheet name="115.6.1-6.30公付代課-身心調適假" sheetId="6" r:id="rId10"/>
+    <sheet name="115.6.1-6.30公付代課-身心調適假" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
   <si>
     <t>編號</t>
   </si>
@@ -235,7 +235,7 @@
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
-    <t>臺北市立建成國中[[年]]年[[月]]月([[日期]])公付代課-身心調適假鐘點費印領清冊 </t>
+    <t>臺北市立建成國中[[年]]年[[月]]月([[日期]])公付代課-身心調適假鐘點費印領清冊</t>
   </si>
 </sst>
 </file>
@@ -945,29 +945,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1215,48 +1215,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{602F95BD-7AA8-444D-825B-220957798382}">
   <dimension ref="A1:P22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="5.5" style="110" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="5.453125" style="110" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="65" customWidth="1"/>
-    <col min="3" max="3" width="15.125" style="94" customWidth="1"/>
-    <col min="4" max="4" width="9.375" style="94" customWidth="1"/>
-    <col min="5" max="5" width="25.875" style="138" customWidth="1"/>
-    <col min="6" max="6" width="5.875" style="116" customWidth="1"/>
-    <col min="7" max="7" width="6.5" style="116" customWidth="1"/>
-    <col min="8" max="8" width="6.875" style="86" customWidth="1"/>
+    <col min="3" max="3" width="15.08984375" style="94" customWidth="1"/>
+    <col min="4" max="4" width="9.36328125" style="94" customWidth="1"/>
+    <col min="5" max="5" width="25.90625" style="138" customWidth="1"/>
+    <col min="6" max="6" width="5.90625" style="116" customWidth="1"/>
+    <col min="7" max="7" width="6.453125" style="116" customWidth="1"/>
+    <col min="8" max="8" width="6.90625" style="86" customWidth="1"/>
     <col min="9" max="9" width="9" style="76" customWidth="1"/>
-    <col min="10" max="10" width="8.125" style="86" customWidth="1"/>
-    <col min="11" max="11" width="17.125" style="86" customWidth="1"/>
-    <col min="12" max="13" width="0.25" style="94" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="12.75" style="94" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="48.375" style="119" customWidth="1"/>
-    <col min="16" max="16" width="11.5" style="94" customWidth="1"/>
+    <col min="10" max="10" width="8.08984375" style="86" customWidth="1"/>
+    <col min="11" max="11" width="17.08984375" style="86" customWidth="1"/>
+    <col min="12" max="13" width="0.26953125" style="94" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7265625" style="94" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="48.36328125" style="119" customWidth="1"/>
+    <col min="16" max="16" width="11.453125" style="94" customWidth="1"/>
     <col min="17" max="16384" width="9" style="94"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="110" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="140" t="s">
+    <row r="1" spans="1:16" s="110" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="143" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
+      <c r="K1" s="143"/>
+      <c r="L1" s="143"/>
+      <c r="M1" s="143"/>
+      <c r="N1" s="143"/>
+      <c r="O1" s="143"/>
       <c r="P1" s="119"/>
     </row>
-    <row r="2" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="88" t="s">
         <v>0</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="88"/>
       <c r="B3" s="124"/>
       <c r="C3" s="96"/>
@@ -1321,7 +1321,7 @@
       <c r="O3" s="129"/>
       <c r="P3" s="130"/>
     </row>
-    <row r="4" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="88"/>
       <c r="B4" s="124"/>
       <c r="C4" s="96"/>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="O4" s="129"/>
     </row>
-    <row r="5" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="88"/>
       <c r="B5" s="124"/>
       <c r="C5" s="96"/>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="O5" s="129"/>
     </row>
-    <row r="6" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="88"/>
       <c r="B6" s="124"/>
       <c r="C6" s="96"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="O6" s="129"/>
     </row>
-    <row r="7" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="88"/>
       <c r="B7" s="124"/>
       <c r="C7" s="96"/>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="O7" s="131"/>
     </row>
-    <row r="8" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="88"/>
       <c r="B8" s="124"/>
       <c r="C8" s="96"/>
@@ -1418,7 +1418,7 @@
       <c r="N8" s="102"/>
       <c r="O8" s="132"/>
     </row>
-    <row r="9" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="88"/>
       <c r="B9" s="124"/>
       <c r="C9" s="96"/>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="O9" s="132"/>
     </row>
-    <row r="10" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="88"/>
       <c r="B10" s="124"/>
       <c r="C10" s="96"/>
@@ -1455,7 +1455,7 @@
       <c r="N10" s="102"/>
       <c r="O10" s="132"/>
     </row>
-    <row r="11" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="88"/>
       <c r="B11" s="124"/>
       <c r="C11" s="96"/>
@@ -1472,7 +1472,7 @@
       <c r="N11" s="102"/>
       <c r="O11" s="129"/>
     </row>
-    <row r="12" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="88"/>
       <c r="B12" s="124"/>
       <c r="C12" s="96"/>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="O12" s="131"/>
     </row>
-    <row r="13" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="88"/>
       <c r="B13" s="124"/>
       <c r="C13" s="96"/>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="O13" s="129"/>
     </row>
-    <row r="14" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="88"/>
       <c r="B14" s="124"/>
       <c r="C14" s="96"/>
@@ -1529,7 +1529,7 @@
       <c r="N14" s="102"/>
       <c r="O14" s="129"/>
     </row>
-    <row r="15" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="135"/>
       <c r="C15" s="98"/>
       <c r="D15" s="89">
@@ -1553,25 +1553,25 @@
       </c>
       <c r="O15" s="113"/>
     </row>
-    <row r="16" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="142" t="s">
+    <row r="16" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="144" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="143"/>
-      <c r="D16" s="143"/>
-      <c r="E16" s="143"/>
-      <c r="F16" s="143"/>
-      <c r="G16" s="143"/>
-      <c r="H16" s="143"/>
-      <c r="I16" s="143"/>
-      <c r="J16" s="143"/>
-      <c r="K16" s="143"/>
-      <c r="L16" s="143"/>
-      <c r="M16" s="143"/>
-      <c r="N16" s="143"/>
-      <c r="O16" s="144"/>
-    </row>
-    <row r="17" spans="2:16" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="145"/>
+      <c r="D16" s="145"/>
+      <c r="E16" s="145"/>
+      <c r="F16" s="145"/>
+      <c r="G16" s="145"/>
+      <c r="H16" s="145"/>
+      <c r="I16" s="145"/>
+      <c r="J16" s="145"/>
+      <c r="K16" s="145"/>
+      <c r="L16" s="145"/>
+      <c r="M16" s="145"/>
+      <c r="N16" s="145"/>
+      <c r="O16" s="146"/>
+    </row>
+    <row r="17" spans="2:16" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="137" t="s">
         <v>16</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="2:16" ht="87.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:16" ht="88" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="62"/>
       <c r="C18" s="72"/>
       <c r="D18" s="73" t="s">
@@ -1621,13 +1621,13 @@
       </c>
       <c r="O18" s="80"/>
     </row>
-    <row r="19" spans="2:16" ht="0.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:16" ht="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="K19" s="139" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:16" ht="23.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="2:16" s="110" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:16" ht="23.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="21" spans="2:16" s="110" customFormat="1" ht="33.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="65"/>
       <c r="C21" s="94"/>
       <c r="D21" s="94"/>
@@ -1644,7 +1644,7 @@
       <c r="O21" s="119"/>
       <c r="P21" s="94"/>
     </row>
-    <row r="22" spans="2:16" s="110" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:16" s="110" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="65"/>
       <c r="C22" s="94"/>
       <c r="D22" s="94"/>
@@ -1672,48 +1672,48 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83379523-73FA-4C35-B6DC-2A623A85954C}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:BY14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="0" style="110" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="10.125" style="110" customWidth="1"/>
-    <col min="3" max="3" width="14.125" style="94" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="94" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" style="110" customWidth="1"/>
+    <col min="3" max="3" width="14.08984375" style="94" customWidth="1"/>
+    <col min="4" max="4" width="10.453125" style="94" customWidth="1"/>
     <col min="5" max="5" width="0" style="94" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="6.75" style="116" customWidth="1"/>
-    <col min="7" max="7" width="6.875" style="116" customWidth="1"/>
-    <col min="8" max="8" width="8.875" style="110" customWidth="1"/>
-    <col min="9" max="9" width="6.5" style="76" customWidth="1"/>
-    <col min="10" max="10" width="6.5" style="86" customWidth="1"/>
-    <col min="11" max="11" width="14.5" style="86" customWidth="1"/>
+    <col min="6" max="6" width="6.7265625" style="116" customWidth="1"/>
+    <col min="7" max="7" width="6.90625" style="116" customWidth="1"/>
+    <col min="8" max="8" width="8.90625" style="110" customWidth="1"/>
+    <col min="9" max="9" width="6.453125" style="76" customWidth="1"/>
+    <col min="10" max="10" width="6.453125" style="86" customWidth="1"/>
+    <col min="11" max="11" width="14.453125" style="86" customWidth="1"/>
     <col min="12" max="12" width="9" style="117" customWidth="1"/>
-    <col min="13" max="13" width="11.875" style="86" customWidth="1"/>
-    <col min="14" max="14" width="23.5" style="118" customWidth="1"/>
+    <col min="13" max="13" width="11.90625" style="86" customWidth="1"/>
+    <col min="14" max="14" width="40.453125" style="118" customWidth="1"/>
     <col min="15" max="16384" width="9" style="94"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77" s="86" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="145" t="s">
+    <row r="1" spans="1:77" s="86" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
-      <c r="L1" s="145"/>
-      <c r="M1" s="145"/>
-      <c r="N1" s="145"/>
-    </row>
-    <row r="2" spans="1:77" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="140"/>
+      <c r="M1" s="140"/>
+      <c r="N1" s="140"/>
+    </row>
+    <row r="2" spans="1:77" ht="28.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="87" t="s">
         <v>0</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:77" s="107" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:77" s="107" customFormat="1" ht="30.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="95"/>
       <c r="B3" s="88"/>
       <c r="C3" s="89"/>
@@ -1775,7 +1775,7 @@
       <c r="O3" s="106"/>
       <c r="P3" s="106"/>
     </row>
-    <row r="4" spans="1:77" s="107" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:77" s="107" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="108"/>
       <c r="B4" s="88"/>
       <c r="C4" s="89"/>
@@ -1793,7 +1793,7 @@
       <c r="O4" s="106"/>
       <c r="P4" s="106"/>
     </row>
-    <row r="5" spans="1:77" s="107" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:77" s="107" customFormat="1" ht="26.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="108"/>
       <c r="B5" s="88"/>
       <c r="C5" s="89"/>
@@ -1811,7 +1811,7 @@
       <c r="O5" s="106"/>
       <c r="P5" s="106"/>
     </row>
-    <row r="6" spans="1:77" s="107" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:77" s="107" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="108"/>
       <c r="B6" s="88"/>
       <c r="C6" s="89"/>
@@ -1829,7 +1829,7 @@
       <c r="O6" s="106"/>
       <c r="P6" s="106"/>
     </row>
-    <row r="7" spans="1:77" s="107" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:77" s="107" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="108"/>
       <c r="B7" s="88"/>
       <c r="C7" s="89"/>
@@ -1847,7 +1847,7 @@
       <c r="O7" s="106"/>
       <c r="P7" s="106"/>
     </row>
-    <row r="8" spans="1:77" s="107" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:77" s="107" customFormat="1" ht="32.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="108"/>
       <c r="B8" s="88"/>
       <c r="C8" s="89"/>
@@ -1865,7 +1865,7 @@
       <c r="O8" s="106"/>
       <c r="P8" s="106"/>
     </row>
-    <row r="9" spans="1:77" s="107" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:77" s="107" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="108"/>
       <c r="B9" s="88"/>
       <c r="C9" s="89"/>
@@ -1883,7 +1883,7 @@
       <c r="O9" s="106"/>
       <c r="P9" s="106"/>
     </row>
-    <row r="10" spans="1:77" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:77" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="99"/>
       <c r="C10" s="98"/>
       <c r="D10" s="98"/>
@@ -1961,20 +1961,20 @@
       <c r="BX10" s="78"/>
       <c r="BY10" s="78"/>
     </row>
-    <row r="11" spans="1:77" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="146"/>
-      <c r="C11" s="147"/>
-      <c r="D11" s="147"/>
-      <c r="E11" s="147"/>
-      <c r="F11" s="147"/>
-      <c r="G11" s="147"/>
-      <c r="H11" s="147"/>
-      <c r="I11" s="147"/>
-      <c r="J11" s="147"/>
-      <c r="K11" s="147"/>
-      <c r="L11" s="147"/>
-      <c r="M11" s="147"/>
-      <c r="N11" s="147"/>
+    <row r="11" spans="1:77" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="141"/>
+      <c r="C11" s="142"/>
+      <c r="D11" s="142"/>
+      <c r="E11" s="142"/>
+      <c r="F11" s="142"/>
+      <c r="G11" s="142"/>
+      <c r="H11" s="142"/>
+      <c r="I11" s="142"/>
+      <c r="J11" s="142"/>
+      <c r="K11" s="142"/>
+      <c r="L11" s="142"/>
+      <c r="M11" s="142"/>
+      <c r="N11" s="142"/>
       <c r="O11" s="78"/>
       <c r="P11" s="78"/>
       <c r="Q11" s="78"/>
@@ -2039,7 +2039,7 @@
       <c r="BX11" s="78"/>
       <c r="BY11" s="78"/>
     </row>
-    <row r="12" spans="1:77" s="78" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:77" s="78" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="114" t="s">
         <v>16</v>
       </c>
@@ -2125,7 +2125,7 @@
       <c r="BX12" s="94"/>
       <c r="BY12" s="94"/>
     </row>
-    <row r="13" spans="1:77" s="78" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:77" s="78" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="76"/>
       <c r="C13" s="76"/>
       <c r="E13" s="76"/>
@@ -2201,7 +2201,7 @@
       <c r="BX13" s="94"/>
       <c r="BY13" s="94"/>
     </row>
-    <row r="14" spans="1:77" s="78" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:77" s="78" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B14" s="76"/>
       <c r="C14" s="76"/>
       <c r="E14" s="76"/>
@@ -2294,41 +2294,41 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32EE2485-5990-4EBE-AC24-196E706E14D7}">
   <dimension ref="A1:Q25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="5.5" style="37" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="10.25" style="81" customWidth="1"/>
-    <col min="3" max="3" width="9.625" style="82" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="83" customWidth="1"/>
-    <col min="5" max="5" width="6.5" style="37" customWidth="1"/>
-    <col min="6" max="6" width="13.375" style="37" customWidth="1"/>
-    <col min="7" max="7" width="5.125" style="37" customWidth="1"/>
-    <col min="8" max="8" width="19.125" style="84" customWidth="1"/>
-    <col min="9" max="9" width="61.25" style="85" customWidth="1"/>
-    <col min="10" max="10" width="5.5" style="38" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.125" style="38" hidden="1" customWidth="1"/>
-    <col min="12" max="13" width="5.125" style="38" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="1.75" style="38" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="5.453125" style="37" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" style="81" customWidth="1"/>
+    <col min="3" max="3" width="9.6328125" style="82" customWidth="1"/>
+    <col min="4" max="4" width="6.453125" style="83" customWidth="1"/>
+    <col min="5" max="5" width="6.453125" style="37" customWidth="1"/>
+    <col min="6" max="6" width="13.36328125" style="37" customWidth="1"/>
+    <col min="7" max="7" width="5.08984375" style="37" customWidth="1"/>
+    <col min="8" max="8" width="19.08984375" style="84" customWidth="1"/>
+    <col min="9" max="9" width="61.26953125" style="85" customWidth="1"/>
+    <col min="10" max="10" width="5.453125" style="38" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.08984375" style="38" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="5.08984375" style="38" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="1.7265625" style="38" hidden="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="37" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="140" t="s">
+    <row r="1" spans="1:17" s="37" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="143" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
       <c r="P1" s="38"/>
       <c r="Q1" s="39"/>
     </row>
-    <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="40" t="s">
         <v>0</v>
       </c>
@@ -2369,7 +2369,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="48"/>
       <c r="B3" s="42"/>
       <c r="C3" s="49"/>
@@ -2384,7 +2384,7 @@
       <c r="M3" s="54"/>
       <c r="N3" s="53"/>
     </row>
-    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="48"/>
       <c r="B4" s="42"/>
       <c r="C4" s="49"/>
@@ -2405,7 +2405,7 @@
       <c r="M4" s="54"/>
       <c r="N4" s="53"/>
     </row>
-    <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="48"/>
       <c r="B5" s="42"/>
       <c r="C5" s="49"/>
@@ -2426,7 +2426,7 @@
       <c r="M5" s="54"/>
       <c r="N5" s="53"/>
     </row>
-    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="48"/>
       <c r="B6" s="42"/>
       <c r="C6" s="49"/>
@@ -2447,7 +2447,7 @@
       <c r="M6" s="54"/>
       <c r="N6" s="53"/>
     </row>
-    <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="48"/>
       <c r="B7" s="42"/>
       <c r="C7" s="49"/>
@@ -2468,7 +2468,7 @@
       <c r="M7" s="54"/>
       <c r="N7" s="53"/>
     </row>
-    <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="48"/>
       <c r="B8" s="42"/>
       <c r="C8" s="49"/>
@@ -2483,7 +2483,7 @@
       <c r="M8" s="54"/>
       <c r="N8" s="53"/>
     </row>
-    <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="48"/>
       <c r="B9" s="42"/>
       <c r="C9" s="49"/>
@@ -2504,7 +2504,7 @@
       <c r="M9" s="54"/>
       <c r="N9" s="53"/>
     </row>
-    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="48"/>
       <c r="B10" s="42"/>
       <c r="C10" s="49"/>
@@ -2525,7 +2525,7 @@
       <c r="M10" s="54"/>
       <c r="N10" s="53"/>
     </row>
-    <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="48"/>
       <c r="B11" s="42"/>
       <c r="C11" s="49"/>
@@ -2546,7 +2546,7 @@
       <c r="M11" s="54"/>
       <c r="N11" s="53"/>
     </row>
-    <row r="12" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="48"/>
       <c r="B12" s="42"/>
       <c r="C12" s="49"/>
@@ -2567,7 +2567,7 @@
       <c r="M12" s="54"/>
       <c r="N12" s="53"/>
     </row>
-    <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="48"/>
       <c r="B13" s="42"/>
       <c r="C13" s="49"/>
@@ -2588,7 +2588,7 @@
       <c r="M13" s="54"/>
       <c r="N13" s="53"/>
     </row>
-    <row r="14" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="55"/>
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
@@ -2598,7 +2598,7 @@
       <c r="H14" s="59"/>
       <c r="I14" s="51"/>
     </row>
-    <row r="15" spans="1:17" s="60" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" s="60" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="61" t="s">
         <v>16</v>
       </c>
@@ -2616,7 +2616,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="60" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" s="60" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="61"/>
       <c r="C16" s="62"/>
       <c r="D16" s="63"/>
@@ -2626,7 +2626,7 @@
       <c r="H16" s="63"/>
       <c r="I16" s="66"/>
     </row>
-    <row r="17" spans="2:9" s="60" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" s="60" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="61"/>
       <c r="C17" s="62"/>
       <c r="D17" s="63"/>
@@ -2636,7 +2636,7 @@
       <c r="H17" s="63"/>
       <c r="I17" s="67"/>
     </row>
-    <row r="18" spans="2:9" s="60" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" s="60" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="68"/>
       <c r="C18" s="62"/>
       <c r="D18" s="63" t="s">
@@ -2652,7 +2652,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" ht="11.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="69"/>
       <c r="C19" s="70"/>
       <c r="D19" s="71"/>
@@ -2662,7 +2662,7 @@
       <c r="H19" s="73"/>
       <c r="I19" s="74"/>
     </row>
-    <row r="20" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="75"/>
       <c r="C20" s="76"/>
       <c r="D20" s="77"/>
@@ -2672,10 +2672,10 @@
       <c r="H20" s="79"/>
       <c r="I20" s="80"/>
     </row>
-    <row r="21" spans="2:9" ht="11.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="2:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="2:9" ht="11.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="23" spans="2:9" ht="28" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="24" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="25" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:I1"/>
@@ -2686,24 +2686,24 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E98D86-3BBD-4165-99BF-0B3AF952A4EF}">
   <dimension ref="A1:J24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15" style="30" customWidth="1"/>
-    <col min="2" max="2" width="18.375" style="30" customWidth="1"/>
-    <col min="3" max="3" width="17.625" style="22" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" style="30" customWidth="1"/>
+    <col min="3" max="3" width="17.6328125" style="22" customWidth="1"/>
     <col min="4" max="4" width="20" style="32" customWidth="1"/>
-    <col min="5" max="5" width="5.375" style="30" customWidth="1"/>
-    <col min="6" max="6" width="9.25" style="17" customWidth="1"/>
-    <col min="7" max="7" width="8.75" style="17" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="18" customWidth="1"/>
-    <col min="9" max="9" width="18.25" style="30" customWidth="1"/>
-    <col min="10" max="10" width="17.625" style="22" customWidth="1"/>
+    <col min="5" max="5" width="5.36328125" style="30" customWidth="1"/>
+    <col min="6" max="6" width="9.26953125" style="17" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" style="17" customWidth="1"/>
+    <col min="8" max="8" width="13.7265625" style="18" customWidth="1"/>
+    <col min="9" max="9" width="18.26953125" style="30" customWidth="1"/>
+    <col min="10" max="10" width="17.6328125" style="22" customWidth="1"/>
     <col min="11" max="16384" width="9" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="148" t="s">
         <v>59</v>
       </c>
@@ -2717,7 +2717,7 @@
       <c r="I1" s="149"/>
       <c r="J1" s="149"/>
     </row>
-    <row r="2" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>37</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="14"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -2761,7 +2761,7 @@
       <c r="I3" s="14"/>
       <c r="J3" s="14"/>
     </row>
-    <row r="4" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14"/>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -2773,7 +2773,7 @@
       <c r="I4" s="14"/>
       <c r="J4" s="14"/>
     </row>
-    <row r="5" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14"/>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
@@ -2785,7 +2785,7 @@
       <c r="I5" s="14"/>
       <c r="J5" s="14"/>
     </row>
-    <row r="6" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14"/>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -2797,7 +2797,7 @@
       <c r="I6" s="14"/>
       <c r="J6" s="14"/>
     </row>
-    <row r="7" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14"/>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
@@ -2809,7 +2809,7 @@
       <c r="I7" s="14"/>
       <c r="J7" s="14"/>
     </row>
-    <row r="8" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="14"/>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
@@ -2821,7 +2821,7 @@
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
     </row>
-    <row r="9" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -2833,7 +2833,7 @@
       <c r="I9" s="14"/>
       <c r="J9" s="14"/>
     </row>
-    <row r="10" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14"/>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -2845,7 +2845,7 @@
       <c r="I10" s="14"/>
       <c r="J10" s="14"/>
     </row>
-    <row r="11" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -2857,7 +2857,7 @@
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
     </row>
-    <row r="12" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14"/>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -2869,7 +2869,7 @@
       <c r="I12" s="14"/>
       <c r="J12" s="14"/>
     </row>
-    <row r="13" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -2881,7 +2881,7 @@
       <c r="I13" s="14"/>
       <c r="J13" s="14"/>
     </row>
-    <row r="14" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -2893,7 +2893,7 @@
       <c r="I14" s="29"/>
       <c r="J14" s="29"/>
     </row>
-    <row r="15" spans="1:10" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="19.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="19" t="s">
         <v>16</v>
       </c>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="J15" s="19"/>
     </row>
-    <row r="16" spans="1:10" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="11.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="19"/>
       <c r="B16" s="19"/>
       <c r="C16" s="30"/>
@@ -2921,13 +2921,13 @@
       <c r="I16" s="31"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="1:10" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="44.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="31"/>
       <c r="C17" s="30"/>
       <c r="D17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="1:10" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="75.650000000000006" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="19" t="s">
         <v>22</v>
       </c>
@@ -2941,7 +2941,7 @@
       <c r="I18" s="17"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="1:10" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="19.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="22"/>
       <c r="B19" s="22"/>
       <c r="E19" s="22"/>
@@ -2950,7 +2950,7 @@
       <c r="H19" s="34"/>
       <c r="I19" s="22"/>
     </row>
-    <row r="20" spans="1:10" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="19.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="22"/>
       <c r="B20" s="22"/>
       <c r="E20" s="22"/>
@@ -2959,25 +2959,25 @@
       <c r="H20" s="35"/>
       <c r="I20" s="22"/>
     </row>
-    <row r="21" spans="1:10" s="30" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" s="30" customFormat="1" ht="19.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="22"/>
       <c r="D21" s="32"/>
       <c r="H21" s="36"/>
       <c r="J21" s="22"/>
     </row>
-    <row r="22" spans="1:10" s="30" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" s="30" customFormat="1" ht="19.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="22"/>
       <c r="D22" s="32"/>
       <c r="H22" s="36"/>
       <c r="J22" s="22"/>
     </row>
-    <row r="23" spans="1:10" s="30" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" s="30" customFormat="1" ht="19.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="22"/>
       <c r="D23" s="32"/>
       <c r="H23" s="36"/>
       <c r="J23" s="22"/>
     </row>
-    <row r="24" spans="1:10" s="30" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" s="30" customFormat="1" ht="19.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="22"/>
       <c r="D24" s="32"/>
       <c r="H24" s="36"/>
@@ -2993,24 +2993,24 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D6224E1-2B9C-43DA-8D8F-272D7D48239E}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13" style="8" customWidth="1"/>
-    <col min="2" max="2" width="18.375" style="8" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" style="8" customWidth="1"/>
     <col min="3" max="3" width="14" style="8" customWidth="1"/>
-    <col min="4" max="4" width="6.125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="6.08984375" style="8" customWidth="1"/>
     <col min="5" max="5" width="8" style="8" customWidth="1"/>
-    <col min="6" max="6" width="11.875" style="8" customWidth="1"/>
-    <col min="7" max="7" width="7.375" style="8" customWidth="1"/>
-    <col min="8" max="8" width="9.625" style="21" customWidth="1"/>
-    <col min="9" max="9" width="12.5" style="8" customWidth="1"/>
-    <col min="10" max="10" width="17.5" style="8" customWidth="1"/>
+    <col min="6" max="6" width="11.90625" style="8" customWidth="1"/>
+    <col min="7" max="7" width="7.36328125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="9.6328125" style="21" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="17.453125" style="8" customWidth="1"/>
     <col min="11" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="150" t="s">
         <v>60</v>
       </c>
@@ -3024,7 +3024,7 @@
       <c r="I1" s="151"/>
       <c r="J1" s="151"/>
     </row>
-    <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>37</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="9"/>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -3068,7 +3068,7 @@
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
     </row>
-    <row r="4" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="9"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -3080,7 +3080,7 @@
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="9"/>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -3092,7 +3092,7 @@
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
     </row>
-    <row r="6" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="9"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -3104,7 +3104,7 @@
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -3116,7 +3116,7 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="9"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -3128,7 +3128,7 @@
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
     </row>
-    <row r="9" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="9"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -3140,7 +3140,7 @@
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="9"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -3152,7 +3152,7 @@
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
     </row>
-    <row r="11" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="4"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -3164,7 +3164,7 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
     </row>
-    <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="17" t="s">
         <v>16</v>
       </c>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="J12" s="20"/>
     </row>
-    <row r="13" spans="1:10" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="17"/>
       <c r="B13" s="17"/>
       <c r="D13" s="17"/>
@@ -3196,7 +3196,7 @@
       <c r="I13" s="17"/>
       <c r="J13" s="20"/>
     </row>
-    <row r="14" spans="1:10" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="46" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="17"/>
       <c r="B14" s="17" t="s">
         <v>53</v>
@@ -3223,41 +3223,41 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D9062A-9A8A-4BB0-9697-639D0D0AC416}">
   <dimension ref="A1:Q25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="5.5" style="37" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="10.25" style="81" customWidth="1"/>
-    <col min="3" max="3" width="9.625" style="82" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="83" customWidth="1"/>
-    <col min="5" max="5" width="6.5" style="37" customWidth="1"/>
-    <col min="6" max="6" width="13.375" style="37" customWidth="1"/>
-    <col min="7" max="7" width="5.125" style="37" customWidth="1"/>
-    <col min="8" max="8" width="19.125" style="84" customWidth="1"/>
-    <col min="9" max="9" width="61.25" style="85" customWidth="1"/>
-    <col min="10" max="10" width="5.5" style="38" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.125" style="38" hidden="1" customWidth="1"/>
-    <col min="12" max="13" width="5.125" style="38" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="1.75" style="38" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="5.453125" style="37" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" style="81" customWidth="1"/>
+    <col min="3" max="3" width="9.6328125" style="82" customWidth="1"/>
+    <col min="4" max="4" width="6.453125" style="83" customWidth="1"/>
+    <col min="5" max="5" width="6.453125" style="37" customWidth="1"/>
+    <col min="6" max="6" width="13.36328125" style="37" customWidth="1"/>
+    <col min="7" max="7" width="5.08984375" style="37" customWidth="1"/>
+    <col min="8" max="8" width="19.08984375" style="84" customWidth="1"/>
+    <col min="9" max="9" width="61.26953125" style="85" customWidth="1"/>
+    <col min="10" max="10" width="5.453125" style="38" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.08984375" style="38" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="5.08984375" style="38" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="1.7265625" style="38" hidden="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="37" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="140" t="s">
+    <row r="1" spans="1:17" s="37" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="143" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
       <c r="P1" s="38"/>
       <c r="Q1" s="39"/>
     </row>
-    <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="40" t="s">
         <v>0</v>
       </c>
@@ -3298,7 +3298,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="48"/>
       <c r="B3" s="42"/>
       <c r="C3" s="49"/>
@@ -3313,7 +3313,7 @@
       <c r="M3" s="54"/>
       <c r="N3" s="53"/>
     </row>
-    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="48"/>
       <c r="B4" s="42"/>
       <c r="C4" s="49"/>
@@ -3334,7 +3334,7 @@
       <c r="M4" s="54"/>
       <c r="N4" s="53"/>
     </row>
-    <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="48"/>
       <c r="B5" s="42"/>
       <c r="C5" s="49"/>
@@ -3355,7 +3355,7 @@
       <c r="M5" s="54"/>
       <c r="N5" s="53"/>
     </row>
-    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="48"/>
       <c r="B6" s="42"/>
       <c r="C6" s="49"/>
@@ -3376,7 +3376,7 @@
       <c r="M6" s="54"/>
       <c r="N6" s="53"/>
     </row>
-    <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="48"/>
       <c r="B7" s="42"/>
       <c r="C7" s="49"/>
@@ -3397,7 +3397,7 @@
       <c r="M7" s="54"/>
       <c r="N7" s="53"/>
     </row>
-    <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="48"/>
       <c r="B8" s="42"/>
       <c r="C8" s="49"/>
@@ -3412,7 +3412,7 @@
       <c r="M8" s="54"/>
       <c r="N8" s="53"/>
     </row>
-    <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="48"/>
       <c r="B9" s="42"/>
       <c r="C9" s="49"/>
@@ -3433,7 +3433,7 @@
       <c r="M9" s="54"/>
       <c r="N9" s="53"/>
     </row>
-    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="48"/>
       <c r="B10" s="42"/>
       <c r="C10" s="49"/>
@@ -3454,7 +3454,7 @@
       <c r="M10" s="54"/>
       <c r="N10" s="53"/>
     </row>
-    <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="48"/>
       <c r="B11" s="42"/>
       <c r="C11" s="49"/>
@@ -3475,7 +3475,7 @@
       <c r="M11" s="54"/>
       <c r="N11" s="53"/>
     </row>
-    <row r="12" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="48"/>
       <c r="B12" s="42"/>
       <c r="C12" s="49"/>
@@ -3496,7 +3496,7 @@
       <c r="M12" s="54"/>
       <c r="N12" s="53"/>
     </row>
-    <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="48"/>
       <c r="B13" s="42"/>
       <c r="C13" s="49"/>
@@ -3517,7 +3517,7 @@
       <c r="M13" s="54"/>
       <c r="N13" s="53"/>
     </row>
-    <row r="14" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="55"/>
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
@@ -3527,7 +3527,7 @@
       <c r="H14" s="59"/>
       <c r="I14" s="51"/>
     </row>
-    <row r="15" spans="1:17" s="60" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" s="60" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="61" t="s">
         <v>16</v>
       </c>
@@ -3545,7 +3545,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="60" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" s="60" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="61"/>
       <c r="C16" s="62"/>
       <c r="D16" s="63"/>
@@ -3555,7 +3555,7 @@
       <c r="H16" s="63"/>
       <c r="I16" s="66"/>
     </row>
-    <row r="17" spans="2:9" s="60" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" s="60" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="61"/>
       <c r="C17" s="62"/>
       <c r="D17" s="63"/>
@@ -3565,7 +3565,7 @@
       <c r="H17" s="63"/>
       <c r="I17" s="67"/>
     </row>
-    <row r="18" spans="2:9" s="60" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" s="60" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="68"/>
       <c r="C18" s="62"/>
       <c r="D18" s="63" t="s">
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" ht="11.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="69"/>
       <c r="C19" s="70"/>
       <c r="D19" s="71"/>
@@ -3591,7 +3591,7 @@
       <c r="H19" s="73"/>
       <c r="I19" s="74"/>
     </row>
-    <row r="20" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="75"/>
       <c r="C20" s="76"/>
       <c r="D20" s="77"/>
@@ -3601,10 +3601,10 @@
       <c r="H20" s="79"/>
       <c r="I20" s="80"/>
     </row>
-    <row r="21" spans="2:9" ht="11.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="2:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="2:9" ht="11.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="23" spans="2:9" ht="28" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="24" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="25" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:I1"/>

--- a/templates/accounting-template.xlsx
+++ b/templates/accounting-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\school-substitution-sys\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413FA4F8-D5A1-4B7F-BBA4-E3F6FAE00965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D622EB-1052-4B99-90A3-73E8F81BFBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="超鐘點" sheetId="5" r:id="rId1"/>
@@ -939,6 +939,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -974,9 +977,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1214,46 +1214,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{602F95BD-7AA8-444D-825B-220957798382}">
   <dimension ref="A1:P22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.453125" style="108" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5" style="108" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="63" customWidth="1"/>
-    <col min="3" max="3" width="15.08984375" style="92" customWidth="1"/>
-    <col min="4" max="4" width="9.36328125" style="92" customWidth="1"/>
-    <col min="5" max="5" width="25.90625" style="136" customWidth="1"/>
-    <col min="6" max="6" width="5.90625" style="114" customWidth="1"/>
-    <col min="7" max="7" width="6.453125" style="114" customWidth="1"/>
-    <col min="8" max="8" width="6.90625" style="84" customWidth="1"/>
+    <col min="3" max="3" width="15.125" style="92" customWidth="1"/>
+    <col min="4" max="4" width="9.375" style="92" customWidth="1"/>
+    <col min="5" max="5" width="25.875" style="136" customWidth="1"/>
+    <col min="6" max="6" width="5.875" style="114" customWidth="1"/>
+    <col min="7" max="7" width="6.5" style="114" customWidth="1"/>
+    <col min="8" max="8" width="6.875" style="84" customWidth="1"/>
     <col min="9" max="9" width="9" style="74" customWidth="1"/>
-    <col min="10" max="10" width="8.08984375" style="84" customWidth="1"/>
-    <col min="11" max="11" width="17.08984375" style="84" customWidth="1"/>
-    <col min="12" max="13" width="0.26953125" style="92" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7265625" style="92" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="48.36328125" style="117" customWidth="1"/>
-    <col min="16" max="16" width="11.453125" style="92" customWidth="1"/>
+    <col min="10" max="10" width="8.125" style="84" customWidth="1"/>
+    <col min="11" max="11" width="17.125" style="84" customWidth="1"/>
+    <col min="12" max="13" width="0.25" style="92" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="12.75" style="92" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="48.375" style="117" customWidth="1"/>
+    <col min="16" max="16" width="11.5" style="92" customWidth="1"/>
     <col min="17" max="16384" width="9" style="92"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="108" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="141" t="s">
+    <row r="1" spans="1:16" s="108" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="142" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="142"/>
+      <c r="K1" s="142"/>
+      <c r="L1" s="142"/>
+      <c r="M1" s="142"/>
+      <c r="N1" s="142"/>
+      <c r="O1" s="142"/>
       <c r="P1" s="117"/>
     </row>
-    <row r="2" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="86" t="s">
         <v>0</v>
       </c>
@@ -1300,7 +1300,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="86"/>
       <c r="B3" s="122"/>
       <c r="C3" s="94"/>
@@ -1318,7 +1318,7 @@
       <c r="O3" s="127"/>
       <c r="P3" s="128"/>
     </row>
-    <row r="4" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="86"/>
       <c r="B4" s="122"/>
       <c r="C4" s="94"/>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="O4" s="127"/>
     </row>
-    <row r="5" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="86"/>
       <c r="B5" s="122"/>
       <c r="C5" s="94"/>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="O5" s="127"/>
     </row>
-    <row r="6" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="86"/>
       <c r="B6" s="122"/>
       <c r="C6" s="94"/>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="O6" s="127"/>
     </row>
-    <row r="7" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="86"/>
       <c r="B7" s="122"/>
       <c r="C7" s="94"/>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="O7" s="129"/>
     </row>
-    <row r="8" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="86"/>
       <c r="B8" s="122"/>
       <c r="C8" s="94"/>
@@ -1415,7 +1415,7 @@
       <c r="N8" s="100"/>
       <c r="O8" s="130"/>
     </row>
-    <row r="9" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="86"/>
       <c r="B9" s="122"/>
       <c r="C9" s="94"/>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="O9" s="130"/>
     </row>
-    <row r="10" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="86"/>
       <c r="B10" s="122"/>
       <c r="C10" s="94"/>
@@ -1452,7 +1452,7 @@
       <c r="N10" s="100"/>
       <c r="O10" s="130"/>
     </row>
-    <row r="11" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="86"/>
       <c r="B11" s="122"/>
       <c r="C11" s="94"/>
@@ -1469,7 +1469,7 @@
       <c r="N11" s="100"/>
       <c r="O11" s="127"/>
     </row>
-    <row r="12" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="86"/>
       <c r="B12" s="122"/>
       <c r="C12" s="94"/>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="O12" s="129"/>
     </row>
-    <row r="13" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="86"/>
       <c r="B13" s="122"/>
       <c r="C13" s="94"/>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="O13" s="127"/>
     </row>
-    <row r="14" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="86"/>
       <c r="B14" s="122"/>
       <c r="C14" s="94"/>
@@ -1526,7 +1526,7 @@
       <c r="N14" s="100"/>
       <c r="O14" s="127"/>
     </row>
-    <row r="15" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="133"/>
       <c r="C15" s="96"/>
       <c r="D15" s="87">
@@ -1550,25 +1550,25 @@
       </c>
       <c r="O15" s="111"/>
     </row>
-    <row r="16" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="142" t="s">
+    <row r="16" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="143" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="143"/>
-      <c r="D16" s="143"/>
-      <c r="E16" s="143"/>
-      <c r="F16" s="143"/>
-      <c r="G16" s="143"/>
-      <c r="H16" s="143"/>
-      <c r="I16" s="143"/>
-      <c r="J16" s="143"/>
-      <c r="K16" s="143"/>
-      <c r="L16" s="143"/>
-      <c r="M16" s="143"/>
-      <c r="N16" s="143"/>
-      <c r="O16" s="144"/>
-    </row>
-    <row r="17" spans="2:16" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C16" s="144"/>
+      <c r="D16" s="144"/>
+      <c r="E16" s="144"/>
+      <c r="F16" s="144"/>
+      <c r="G16" s="144"/>
+      <c r="H16" s="144"/>
+      <c r="I16" s="144"/>
+      <c r="J16" s="144"/>
+      <c r="K16" s="144"/>
+      <c r="L16" s="144"/>
+      <c r="M16" s="144"/>
+      <c r="N16" s="144"/>
+      <c r="O16" s="145"/>
+    </row>
+    <row r="17" spans="2:16" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="135" t="s">
         <v>16</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="2:16" ht="88" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:16" ht="87.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="60"/>
       <c r="C18" s="70"/>
       <c r="D18" s="71" t="s">
@@ -1618,13 +1618,13 @@
       </c>
       <c r="O18" s="78"/>
     </row>
-    <row r="19" spans="2:16" ht="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:16" ht="0.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K19" s="137" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:16" ht="23.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="21" spans="2:16" s="108" customFormat="1" ht="33.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:16" ht="23.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="2:16" s="108" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="63"/>
       <c r="C21" s="92"/>
       <c r="D21" s="92"/>
@@ -1641,7 +1641,7 @@
       <c r="O21" s="117"/>
       <c r="P21" s="92"/>
     </row>
-    <row r="22" spans="2:16" s="108" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:16" s="108" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="63"/>
       <c r="C22" s="92"/>
       <c r="D22" s="92"/>
@@ -1674,43 +1674,43 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:BY14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0" style="108" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="10.08984375" style="108" customWidth="1"/>
-    <col min="3" max="3" width="14.08984375" style="92" customWidth="1"/>
-    <col min="4" max="4" width="10.453125" style="92" customWidth="1"/>
+    <col min="2" max="2" width="10.125" style="108" customWidth="1"/>
+    <col min="3" max="3" width="14.125" style="92" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="92" customWidth="1"/>
     <col min="5" max="5" width="0" style="92" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7265625" style="114" customWidth="1"/>
-    <col min="7" max="7" width="6.90625" style="114" customWidth="1"/>
-    <col min="8" max="8" width="8.90625" style="108" customWidth="1"/>
-    <col min="9" max="9" width="6.453125" style="74" customWidth="1"/>
-    <col min="10" max="10" width="6.453125" style="84" customWidth="1"/>
-    <col min="11" max="11" width="14.453125" style="84" customWidth="1"/>
+    <col min="6" max="6" width="6.75" style="114" customWidth="1"/>
+    <col min="7" max="7" width="6.875" style="114" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="108" customWidth="1"/>
+    <col min="9" max="9" width="6.5" style="74" customWidth="1"/>
+    <col min="10" max="10" width="6.5" style="84" customWidth="1"/>
+    <col min="11" max="11" width="14.5" style="84" customWidth="1"/>
     <col min="12" max="12" width="9" style="115" customWidth="1"/>
-    <col min="13" max="13" width="11.90625" style="84" customWidth="1"/>
-    <col min="14" max="14" width="40.453125" style="116" customWidth="1"/>
+    <col min="13" max="13" width="11.875" style="84" customWidth="1"/>
+    <col min="14" max="14" width="40.5" style="116" customWidth="1"/>
     <col min="15" max="16384" width="9" style="92"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77" s="84" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="138" t="s">
+    <row r="1" spans="1:77" s="84" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="139" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="138"/>
-      <c r="L1" s="138"/>
-      <c r="M1" s="138"/>
-      <c r="N1" s="138"/>
-    </row>
-    <row r="2" spans="1:77" ht="28.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+    </row>
+    <row r="2" spans="1:77" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="85" t="s">
         <v>0</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:77" s="105" customFormat="1" ht="30.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:77" s="105" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="93"/>
       <c r="B3" s="86"/>
       <c r="C3" s="87"/>
@@ -1767,12 +1767,15 @@
       <c r="J3" s="99"/>
       <c r="K3" s="100"/>
       <c r="L3" s="101"/>
-      <c r="M3" s="102"/>
+      <c r="M3" s="102" t="str">
+        <f>IF(K3-L3=0,"",K3-L3)</f>
+        <v/>
+      </c>
       <c r="N3" s="103"/>
       <c r="O3" s="104"/>
       <c r="P3" s="104"/>
     </row>
-    <row r="4" spans="1:77" s="105" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:77" s="105" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="106"/>
       <c r="B4" s="86"/>
       <c r="C4" s="87"/>
@@ -1785,12 +1788,15 @@
       <c r="J4" s="99"/>
       <c r="K4" s="100"/>
       <c r="L4" s="101"/>
-      <c r="M4" s="102"/>
+      <c r="M4" s="102" t="str">
+        <f t="shared" ref="M4:M10" si="0">IF(K4-L4=0,"",K4-L4)</f>
+        <v/>
+      </c>
       <c r="N4" s="103"/>
       <c r="O4" s="104"/>
       <c r="P4" s="104"/>
     </row>
-    <row r="5" spans="1:77" s="105" customFormat="1" ht="26.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:77" s="105" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="106"/>
       <c r="B5" s="86"/>
       <c r="C5" s="87"/>
@@ -1803,12 +1809,15 @@
       <c r="J5" s="99"/>
       <c r="K5" s="100"/>
       <c r="L5" s="101"/>
-      <c r="M5" s="102"/>
+      <c r="M5" s="102" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="N5" s="103"/>
       <c r="O5" s="104"/>
       <c r="P5" s="104"/>
     </row>
-    <row r="6" spans="1:77" s="105" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:77" s="105" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="106"/>
       <c r="B6" s="86"/>
       <c r="C6" s="87"/>
@@ -1821,12 +1830,15 @@
       <c r="J6" s="99"/>
       <c r="K6" s="100"/>
       <c r="L6" s="101"/>
-      <c r="M6" s="102"/>
+      <c r="M6" s="102" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="N6" s="103"/>
       <c r="O6" s="104"/>
       <c r="P6" s="104"/>
     </row>
-    <row r="7" spans="1:77" s="105" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:77" s="105" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="106"/>
       <c r="B7" s="86"/>
       <c r="C7" s="87"/>
@@ -1839,12 +1851,15 @@
       <c r="J7" s="99"/>
       <c r="K7" s="100"/>
       <c r="L7" s="101"/>
-      <c r="M7" s="102"/>
+      <c r="M7" s="102" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="N7" s="103"/>
       <c r="O7" s="104"/>
       <c r="P7" s="104"/>
     </row>
-    <row r="8" spans="1:77" s="105" customFormat="1" ht="32.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:77" s="105" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="106"/>
       <c r="B8" s="86"/>
       <c r="C8" s="87"/>
@@ -1857,12 +1872,15 @@
       <c r="J8" s="99"/>
       <c r="K8" s="100"/>
       <c r="L8" s="101"/>
-      <c r="M8" s="102"/>
+      <c r="M8" s="102" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="N8" s="107"/>
       <c r="O8" s="104"/>
       <c r="P8" s="104"/>
     </row>
-    <row r="9" spans="1:77" s="105" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:77" s="105" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="106"/>
       <c r="B9" s="86"/>
       <c r="C9" s="87"/>
@@ -1875,12 +1893,15 @@
       <c r="J9" s="99"/>
       <c r="K9" s="100"/>
       <c r="L9" s="101"/>
-      <c r="M9" s="102"/>
+      <c r="M9" s="102" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="N9" s="103"/>
       <c r="O9" s="104"/>
       <c r="P9" s="104"/>
     </row>
-    <row r="10" spans="1:77" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:77" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="97"/>
       <c r="C10" s="96"/>
       <c r="D10" s="96"/>
@@ -1892,7 +1913,10 @@
       <c r="J10" s="96"/>
       <c r="K10" s="109"/>
       <c r="L10" s="110"/>
-      <c r="M10" s="109"/>
+      <c r="M10" s="102" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="N10" s="111"/>
       <c r="O10" s="76"/>
       <c r="P10" s="76"/>
@@ -1958,20 +1982,20 @@
       <c r="BX10" s="76"/>
       <c r="BY10" s="76"/>
     </row>
-    <row r="11" spans="1:77" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="139"/>
-      <c r="C11" s="140"/>
-      <c r="D11" s="140"/>
-      <c r="E11" s="140"/>
-      <c r="F11" s="140"/>
-      <c r="G11" s="140"/>
-      <c r="H11" s="140"/>
-      <c r="I11" s="140"/>
-      <c r="J11" s="140"/>
-      <c r="K11" s="140"/>
-      <c r="L11" s="140"/>
-      <c r="M11" s="140"/>
-      <c r="N11" s="140"/>
+    <row r="11" spans="1:77" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="140"/>
+      <c r="C11" s="141"/>
+      <c r="D11" s="141"/>
+      <c r="E11" s="141"/>
+      <c r="F11" s="141"/>
+      <c r="G11" s="141"/>
+      <c r="H11" s="141"/>
+      <c r="I11" s="141"/>
+      <c r="J11" s="141"/>
+      <c r="K11" s="141"/>
+      <c r="L11" s="141"/>
+      <c r="M11" s="141"/>
+      <c r="N11" s="141"/>
       <c r="O11" s="76"/>
       <c r="P11" s="76"/>
       <c r="Q11" s="76"/>
@@ -2036,7 +2060,7 @@
       <c r="BX11" s="76"/>
       <c r="BY11" s="76"/>
     </row>
-    <row r="12" spans="1:77" s="76" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:77" s="76" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="112" t="s">
         <v>16</v>
       </c>
@@ -2122,7 +2146,7 @@
       <c r="BX12" s="92"/>
       <c r="BY12" s="92"/>
     </row>
-    <row r="13" spans="1:77" s="76" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:77" s="76" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="74"/>
       <c r="C13" s="74"/>
       <c r="E13" s="74"/>
@@ -2198,7 +2222,7 @@
       <c r="BX13" s="92"/>
       <c r="BY13" s="92"/>
     </row>
-    <row r="14" spans="1:77" s="76" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:77" s="76" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="74"/>
       <c r="C14" s="74"/>
       <c r="E14" s="74"/>
@@ -2293,39 +2317,39 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32EE2485-5990-4EBE-AC24-196E706E14D7}">
   <dimension ref="A1:Q25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.453125" style="35" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" style="79" customWidth="1"/>
-    <col min="3" max="3" width="9.6328125" style="80" customWidth="1"/>
-    <col min="4" max="4" width="6.453125" style="81" customWidth="1"/>
-    <col min="5" max="5" width="6.453125" style="35" customWidth="1"/>
-    <col min="6" max="6" width="13.36328125" style="35" customWidth="1"/>
-    <col min="7" max="7" width="5.08984375" style="35" customWidth="1"/>
-    <col min="8" max="8" width="19.08984375" style="82" customWidth="1"/>
-    <col min="9" max="9" width="61.26953125" style="83" customWidth="1"/>
-    <col min="10" max="10" width="5.453125" style="36" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.08984375" style="36" hidden="1" customWidth="1"/>
-    <col min="12" max="13" width="5.08984375" style="36" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="1.7265625" style="36" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5" style="35" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="10.25" style="79" customWidth="1"/>
+    <col min="3" max="3" width="9.625" style="80" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="81" customWidth="1"/>
+    <col min="5" max="5" width="6.5" style="35" customWidth="1"/>
+    <col min="6" max="6" width="13.375" style="35" customWidth="1"/>
+    <col min="7" max="7" width="5.125" style="35" customWidth="1"/>
+    <col min="8" max="8" width="19.125" style="82" customWidth="1"/>
+    <col min="9" max="9" width="61.25" style="83" customWidth="1"/>
+    <col min="10" max="10" width="5.5" style="36" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.125" style="36" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="5.125" style="36" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="1.75" style="36" hidden="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="35" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="141" t="s">
+    <row r="1" spans="1:17" s="35" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="142" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="146"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="146"/>
+      <c r="I1" s="146"/>
       <c r="P1" s="36"/>
       <c r="Q1" s="37"/>
     </row>
-    <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>0</v>
       </c>
@@ -2366,7 +2390,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="46"/>
       <c r="B3" s="40"/>
       <c r="C3" s="47"/>
@@ -2381,7 +2405,7 @@
       <c r="M3" s="52"/>
       <c r="N3" s="51"/>
     </row>
-    <row r="4" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="46"/>
       <c r="B4" s="40"/>
       <c r="C4" s="47"/>
@@ -2402,7 +2426,7 @@
       <c r="M4" s="52"/>
       <c r="N4" s="51"/>
     </row>
-    <row r="5" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="46"/>
       <c r="B5" s="40"/>
       <c r="C5" s="47"/>
@@ -2423,7 +2447,7 @@
       <c r="M5" s="52"/>
       <c r="N5" s="51"/>
     </row>
-    <row r="6" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="46"/>
       <c r="B6" s="40"/>
       <c r="C6" s="47"/>
@@ -2444,7 +2468,7 @@
       <c r="M6" s="52"/>
       <c r="N6" s="51"/>
     </row>
-    <row r="7" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="46"/>
       <c r="B7" s="40"/>
       <c r="C7" s="47"/>
@@ -2465,7 +2489,7 @@
       <c r="M7" s="52"/>
       <c r="N7" s="51"/>
     </row>
-    <row r="8" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="46"/>
       <c r="B8" s="40"/>
       <c r="C8" s="47"/>
@@ -2480,7 +2504,7 @@
       <c r="M8" s="52"/>
       <c r="N8" s="51"/>
     </row>
-    <row r="9" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="46"/>
       <c r="B9" s="40"/>
       <c r="C9" s="47"/>
@@ -2501,7 +2525,7 @@
       <c r="M9" s="52"/>
       <c r="N9" s="51"/>
     </row>
-    <row r="10" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="46"/>
       <c r="B10" s="40"/>
       <c r="C10" s="47"/>
@@ -2522,7 +2546,7 @@
       <c r="M10" s="52"/>
       <c r="N10" s="51"/>
     </row>
-    <row r="11" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="46"/>
       <c r="B11" s="40"/>
       <c r="C11" s="47"/>
@@ -2543,7 +2567,7 @@
       <c r="M11" s="52"/>
       <c r="N11" s="51"/>
     </row>
-    <row r="12" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="46"/>
       <c r="B12" s="40"/>
       <c r="C12" s="47"/>
@@ -2564,7 +2588,7 @@
       <c r="M12" s="52"/>
       <c r="N12" s="51"/>
     </row>
-    <row r="13" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="46"/>
       <c r="B13" s="40"/>
       <c r="C13" s="47"/>
@@ -2585,7 +2609,7 @@
       <c r="M13" s="52"/>
       <c r="N13" s="51"/>
     </row>
-    <row r="14" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="53"/>
       <c r="C14" s="54"/>
       <c r="D14" s="54"/>
@@ -2595,7 +2619,7 @@
       <c r="H14" s="57"/>
       <c r="I14" s="49"/>
     </row>
-    <row r="15" spans="1:17" s="58" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" s="58" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="59" t="s">
         <v>16</v>
       </c>
@@ -2613,7 +2637,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="58" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" s="58" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="59"/>
       <c r="C16" s="60"/>
       <c r="D16" s="61"/>
@@ -2623,7 +2647,7 @@
       <c r="H16" s="61"/>
       <c r="I16" s="64"/>
     </row>
-    <row r="17" spans="2:9" s="58" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:9" s="58" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="59"/>
       <c r="C17" s="60"/>
       <c r="D17" s="61"/>
@@ -2633,7 +2657,7 @@
       <c r="H17" s="61"/>
       <c r="I17" s="65"/>
     </row>
-    <row r="18" spans="2:9" s="58" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:9" s="58" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="66"/>
       <c r="C18" s="60"/>
       <c r="D18" s="61" t="s">
@@ -2649,7 +2673,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="11.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="67"/>
       <c r="C19" s="68"/>
       <c r="D19" s="69"/>
@@ -2659,7 +2683,7 @@
       <c r="H19" s="71"/>
       <c r="I19" s="72"/>
     </row>
-    <row r="20" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="73"/>
       <c r="C20" s="74"/>
       <c r="D20" s="75"/>
@@ -2669,10 +2693,10 @@
       <c r="H20" s="77"/>
       <c r="I20" s="78"/>
     </row>
-    <row r="21" spans="2:9" ht="11.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="23" spans="2:9" ht="28" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="24" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="25" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="21" spans="2:9" ht="11.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:I1"/>
@@ -2685,36 +2709,36 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E98D86-3BBD-4165-99BF-0B3AF952A4EF}">
   <dimension ref="A1:J24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="28" customWidth="1"/>
-    <col min="2" max="2" width="18.36328125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="17.6328125" style="20" customWidth="1"/>
+    <col min="2" max="2" width="18.375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="17.625" style="20" customWidth="1"/>
     <col min="4" max="4" width="20" style="30" customWidth="1"/>
-    <col min="5" max="5" width="5.36328125" style="28" customWidth="1"/>
-    <col min="6" max="6" width="9.26953125" style="15" customWidth="1"/>
-    <col min="7" max="7" width="8.7265625" style="15" customWidth="1"/>
-    <col min="8" max="8" width="13.7265625" style="16" customWidth="1"/>
-    <col min="9" max="9" width="18.26953125" style="28" customWidth="1"/>
-    <col min="10" max="10" width="17.6328125" style="20" customWidth="1"/>
+    <col min="5" max="5" width="5.375" style="28" customWidth="1"/>
+    <col min="6" max="6" width="9.25" style="15" customWidth="1"/>
+    <col min="7" max="7" width="8.75" style="15" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="16" customWidth="1"/>
+    <col min="9" max="9" width="18.25" style="28" customWidth="1"/>
+    <col min="10" max="10" width="17.625" style="20" customWidth="1"/>
     <col min="11" max="16384" width="9" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="146" t="s">
+    <row r="1" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="147" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-    </row>
-    <row r="2" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="148"/>
+      <c r="C1" s="148"/>
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="148"/>
+      <c r="G1" s="148"/>
+      <c r="H1" s="148"/>
+      <c r="I1" s="148"/>
+      <c r="J1" s="148"/>
+    </row>
+    <row r="2" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>37</v>
       </c>
@@ -2746,7 +2770,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -2758,7 +2782,7 @@
       <c r="I3" s="12"/>
       <c r="J3" s="12"/>
     </row>
-    <row r="4" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -2770,7 +2794,7 @@
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12"/>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -2782,7 +2806,7 @@
       <c r="I5" s="12"/>
       <c r="J5" s="12"/>
     </row>
-    <row r="6" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -2794,7 +2818,7 @@
       <c r="I6" s="12"/>
       <c r="J6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -2806,7 +2830,7 @@
       <c r="I7" s="12"/>
       <c r="J7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -2818,7 +2842,7 @@
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
     </row>
-    <row r="9" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -2830,7 +2854,7 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
     </row>
-    <row r="10" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -2842,7 +2866,7 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
     </row>
-    <row r="11" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -2854,7 +2878,7 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
     </row>
-    <row r="12" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -2866,7 +2890,7 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
     </row>
-    <row r="13" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -2878,7 +2902,7 @@
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
     </row>
-    <row r="14" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -2890,7 +2914,7 @@
       <c r="I14" s="27"/>
       <c r="J14" s="27"/>
     </row>
-    <row r="15" spans="1:10" ht="19.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>16</v>
       </c>
@@ -2909,7 +2933,7 @@
       </c>
       <c r="J15" s="17"/>
     </row>
-    <row r="16" spans="1:10" ht="11.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
       <c r="C16" s="28"/>
@@ -2918,13 +2942,13 @@
       <c r="I16" s="29"/>
       <c r="J16" s="28"/>
     </row>
-    <row r="17" spans="1:10" ht="44.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="29"/>
       <c r="C17" s="28"/>
       <c r="D17" s="28"/>
       <c r="J17" s="28"/>
     </row>
-    <row r="18" spans="1:10" ht="75.650000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="17" t="s">
         <v>22</v>
       </c>
@@ -2938,7 +2962,7 @@
       <c r="I18" s="15"/>
       <c r="J18" s="28"/>
     </row>
-    <row r="19" spans="1:10" ht="19.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20"/>
       <c r="B19" s="20"/>
       <c r="E19" s="20"/>
@@ -2947,7 +2971,7 @@
       <c r="H19" s="32"/>
       <c r="I19" s="20"/>
     </row>
-    <row r="20" spans="1:10" ht="19.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="20"/>
       <c r="B20" s="20"/>
       <c r="E20" s="20"/>
@@ -2956,25 +2980,25 @@
       <c r="H20" s="33"/>
       <c r="I20" s="20"/>
     </row>
-    <row r="21" spans="1:10" s="28" customFormat="1" ht="19.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" s="28" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="20"/>
       <c r="D21" s="30"/>
       <c r="H21" s="34"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="1:10" s="28" customFormat="1" ht="19.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" s="28" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="20"/>
       <c r="D22" s="30"/>
       <c r="H22" s="34"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="1:10" s="28" customFormat="1" ht="19.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" s="28" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="20"/>
       <c r="D23" s="30"/>
       <c r="H23" s="34"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="1:10" s="28" customFormat="1" ht="19.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" s="28" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="20"/>
       <c r="D24" s="30"/>
       <c r="H24" s="34"/>
@@ -2992,36 +3016,36 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D6224E1-2B9C-43DA-8D8F-272D7D48239E}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" style="6" customWidth="1"/>
-    <col min="2" max="2" width="18.36328125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="18.375" style="6" customWidth="1"/>
     <col min="3" max="3" width="14" style="6" customWidth="1"/>
-    <col min="4" max="4" width="6.08984375" style="6" customWidth="1"/>
+    <col min="4" max="4" width="6.125" style="6" customWidth="1"/>
     <col min="5" max="5" width="8" style="6" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="7.36328125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="9.6328125" style="19" customWidth="1"/>
-    <col min="9" max="9" width="12.453125" style="6" customWidth="1"/>
-    <col min="10" max="10" width="17.453125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="11.875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="7.375" style="6" customWidth="1"/>
+    <col min="8" max="8" width="9.625" style="19" customWidth="1"/>
+    <col min="9" max="9" width="12.5" style="6" customWidth="1"/>
+    <col min="10" max="10" width="17.5" style="6" customWidth="1"/>
     <col min="11" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="148" t="s">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="149" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="149"/>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="149"/>
-      <c r="G1" s="149"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="149"/>
-      <c r="J1" s="149"/>
-    </row>
-    <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+    </row>
+    <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>37</v>
       </c>
@@ -3053,10 +3077,10 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
-      <c r="C3" s="150"/>
+      <c r="C3" s="138"/>
       <c r="D3" s="8"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
@@ -3065,10 +3089,10 @@
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="8"/>
-      <c r="C4" s="150"/>
+      <c r="C4" s="138"/>
       <c r="D4" s="8"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
@@ -3077,10 +3101,10 @@
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="150"/>
+      <c r="C5" s="138"/>
       <c r="D5" s="8"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
@@ -3089,10 +3113,10 @@
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
     </row>
-    <row r="6" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="8"/>
-      <c r="C6" s="150"/>
+      <c r="C6" s="138"/>
       <c r="D6" s="8"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
@@ -3101,10 +3125,10 @@
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
-    <row r="7" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="8"/>
-      <c r="C7" s="150"/>
+      <c r="C7" s="138"/>
       <c r="D7" s="8"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
@@ -3113,10 +3137,10 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="8"/>
-      <c r="C8" s="150"/>
+      <c r="C8" s="138"/>
       <c r="D8" s="8"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
@@ -3125,10 +3149,10 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
     </row>
-    <row r="9" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="8"/>
-      <c r="C9" s="150"/>
+      <c r="C9" s="138"/>
       <c r="D9" s="8"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
@@ -3137,10 +3161,10 @@
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="8"/>
-      <c r="C10" s="150"/>
+      <c r="C10" s="138"/>
       <c r="D10" s="8"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
@@ -3149,7 +3173,7 @@
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -3161,7 +3185,7 @@
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
     </row>
-    <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>16</v>
       </c>
@@ -3182,7 +3206,7 @@
       </c>
       <c r="J12" s="18"/>
     </row>
-    <row r="13" spans="1:10" ht="29.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="D13" s="15"/>
@@ -3193,7 +3217,7 @@
       <c r="I13" s="15"/>
       <c r="J13" s="18"/>
     </row>
-    <row r="14" spans="1:10" ht="46" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15"/>
       <c r="B14" s="15" t="s">
         <v>52</v>
@@ -3222,39 +3246,39 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D9062A-9A8A-4BB0-9697-639D0D0AC416}">
   <dimension ref="A1:Q25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.453125" style="35" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" style="79" customWidth="1"/>
-    <col min="3" max="3" width="9.6328125" style="80" customWidth="1"/>
-    <col min="4" max="4" width="6.453125" style="81" customWidth="1"/>
-    <col min="5" max="5" width="6.453125" style="35" customWidth="1"/>
-    <col min="6" max="6" width="13.36328125" style="35" customWidth="1"/>
-    <col min="7" max="7" width="5.08984375" style="35" customWidth="1"/>
-    <col min="8" max="8" width="19.08984375" style="82" customWidth="1"/>
-    <col min="9" max="9" width="61.26953125" style="83" customWidth="1"/>
-    <col min="10" max="10" width="5.453125" style="36" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.08984375" style="36" hidden="1" customWidth="1"/>
-    <col min="12" max="13" width="5.08984375" style="36" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="1.7265625" style="36" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5" style="35" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="10.25" style="79" customWidth="1"/>
+    <col min="3" max="3" width="9.625" style="80" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="81" customWidth="1"/>
+    <col min="5" max="5" width="6.5" style="35" customWidth="1"/>
+    <col min="6" max="6" width="13.375" style="35" customWidth="1"/>
+    <col min="7" max="7" width="5.125" style="35" customWidth="1"/>
+    <col min="8" max="8" width="19.125" style="82" customWidth="1"/>
+    <col min="9" max="9" width="61.25" style="83" customWidth="1"/>
+    <col min="10" max="10" width="5.5" style="36" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.125" style="36" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="5.125" style="36" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="1.75" style="36" hidden="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="35" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="141" t="s">
+    <row r="1" spans="1:17" s="35" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="146"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="146"/>
+      <c r="I1" s="146"/>
       <c r="P1" s="36"/>
       <c r="Q1" s="37"/>
     </row>
-    <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>0</v>
       </c>
@@ -3295,7 +3319,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="46"/>
       <c r="B3" s="40"/>
       <c r="C3" s="47"/>
@@ -3310,7 +3334,7 @@
       <c r="M3" s="52"/>
       <c r="N3" s="51"/>
     </row>
-    <row r="4" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="46"/>
       <c r="B4" s="40"/>
       <c r="C4" s="47"/>
@@ -3331,7 +3355,7 @@
       <c r="M4" s="52"/>
       <c r="N4" s="51"/>
     </row>
-    <row r="5" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="46"/>
       <c r="B5" s="40"/>
       <c r="C5" s="47"/>
@@ -3352,7 +3376,7 @@
       <c r="M5" s="52"/>
       <c r="N5" s="51"/>
     </row>
-    <row r="6" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="46"/>
       <c r="B6" s="40"/>
       <c r="C6" s="47"/>
@@ -3373,7 +3397,7 @@
       <c r="M6" s="52"/>
       <c r="N6" s="51"/>
     </row>
-    <row r="7" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="46"/>
       <c r="B7" s="40"/>
       <c r="C7" s="47"/>
@@ -3394,7 +3418,7 @@
       <c r="M7" s="52"/>
       <c r="N7" s="51"/>
     </row>
-    <row r="8" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="46"/>
       <c r="B8" s="40"/>
       <c r="C8" s="47"/>
@@ -3409,7 +3433,7 @@
       <c r="M8" s="52"/>
       <c r="N8" s="51"/>
     </row>
-    <row r="9" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="46"/>
       <c r="B9" s="40"/>
       <c r="C9" s="47"/>
@@ -3430,7 +3454,7 @@
       <c r="M9" s="52"/>
       <c r="N9" s="51"/>
     </row>
-    <row r="10" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="46"/>
       <c r="B10" s="40"/>
       <c r="C10" s="47"/>
@@ -3451,7 +3475,7 @@
       <c r="M10" s="52"/>
       <c r="N10" s="51"/>
     </row>
-    <row r="11" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="46"/>
       <c r="B11" s="40"/>
       <c r="C11" s="47"/>
@@ -3472,7 +3496,7 @@
       <c r="M11" s="52"/>
       <c r="N11" s="51"/>
     </row>
-    <row r="12" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="46"/>
       <c r="B12" s="40"/>
       <c r="C12" s="47"/>
@@ -3493,7 +3517,7 @@
       <c r="M12" s="52"/>
       <c r="N12" s="51"/>
     </row>
-    <row r="13" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="46"/>
       <c r="B13" s="40"/>
       <c r="C13" s="47"/>
@@ -3514,7 +3538,7 @@
       <c r="M13" s="52"/>
       <c r="N13" s="51"/>
     </row>
-    <row r="14" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="53"/>
       <c r="C14" s="54"/>
       <c r="D14" s="54"/>
@@ -3524,7 +3548,7 @@
       <c r="H14" s="57"/>
       <c r="I14" s="49"/>
     </row>
-    <row r="15" spans="1:17" s="58" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" s="58" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="59" t="s">
         <v>16</v>
       </c>
@@ -3542,7 +3566,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="58" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" s="58" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="59"/>
       <c r="C16" s="60"/>
       <c r="D16" s="61"/>
@@ -3552,7 +3576,7 @@
       <c r="H16" s="61"/>
       <c r="I16" s="64"/>
     </row>
-    <row r="17" spans="2:9" s="58" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:9" s="58" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="59"/>
       <c r="C17" s="60"/>
       <c r="D17" s="61"/>
@@ -3562,7 +3586,7 @@
       <c r="H17" s="61"/>
       <c r="I17" s="65"/>
     </row>
-    <row r="18" spans="2:9" s="58" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:9" s="58" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="66"/>
       <c r="C18" s="60"/>
       <c r="D18" s="61" t="s">
@@ -3578,7 +3602,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="11.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="67"/>
       <c r="C19" s="68"/>
       <c r="D19" s="69"/>
@@ -3588,7 +3612,7 @@
       <c r="H19" s="71"/>
       <c r="I19" s="72"/>
     </row>
-    <row r="20" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="73"/>
       <c r="C20" s="74"/>
       <c r="D20" s="75"/>
@@ -3598,10 +3622,10 @@
       <c r="H20" s="77"/>
       <c r="I20" s="78"/>
     </row>
-    <row r="21" spans="2:9" ht="11.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="23" spans="2:9" ht="28" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="24" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="25" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="21" spans="2:9" ht="11.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:I1"/>

--- a/templates/accounting-template.xlsx
+++ b/templates/accounting-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\school-substitution-sys\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D622EB-1052-4B99-90A3-73E8F81BFBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8313EE42-BE54-43B4-B91F-A846217C3E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1767,10 +1767,7 @@
       <c r="J3" s="99"/>
       <c r="K3" s="100"/>
       <c r="L3" s="101"/>
-      <c r="M3" s="102" t="str">
-        <f>IF(K3-L3=0,"",K3-L3)</f>
-        <v/>
-      </c>
+      <c r="M3" s="102"/>
       <c r="N3" s="103"/>
       <c r="O3" s="104"/>
       <c r="P3" s="104"/>
@@ -1788,10 +1785,7 @@
       <c r="J4" s="99"/>
       <c r="K4" s="100"/>
       <c r="L4" s="101"/>
-      <c r="M4" s="102" t="str">
-        <f t="shared" ref="M4:M10" si="0">IF(K4-L4=0,"",K4-L4)</f>
-        <v/>
-      </c>
+      <c r="M4" s="102"/>
       <c r="N4" s="103"/>
       <c r="O4" s="104"/>
       <c r="P4" s="104"/>
@@ -1809,10 +1803,7 @@
       <c r="J5" s="99"/>
       <c r="K5" s="100"/>
       <c r="L5" s="101"/>
-      <c r="M5" s="102" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="M5" s="102"/>
       <c r="N5" s="103"/>
       <c r="O5" s="104"/>
       <c r="P5" s="104"/>
@@ -1830,10 +1821,7 @@
       <c r="J6" s="99"/>
       <c r="K6" s="100"/>
       <c r="L6" s="101"/>
-      <c r="M6" s="102" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="M6" s="102"/>
       <c r="N6" s="103"/>
       <c r="O6" s="104"/>
       <c r="P6" s="104"/>
@@ -1851,10 +1839,7 @@
       <c r="J7" s="99"/>
       <c r="K7" s="100"/>
       <c r="L7" s="101"/>
-      <c r="M7" s="102" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="M7" s="102"/>
       <c r="N7" s="103"/>
       <c r="O7" s="104"/>
       <c r="P7" s="104"/>
@@ -1872,10 +1857,7 @@
       <c r="J8" s="99"/>
       <c r="K8" s="100"/>
       <c r="L8" s="101"/>
-      <c r="M8" s="102" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="M8" s="102"/>
       <c r="N8" s="107"/>
       <c r="O8" s="104"/>
       <c r="P8" s="104"/>
@@ -1893,10 +1875,7 @@
       <c r="J9" s="99"/>
       <c r="K9" s="100"/>
       <c r="L9" s="101"/>
-      <c r="M9" s="102" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="M9" s="102"/>
       <c r="N9" s="103"/>
       <c r="O9" s="104"/>
       <c r="P9" s="104"/>
@@ -1913,10 +1892,7 @@
       <c r="J10" s="96"/>
       <c r="K10" s="109"/>
       <c r="L10" s="110"/>
-      <c r="M10" s="102" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="M10" s="102"/>
       <c r="N10" s="111"/>
       <c r="O10" s="76"/>
       <c r="P10" s="76"/>

--- a/templates/accounting-template.xlsx
+++ b/templates/accounting-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\school-substitution-sys\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8313EE42-BE54-43B4-B91F-A846217C3E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AE5EC0-8798-4E8E-8B87-EFBE4D0D9916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1688,7 +1688,7 @@
     <col min="10" max="10" width="6.5" style="84" customWidth="1"/>
     <col min="11" max="11" width="14.5" style="84" customWidth="1"/>
     <col min="12" max="12" width="9" style="115" customWidth="1"/>
-    <col min="13" max="13" width="11.875" style="84" customWidth="1"/>
+    <col min="13" max="13" width="14.375" style="84" customWidth="1"/>
     <col min="14" max="14" width="40.5" style="116" customWidth="1"/>
     <col min="15" max="16384" width="9" style="92"/>
   </cols>

--- a/templates/accounting-template.xlsx
+++ b/templates/accounting-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\school-substitution-sys\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AE5EC0-8798-4E8E-8B87-EFBE4D0D9916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B223AB0A-774F-4AD3-9067-A21421839B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="超鐘點" sheetId="5" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="公付代課" sheetId="3" r:id="rId3"/>
     <sheet name=" 自付代課" sheetId="2" r:id="rId4"/>
     <sheet name="代導鐘點" sheetId="1" r:id="rId5"/>
-    <sheet name="115.6.1-6.30公付代課-身心調適假" sheetId="6" r:id="rId6"/>
+    <sheet name="公付代課-身心調適假" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="64">
   <si>
     <t>編號</t>
   </si>
@@ -49,27 +49,13 @@
     <t>姓名</t>
   </si>
   <si>
-    <t>每週超鐘點(兼課)</t>
-  </si>
-  <si>
     <t>超鐘星期/節次</t>
-  </si>
-  <si>
-    <t>應發周數</t>
-  </si>
-  <si>
-    <t>共兼
-課數</t>
   </si>
   <si>
     <t>請假
 扣超鐘節</t>
   </si>
   <si>
-    <t>合計
-時數</t>
-  </si>
-  <si>
     <t>鐘點費</t>
   </si>
   <si>
@@ -170,10 +156,6 @@
     <t>節次</t>
   </si>
   <si>
-    <t>合計
-節數</t>
-  </si>
-  <si>
     <t>備</t>
   </si>
   <si>
@@ -211,10 +193,6 @@
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
-    <t>臺北市立建成國中[[年]]年[[月]]月([[日期]])超鐘點（[[計畫]]）印領清冊</t>
-    <phoneticPr fontId="25" type="noConversion"/>
-  </si>
-  <si>
     <t>臺北市立建成國中[[年]]年[[月]]月([[日期]])教師兼課費印領清冊</t>
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
@@ -231,10 +209,47 @@
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
-    <t>臺北市立建成國中[[年]]年[[月]]月([[日期]])公付代課-身心調適假鐘點費印領清冊</t>
-  </si>
-  <si>
     <t>課務</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>每週超鐘點</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>應發
+節數</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>應發
+週數</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>實發
+節數</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>鐘點費單價</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>鐘點費
+單價</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>合計節數</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>臺北市立建成國民中學[[年]]年[[月]]月([[日期]])公付代課-身心調適假鐘點費印領清冊</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>臺北市立建成國民中學[[年]]年[[月]]月([[日期]])超鐘點費（[[計畫]]）印領清冊</t>
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
 </sst>
@@ -942,6 +957,18 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -950,18 +977,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1235,22 +1250,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="108" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="142" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="142"/>
-      <c r="H1" s="142"/>
-      <c r="I1" s="142"/>
-      <c r="J1" s="142"/>
-      <c r="K1" s="142"/>
-      <c r="L1" s="142"/>
-      <c r="M1" s="142"/>
-      <c r="N1" s="142"/>
-      <c r="O1" s="142"/>
+      <c r="B1" s="139" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
       <c r="P1" s="117"/>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1264,40 +1279,40 @@
         <v>2</v>
       </c>
       <c r="D2" s="118" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="119" t="s">
+      <c r="F2" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="40" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="40" t="s">
+      <c r="I2" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="K2" s="120" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="L2" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="M2" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="118" t="s">
+      <c r="N2" s="121" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="120" t="s">
+      <c r="O2" s="120" t="s">
         <v>10</v>
-      </c>
-      <c r="L2" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="42" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" s="121" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="120" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -1535,7 +1550,7 @@
       </c>
       <c r="E15" s="134"/>
       <c r="F15" s="96" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G15" s="96"/>
       <c r="H15" s="97"/>
@@ -1551,76 +1566,76 @@
       <c r="O15" s="111"/>
     </row>
     <row r="16" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="143" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="144"/>
-      <c r="D16" s="144"/>
-      <c r="E16" s="144"/>
-      <c r="F16" s="144"/>
-      <c r="G16" s="144"/>
-      <c r="H16" s="144"/>
-      <c r="I16" s="144"/>
-      <c r="J16" s="144"/>
-      <c r="K16" s="144"/>
-      <c r="L16" s="144"/>
-      <c r="M16" s="144"/>
-      <c r="N16" s="144"/>
-      <c r="O16" s="145"/>
+      <c r="B16" s="140" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="141"/>
+      <c r="D16" s="141"/>
+      <c r="E16" s="141"/>
+      <c r="F16" s="141"/>
+      <c r="G16" s="141"/>
+      <c r="H16" s="141"/>
+      <c r="I16" s="141"/>
+      <c r="J16" s="141"/>
+      <c r="K16" s="141"/>
+      <c r="L16" s="141"/>
+      <c r="M16" s="141"/>
+      <c r="N16" s="141"/>
+      <c r="O16" s="142"/>
     </row>
     <row r="17" spans="2:16" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="135" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C17" s="70"/>
       <c r="D17" s="71" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E17" s="76"/>
       <c r="F17" s="74"/>
       <c r="G17" s="71" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H17" s="68"/>
       <c r="J17" s="74"/>
       <c r="K17" s="112" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L17" s="74"/>
       <c r="M17" s="68"/>
       <c r="N17" s="68" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="O17" s="113" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="87.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="60"/>
       <c r="C18" s="70"/>
       <c r="D18" s="71" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E18" s="76"/>
       <c r="F18" s="74"/>
       <c r="G18" s="71" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H18" s="68"/>
       <c r="J18" s="74"/>
       <c r="K18" s="112" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L18" s="74"/>
       <c r="M18" s="68"/>
       <c r="N18" s="68" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="O18" s="78"/>
     </row>
     <row r="19" spans="2:16" ht="0.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K19" s="137" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="2:16" ht="23.45" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1694,21 +1709,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:77" s="84" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="139" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
+      <c r="B1" s="143" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
+      <c r="K1" s="143"/>
+      <c r="L1" s="143"/>
+      <c r="M1" s="143"/>
+      <c r="N1" s="143"/>
     </row>
     <row r="2" spans="1:77" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="85" t="s">
@@ -1721,37 +1736,37 @@
         <v>2</v>
       </c>
       <c r="D2" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="89" t="s">
+      <c r="F2" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="88" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="88" t="s">
+      <c r="I2" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="88" t="s">
+        <v>60</v>
+      </c>
+      <c r="K2" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="88" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="88" t="s">
+      <c r="L2" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="88" t="s">
+      <c r="M2" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="90" t="s">
+      <c r="N2" s="87" t="s">
         <v>10</v>
-      </c>
-      <c r="L2" s="91" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" s="90" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" s="87" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:77" s="105" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1959,19 +1974,19 @@
       <c r="BY10" s="76"/>
     </row>
     <row r="11" spans="1:77" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="140"/>
-      <c r="C11" s="141"/>
-      <c r="D11" s="141"/>
-      <c r="E11" s="141"/>
-      <c r="F11" s="141"/>
-      <c r="G11" s="141"/>
-      <c r="H11" s="141"/>
-      <c r="I11" s="141"/>
-      <c r="J11" s="141"/>
-      <c r="K11" s="141"/>
-      <c r="L11" s="141"/>
-      <c r="M11" s="141"/>
-      <c r="N11" s="141"/>
+      <c r="B11" s="144"/>
+      <c r="C11" s="145"/>
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="145"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="145"/>
+      <c r="J11" s="145"/>
+      <c r="K11" s="145"/>
+      <c r="L11" s="145"/>
+      <c r="M11" s="145"/>
+      <c r="N11" s="145"/>
       <c r="O11" s="76"/>
       <c r="P11" s="76"/>
       <c r="Q11" s="76"/>
@@ -2038,25 +2053,25 @@
     </row>
     <row r="12" spans="1:77" s="76" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="112" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C12" s="74"/>
       <c r="E12" s="74"/>
       <c r="F12" s="77" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G12" s="74"/>
       <c r="I12" s="75"/>
       <c r="J12" s="77" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="K12" s="74"/>
       <c r="L12" s="68" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M12" s="74"/>
       <c r="N12" s="112" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="O12" s="92"/>
       <c r="P12" s="92"/>
@@ -2203,16 +2218,16 @@
       <c r="C14" s="74"/>
       <c r="E14" s="74"/>
       <c r="F14" s="77" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G14" s="74"/>
       <c r="I14" s="75"/>
       <c r="J14" s="77" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K14" s="74"/>
       <c r="L14" s="68" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M14" s="74"/>
       <c r="N14" s="113"/>
@@ -2312,8 +2327,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="35" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="142" t="s">
-        <v>57</v>
+      <c r="B1" s="139" t="s">
+        <v>51</v>
       </c>
       <c r="C1" s="146"/>
       <c r="D1" s="146"/>
@@ -2336,34 +2351,34 @@
         <v>2</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E2" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="I2" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="121" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="39" t="s">
-        <v>14</v>
-      </c>
       <c r="K2" s="43" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="M2" s="45" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2597,20 +2612,20 @@
     </row>
     <row r="15" spans="1:17" s="58" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="59" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C15" s="60"/>
       <c r="D15" s="61" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E15" s="62"/>
       <c r="F15" s="63"/>
       <c r="G15" s="62" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H15" s="61"/>
       <c r="I15" s="64" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="58" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2637,16 +2652,16 @@
       <c r="B18" s="66"/>
       <c r="C18" s="60"/>
       <c r="D18" s="61" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E18" s="62"/>
       <c r="F18" s="63"/>
       <c r="G18" s="62" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H18" s="61"/>
       <c r="I18" s="64" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2702,7 +2717,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="147" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B1" s="148"/>
       <c r="C1" s="148"/>
@@ -2716,34 +2731,34 @@
     </row>
     <row r="2" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="F2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="J2" s="23" t="s">
         <v>39</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="J2" s="23" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
@@ -2892,20 +2907,20 @@
     </row>
     <row r="15" spans="1:10" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C15" s="28"/>
       <c r="D15" s="17" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I15" s="28" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J15" s="17"/>
     </row>
@@ -2926,14 +2941,14 @@
     </row>
     <row r="18" spans="1:10" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="17" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C18" s="28"/>
       <c r="D18" s="17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I18" s="15"/>
       <c r="J18" s="28"/>
@@ -3009,7 +3024,7 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="149" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B1" s="150"/>
       <c r="C1" s="150"/>
@@ -3023,34 +3038,34 @@
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="F2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3163,22 +3178,22 @@
     </row>
     <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="15" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F12" s="15"/>
       <c r="G12" s="15" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H12" s="16"/>
       <c r="I12" s="17" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J12" s="18"/>
     </row>
@@ -3196,15 +3211,15 @@
     <row r="14" spans="1:10" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15"/>
       <c r="B14" s="15" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="15" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="15" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H14" s="16"/>
       <c r="I14" s="15"/>
@@ -3241,8 +3256,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="35" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="142" t="s">
-        <v>60</v>
+      <c r="B1" s="139" t="s">
+        <v>62</v>
       </c>
       <c r="C1" s="146"/>
       <c r="D1" s="146"/>
@@ -3265,34 +3280,34 @@
         <v>2</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E2" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="I2" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="121" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="39" t="s">
-        <v>14</v>
-      </c>
       <c r="K2" s="43" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="M2" s="45" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3526,20 +3541,20 @@
     </row>
     <row r="15" spans="1:17" s="58" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="59" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C15" s="60"/>
       <c r="D15" s="61" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E15" s="62"/>
       <c r="F15" s="63"/>
       <c r="G15" s="62" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H15" s="61"/>
       <c r="I15" s="64" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="58" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3566,16 +3581,16 @@
       <c r="B18" s="66"/>
       <c r="C18" s="60"/>
       <c r="D18" s="61" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E18" s="62"/>
       <c r="F18" s="63"/>
       <c r="G18" s="62" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H18" s="61"/>
       <c r="I18" s="64" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">

--- a/templates/accounting-template.xlsx
+++ b/templates/accounting-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\school-substitution-sys\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B223AB0A-774F-4AD3-9067-A21421839B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9B5DF6-B53E-43E0-A16C-F89D7884C783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="超鐘點" sheetId="5" r:id="rId1"/>
@@ -3010,9 +3010,9 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" style="6" customWidth="1"/>
-    <col min="2" max="2" width="18.375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="20.25" style="6" customWidth="1"/>
     <col min="3" max="3" width="14" style="6" customWidth="1"/>
-    <col min="4" max="4" width="6.125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="7.25" style="6" customWidth="1"/>
     <col min="5" max="5" width="8" style="6" customWidth="1"/>
     <col min="6" max="6" width="11.875" style="6" customWidth="1"/>
     <col min="7" max="7" width="7.375" style="6" customWidth="1"/>

--- a/templates/accounting-template.xlsx
+++ b/templates/accounting-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\school-substitution-sys\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9B5DF6-B53E-43E0-A16C-F89D7884C783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A15601-6E41-47AE-9A73-9C2DA5B16823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="64">
   <si>
     <t>編號</t>
   </si>
@@ -154,12 +154,6 @@
   </si>
   <si>
     <t>節次</t>
-  </si>
-  <si>
-    <t>備</t>
-  </si>
-  <si>
-    <t>註</t>
   </si>
   <si>
     <t xml:space="preserve">       教學組長</t>
@@ -250,6 +244,14 @@
   </si>
   <si>
     <t>臺北市立建成國民中學[[年]]年[[月]]月([[日期]])超鐘點費（[[計畫]]）印領清冊</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註</t>
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
 </sst>
@@ -539,7 +541,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -594,9 +596,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -957,6 +956,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -980,12 +985,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1231,447 +1230,447 @@
   <dimension ref="A1:P22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.5" style="108" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="63" customWidth="1"/>
-    <col min="3" max="3" width="15.125" style="92" customWidth="1"/>
-    <col min="4" max="4" width="9.375" style="92" customWidth="1"/>
-    <col min="5" max="5" width="25.875" style="136" customWidth="1"/>
-    <col min="6" max="6" width="5.875" style="114" customWidth="1"/>
-    <col min="7" max="7" width="6.5" style="114" customWidth="1"/>
-    <col min="8" max="8" width="6.875" style="84" customWidth="1"/>
-    <col min="9" max="9" width="9" style="74" customWidth="1"/>
-    <col min="10" max="10" width="8.125" style="84" customWidth="1"/>
-    <col min="11" max="11" width="17.125" style="84" customWidth="1"/>
-    <col min="12" max="13" width="0.25" style="92" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="12.75" style="92" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="48.375" style="117" customWidth="1"/>
-    <col min="16" max="16" width="11.5" style="92" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="92"/>
+    <col min="1" max="1" width="5.5" style="107" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="62" customWidth="1"/>
+    <col min="3" max="3" width="15.125" style="91" customWidth="1"/>
+    <col min="4" max="4" width="9.375" style="91" customWidth="1"/>
+    <col min="5" max="5" width="25.875" style="135" customWidth="1"/>
+    <col min="6" max="6" width="5.875" style="113" customWidth="1"/>
+    <col min="7" max="7" width="6.5" style="113" customWidth="1"/>
+    <col min="8" max="8" width="6.875" style="83" customWidth="1"/>
+    <col min="9" max="9" width="9" style="73" customWidth="1"/>
+    <col min="10" max="10" width="8.125" style="83" customWidth="1"/>
+    <col min="11" max="11" width="17.125" style="83" customWidth="1"/>
+    <col min="12" max="13" width="0.25" style="91" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="12.75" style="91" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="48.375" style="116" customWidth="1"/>
+    <col min="16" max="16" width="11.5" style="91" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="91"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="108" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="139" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="117"/>
+    <row r="1" spans="1:16" s="107" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="140" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="140"/>
+      <c r="M1" s="140"/>
+      <c r="N1" s="140"/>
+      <c r="O1" s="140"/>
+      <c r="P1" s="116"/>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="39" t="s">
+      <c r="A2" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="94" t="s">
+      <c r="C2" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="118" t="s">
+      <c r="D2" s="117" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="118" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="119" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="40" t="s">
+      <c r="J2" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="K2" s="120" t="s">
+      <c r="K2" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="40" t="s">
+      <c r="L2" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="42" t="s">
+      <c r="M2" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="121" t="s">
+      <c r="N2" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="120" t="s">
+      <c r="O2" s="119" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="86"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="99"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="125"/>
-      <c r="M3" s="126"/>
-      <c r="N3" s="100"/>
-      <c r="O3" s="127"/>
-      <c r="P3" s="128"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="121"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="98"/>
+      <c r="L3" s="124"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="99"/>
+      <c r="O3" s="126"/>
+      <c r="P3" s="127"/>
     </row>
     <row r="4" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="86"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="123"/>
-      <c r="E4" s="124"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="125"/>
-      <c r="M4" s="126"/>
-      <c r="N4" s="100">
+      <c r="A4" s="85"/>
+      <c r="B4" s="121"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="125"/>
+      <c r="N4" s="99">
         <f t="shared" ref="N4:N13" si="0">K4</f>
         <v>0</v>
       </c>
-      <c r="O4" s="127"/>
+      <c r="O4" s="126"/>
     </row>
     <row r="5" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="86"/>
-      <c r="B5" s="122"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="123"/>
-      <c r="E5" s="124"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="99"/>
-      <c r="K5" s="99"/>
-      <c r="L5" s="125"/>
-      <c r="M5" s="126"/>
-      <c r="N5" s="100">
+      <c r="A5" s="85"/>
+      <c r="B5" s="121"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="122"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="96"/>
+      <c r="I5" s="97"/>
+      <c r="J5" s="98"/>
+      <c r="K5" s="98"/>
+      <c r="L5" s="124"/>
+      <c r="M5" s="125"/>
+      <c r="N5" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O5" s="127"/>
+      <c r="O5" s="126"/>
     </row>
     <row r="6" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="86"/>
-      <c r="B6" s="122"/>
-      <c r="C6" s="94"/>
-      <c r="D6" s="123"/>
-      <c r="E6" s="124"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="96"/>
-      <c r="H6" s="97"/>
-      <c r="I6" s="98"/>
-      <c r="J6" s="99"/>
-      <c r="K6" s="99"/>
-      <c r="L6" s="125"/>
-      <c r="M6" s="126"/>
-      <c r="N6" s="100">
+      <c r="A6" s="85"/>
+      <c r="B6" s="121"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="123"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="96"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="98"/>
+      <c r="K6" s="98"/>
+      <c r="L6" s="124"/>
+      <c r="M6" s="125"/>
+      <c r="N6" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O6" s="127"/>
+      <c r="O6" s="126"/>
     </row>
     <row r="7" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="86"/>
-      <c r="B7" s="122"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="124"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="97"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="99"/>
-      <c r="K7" s="99"/>
-      <c r="L7" s="125"/>
-      <c r="M7" s="125"/>
-      <c r="N7" s="100">
+      <c r="A7" s="85"/>
+      <c r="B7" s="121"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="98"/>
+      <c r="K7" s="98"/>
+      <c r="L7" s="124"/>
+      <c r="M7" s="124"/>
+      <c r="N7" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O7" s="129"/>
+      <c r="O7" s="128"/>
     </row>
     <row r="8" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="86"/>
-      <c r="B8" s="122"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="123"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="98"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="97"/>
-      <c r="I8" s="98"/>
-      <c r="J8" s="99"/>
-      <c r="K8" s="99"/>
-      <c r="L8" s="125"/>
-      <c r="M8" s="125"/>
-      <c r="N8" s="100"/>
-      <c r="O8" s="130"/>
+      <c r="A8" s="85"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="122"/>
+      <c r="E8" s="123"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="96"/>
+      <c r="I8" s="97"/>
+      <c r="J8" s="98"/>
+      <c r="K8" s="98"/>
+      <c r="L8" s="124"/>
+      <c r="M8" s="124"/>
+      <c r="N8" s="99"/>
+      <c r="O8" s="129"/>
     </row>
     <row r="9" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="86"/>
-      <c r="B9" s="122"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="123"/>
-      <c r="E9" s="124"/>
-      <c r="F9" s="98"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="97"/>
-      <c r="I9" s="98"/>
-      <c r="J9" s="99"/>
-      <c r="K9" s="99"/>
-      <c r="L9" s="125"/>
-      <c r="M9" s="95"/>
-      <c r="N9" s="100">
+      <c r="A9" s="85"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="122"/>
+      <c r="E9" s="123"/>
+      <c r="F9" s="97"/>
+      <c r="G9" s="95"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="97"/>
+      <c r="J9" s="98"/>
+      <c r="K9" s="98"/>
+      <c r="L9" s="124"/>
+      <c r="M9" s="94"/>
+      <c r="N9" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O9" s="130"/>
+      <c r="O9" s="129"/>
     </row>
     <row r="10" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="86"/>
-      <c r="B10" s="122"/>
-      <c r="C10" s="94"/>
-      <c r="D10" s="123"/>
-      <c r="E10" s="124"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="96"/>
-      <c r="H10" s="97"/>
-      <c r="I10" s="98"/>
-      <c r="J10" s="99"/>
-      <c r="K10" s="99"/>
-      <c r="L10" s="125"/>
-      <c r="M10" s="95"/>
-      <c r="N10" s="100"/>
-      <c r="O10" s="130"/>
+      <c r="A10" s="85"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="122"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="97"/>
+      <c r="G10" s="95"/>
+      <c r="H10" s="96"/>
+      <c r="I10" s="97"/>
+      <c r="J10" s="98"/>
+      <c r="K10" s="98"/>
+      <c r="L10" s="124"/>
+      <c r="M10" s="94"/>
+      <c r="N10" s="99"/>
+      <c r="O10" s="129"/>
     </row>
     <row r="11" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="86"/>
-      <c r="B11" s="122"/>
-      <c r="C11" s="94"/>
-      <c r="D11" s="123"/>
-      <c r="E11" s="124"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="96"/>
-      <c r="H11" s="97"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="99"/>
-      <c r="K11" s="99"/>
-      <c r="L11" s="125"/>
-      <c r="M11" s="126"/>
-      <c r="N11" s="100"/>
-      <c r="O11" s="127"/>
+      <c r="A11" s="85"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="122"/>
+      <c r="E11" s="123"/>
+      <c r="F11" s="97"/>
+      <c r="G11" s="95"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="97"/>
+      <c r="J11" s="98"/>
+      <c r="K11" s="98"/>
+      <c r="L11" s="124"/>
+      <c r="M11" s="125"/>
+      <c r="N11" s="99"/>
+      <c r="O11" s="126"/>
     </row>
     <row r="12" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="86"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="123"/>
-      <c r="E12" s="124"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="96"/>
-      <c r="H12" s="97"/>
-      <c r="I12" s="98"/>
-      <c r="J12" s="99"/>
-      <c r="K12" s="99"/>
-      <c r="L12" s="125"/>
-      <c r="M12" s="125"/>
-      <c r="N12" s="100">
+      <c r="A12" s="85"/>
+      <c r="B12" s="121"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="123"/>
+      <c r="F12" s="97"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="96"/>
+      <c r="I12" s="97"/>
+      <c r="J12" s="98"/>
+      <c r="K12" s="98"/>
+      <c r="L12" s="124"/>
+      <c r="M12" s="124"/>
+      <c r="N12" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O12" s="129"/>
+      <c r="O12" s="128"/>
     </row>
     <row r="13" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="86"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="124"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="97"/>
-      <c r="I13" s="98"/>
-      <c r="J13" s="99"/>
-      <c r="K13" s="99"/>
-      <c r="L13" s="125"/>
-      <c r="M13" s="132"/>
-      <c r="N13" s="100">
+      <c r="A13" s="85"/>
+      <c r="B13" s="121"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="123"/>
+      <c r="F13" s="97"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="97"/>
+      <c r="J13" s="98"/>
+      <c r="K13" s="98"/>
+      <c r="L13" s="124"/>
+      <c r="M13" s="131"/>
+      <c r="N13" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O13" s="127"/>
+      <c r="O13" s="126"/>
     </row>
     <row r="14" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="86"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="94"/>
-      <c r="D14" s="123"/>
-      <c r="E14" s="124"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="96"/>
-      <c r="H14" s="97"/>
-      <c r="I14" s="98"/>
-      <c r="J14" s="99"/>
-      <c r="K14" s="99"/>
-      <c r="L14" s="125"/>
-      <c r="M14" s="132"/>
-      <c r="N14" s="100"/>
-      <c r="O14" s="127"/>
+      <c r="A14" s="85"/>
+      <c r="B14" s="121"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="123"/>
+      <c r="F14" s="97"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="97"/>
+      <c r="J14" s="98"/>
+      <c r="K14" s="98"/>
+      <c r="L14" s="124"/>
+      <c r="M14" s="131"/>
+      <c r="N14" s="99"/>
+      <c r="O14" s="126"/>
     </row>
     <row r="15" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="133"/>
-      <c r="C15" s="96"/>
-      <c r="D15" s="87">
+      <c r="B15" s="132"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="86">
         <f>SUM(D3:D14)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="134"/>
-      <c r="F15" s="96" t="s">
+      <c r="E15" s="133"/>
+      <c r="F15" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="96"/>
-      <c r="H15" s="97"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="99"/>
-      <c r="K15" s="131"/>
-      <c r="L15" s="95"/>
-      <c r="M15" s="95"/>
-      <c r="N15" s="131">
+      <c r="G15" s="95"/>
+      <c r="H15" s="96"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="98"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="94"/>
+      <c r="M15" s="94"/>
+      <c r="N15" s="130">
         <f>SUM(N3:N14)</f>
         <v>0</v>
       </c>
-      <c r="O15" s="111"/>
+      <c r="O15" s="110"/>
     </row>
     <row r="16" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="140" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="141"/>
-      <c r="D16" s="141"/>
-      <c r="E16" s="141"/>
-      <c r="F16" s="141"/>
-      <c r="G16" s="141"/>
-      <c r="H16" s="141"/>
-      <c r="I16" s="141"/>
-      <c r="J16" s="141"/>
-      <c r="K16" s="141"/>
-      <c r="L16" s="141"/>
-      <c r="M16" s="141"/>
-      <c r="N16" s="141"/>
-      <c r="O16" s="142"/>
+      <c r="B16" s="141" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="142"/>
+      <c r="D16" s="142"/>
+      <c r="E16" s="142"/>
+      <c r="F16" s="142"/>
+      <c r="G16" s="142"/>
+      <c r="H16" s="142"/>
+      <c r="I16" s="142"/>
+      <c r="J16" s="142"/>
+      <c r="K16" s="142"/>
+      <c r="L16" s="142"/>
+      <c r="M16" s="142"/>
+      <c r="N16" s="142"/>
+      <c r="O16" s="143"/>
     </row>
     <row r="17" spans="2:16" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="135" t="s">
+      <c r="B17" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="70"/>
-      <c r="D17" s="71" t="s">
+      <c r="C17" s="69"/>
+      <c r="D17" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="76"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="71" t="s">
+      <c r="E17" s="75"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="68"/>
-      <c r="J17" s="74"/>
-      <c r="K17" s="112" t="s">
+      <c r="H17" s="67"/>
+      <c r="J17" s="73"/>
+      <c r="K17" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="L17" s="74"/>
-      <c r="M17" s="68"/>
-      <c r="N17" s="68" t="s">
+      <c r="L17" s="73"/>
+      <c r="M17" s="67"/>
+      <c r="N17" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="O17" s="113" t="s">
+      <c r="O17" s="112" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="87.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="60"/>
-      <c r="C18" s="70"/>
-      <c r="D18" s="71" t="s">
+      <c r="B18" s="59"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="76"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="71" t="s">
+      <c r="E18" s="75"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="68"/>
-      <c r="J18" s="74"/>
-      <c r="K18" s="112" t="s">
+      <c r="H18" s="67"/>
+      <c r="J18" s="73"/>
+      <c r="K18" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="L18" s="74"/>
-      <c r="M18" s="68"/>
-      <c r="N18" s="68" t="s">
+      <c r="L18" s="73"/>
+      <c r="M18" s="67"/>
+      <c r="N18" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="O18" s="78"/>
+      <c r="O18" s="77"/>
     </row>
     <row r="19" spans="2:16" ht="0.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K19" s="137" t="s">
+      <c r="K19" s="136" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="20" spans="2:16" ht="23.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="2:16" s="108" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="63"/>
-      <c r="C21" s="92"/>
-      <c r="D21" s="92"/>
-      <c r="E21" s="136"/>
-      <c r="F21" s="114"/>
-      <c r="G21" s="114"/>
-      <c r="H21" s="84"/>
-      <c r="I21" s="74"/>
-      <c r="J21" s="84"/>
-      <c r="K21" s="84"/>
-      <c r="L21" s="92"/>
-      <c r="M21" s="92"/>
-      <c r="N21" s="92"/>
-      <c r="O21" s="117"/>
-      <c r="P21" s="92"/>
-    </row>
-    <row r="22" spans="2:16" s="108" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="63"/>
-      <c r="C22" s="92"/>
-      <c r="D22" s="92"/>
-      <c r="E22" s="136"/>
-      <c r="F22" s="114"/>
-      <c r="G22" s="114"/>
-      <c r="H22" s="84"/>
-      <c r="I22" s="74"/>
-      <c r="J22" s="84"/>
-      <c r="K22" s="84"/>
-      <c r="L22" s="92"/>
-      <c r="M22" s="92"/>
-      <c r="N22" s="92"/>
-      <c r="O22" s="117"/>
-      <c r="P22" s="92"/>
+    <row r="21" spans="2:16" s="107" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="62"/>
+      <c r="C21" s="91"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="135"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="83"/>
+      <c r="I21" s="73"/>
+      <c r="J21" s="83"/>
+      <c r="K21" s="83"/>
+      <c r="L21" s="91"/>
+      <c r="M21" s="91"/>
+      <c r="N21" s="91"/>
+      <c r="O21" s="116"/>
+      <c r="P21" s="91"/>
+    </row>
+    <row r="22" spans="2:16" s="107" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="62"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="91"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="113"/>
+      <c r="G22" s="113"/>
+      <c r="H22" s="83"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="83"/>
+      <c r="K22" s="83"/>
+      <c r="L22" s="91"/>
+      <c r="M22" s="91"/>
+      <c r="N22" s="91"/>
+      <c r="O22" s="116"/>
+      <c r="P22" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1691,609 +1690,609 @@
   <dimension ref="A1:BY14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0" style="108" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="10.125" style="108" customWidth="1"/>
-    <col min="3" max="3" width="14.125" style="92" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="92" customWidth="1"/>
-    <col min="5" max="5" width="0" style="92" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="6.75" style="114" customWidth="1"/>
-    <col min="7" max="7" width="6.875" style="114" customWidth="1"/>
-    <col min="8" max="8" width="8.875" style="108" customWidth="1"/>
-    <col min="9" max="9" width="6.5" style="74" customWidth="1"/>
-    <col min="10" max="10" width="6.5" style="84" customWidth="1"/>
-    <col min="11" max="11" width="14.5" style="84" customWidth="1"/>
-    <col min="12" max="12" width="9" style="115" customWidth="1"/>
-    <col min="13" max="13" width="14.375" style="84" customWidth="1"/>
-    <col min="14" max="14" width="40.5" style="116" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="92"/>
+    <col min="1" max="1" width="0" style="107" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="10.125" style="107" customWidth="1"/>
+    <col min="3" max="3" width="14.125" style="91" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="91" customWidth="1"/>
+    <col min="5" max="5" width="0" style="91" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="6.75" style="113" customWidth="1"/>
+    <col min="7" max="7" width="6.875" style="113" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="107" customWidth="1"/>
+    <col min="9" max="9" width="6.5" style="73" customWidth="1"/>
+    <col min="10" max="10" width="6.5" style="83" customWidth="1"/>
+    <col min="11" max="11" width="14.5" style="83" customWidth="1"/>
+    <col min="12" max="12" width="9" style="114" customWidth="1"/>
+    <col min="13" max="13" width="14.375" style="83" customWidth="1"/>
+    <col min="14" max="14" width="40.5" style="115" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="91"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77" s="84" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="143" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
-      <c r="K1" s="143"/>
-      <c r="L1" s="143"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="143"/>
+    <row r="1" spans="1:77" s="83" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="144" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
+      <c r="L1" s="144"/>
+      <c r="M1" s="144"/>
+      <c r="N1" s="144"/>
     </row>
     <row r="2" spans="1:77" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="85" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="86" t="s">
+      <c r="A2" s="84" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="87" t="s">
+      <c r="C2" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="88" t="s">
+      <c r="D2" s="87" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="88" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="89" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="87" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="88" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="40" t="s">
+      <c r="J2" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="88" t="s">
-        <v>60</v>
-      </c>
-      <c r="K2" s="90" t="s">
+      <c r="K2" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="91" t="s">
+      <c r="L2" s="90" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="90" t="s">
+      <c r="M2" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="87" t="s">
+      <c r="N2" s="86" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:77" s="105" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="93"/>
-      <c r="B3" s="86"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="99"/>
-      <c r="K3" s="100"/>
-      <c r="L3" s="101"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="103"/>
-      <c r="O3" s="104"/>
-      <c r="P3" s="104"/>
-    </row>
-    <row r="4" spans="1:77" s="105" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="106"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="87"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="100"/>
-      <c r="L4" s="101"/>
-      <c r="M4" s="102"/>
-      <c r="N4" s="103"/>
-      <c r="O4" s="104"/>
-      <c r="P4" s="104"/>
-    </row>
-    <row r="5" spans="1:77" s="105" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="106"/>
-      <c r="B5" s="86"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="95"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="99"/>
-      <c r="K5" s="100"/>
-      <c r="L5" s="101"/>
-      <c r="M5" s="102"/>
-      <c r="N5" s="103"/>
-      <c r="O5" s="104"/>
-      <c r="P5" s="104"/>
-    </row>
-    <row r="6" spans="1:77" s="105" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="106"/>
-      <c r="B6" s="86"/>
-      <c r="C6" s="87"/>
-      <c r="D6" s="94"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="96"/>
-      <c r="G6" s="96"/>
-      <c r="H6" s="97"/>
-      <c r="I6" s="98"/>
-      <c r="J6" s="99"/>
-      <c r="K6" s="100"/>
-      <c r="L6" s="101"/>
-      <c r="M6" s="102"/>
-      <c r="N6" s="103"/>
-      <c r="O6" s="104"/>
-      <c r="P6" s="104"/>
-    </row>
-    <row r="7" spans="1:77" s="105" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="106"/>
-      <c r="B7" s="86"/>
-      <c r="C7" s="87"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="95"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="97"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="99"/>
-      <c r="K7" s="100"/>
-      <c r="L7" s="101"/>
-      <c r="M7" s="102"/>
-      <c r="N7" s="103"/>
-      <c r="O7" s="104"/>
-      <c r="P7" s="104"/>
-    </row>
-    <row r="8" spans="1:77" s="105" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="106"/>
-      <c r="B8" s="86"/>
-      <c r="C8" s="87"/>
-      <c r="D8" s="94"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="97"/>
-      <c r="I8" s="98"/>
-      <c r="J8" s="99"/>
-      <c r="K8" s="100"/>
-      <c r="L8" s="101"/>
-      <c r="M8" s="102"/>
-      <c r="N8" s="107"/>
-      <c r="O8" s="104"/>
-      <c r="P8" s="104"/>
-    </row>
-    <row r="9" spans="1:77" s="105" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="106"/>
-      <c r="B9" s="86"/>
-      <c r="C9" s="87"/>
-      <c r="D9" s="94"/>
-      <c r="E9" s="95"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="97"/>
-      <c r="I9" s="98"/>
-      <c r="J9" s="99"/>
-      <c r="K9" s="100"/>
-      <c r="L9" s="101"/>
-      <c r="M9" s="102"/>
-      <c r="N9" s="103"/>
-      <c r="O9" s="104"/>
-      <c r="P9" s="104"/>
+    <row r="3" spans="1:77" s="104" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="92"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="99"/>
+      <c r="L3" s="100"/>
+      <c r="M3" s="101"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="103"/>
+      <c r="P3" s="103"/>
+    </row>
+    <row r="4" spans="1:77" s="104" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="105"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="100"/>
+      <c r="M4" s="101"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="103"/>
+      <c r="P4" s="103"/>
+    </row>
+    <row r="5" spans="1:77" s="104" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="105"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="86"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="95"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="96"/>
+      <c r="I5" s="97"/>
+      <c r="J5" s="98"/>
+      <c r="K5" s="99"/>
+      <c r="L5" s="100"/>
+      <c r="M5" s="101"/>
+      <c r="N5" s="102"/>
+      <c r="O5" s="103"/>
+      <c r="P5" s="103"/>
+    </row>
+    <row r="6" spans="1:77" s="104" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="105"/>
+      <c r="B6" s="85"/>
+      <c r="C6" s="86"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="96"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="98"/>
+      <c r="K6" s="99"/>
+      <c r="L6" s="100"/>
+      <c r="M6" s="101"/>
+      <c r="N6" s="102"/>
+      <c r="O6" s="103"/>
+      <c r="P6" s="103"/>
+    </row>
+    <row r="7" spans="1:77" s="104" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="105"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="86"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="95"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="98"/>
+      <c r="K7" s="99"/>
+      <c r="L7" s="100"/>
+      <c r="M7" s="101"/>
+      <c r="N7" s="102"/>
+      <c r="O7" s="103"/>
+      <c r="P7" s="103"/>
+    </row>
+    <row r="8" spans="1:77" s="104" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="105"/>
+      <c r="B8" s="85"/>
+      <c r="C8" s="86"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="94"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="96"/>
+      <c r="I8" s="97"/>
+      <c r="J8" s="98"/>
+      <c r="K8" s="99"/>
+      <c r="L8" s="100"/>
+      <c r="M8" s="101"/>
+      <c r="N8" s="106"/>
+      <c r="O8" s="103"/>
+      <c r="P8" s="103"/>
+    </row>
+    <row r="9" spans="1:77" s="104" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="105"/>
+      <c r="B9" s="85"/>
+      <c r="C9" s="86"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="94"/>
+      <c r="F9" s="95"/>
+      <c r="G9" s="95"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="97"/>
+      <c r="J9" s="98"/>
+      <c r="K9" s="99"/>
+      <c r="L9" s="100"/>
+      <c r="M9" s="101"/>
+      <c r="N9" s="102"/>
+      <c r="O9" s="103"/>
+      <c r="P9" s="103"/>
     </row>
     <row r="10" spans="1:77" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="97"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="96"/>
-      <c r="H10" s="96"/>
-      <c r="I10" s="98"/>
-      <c r="J10" s="96"/>
-      <c r="K10" s="109"/>
-      <c r="L10" s="110"/>
-      <c r="M10" s="102"/>
-      <c r="N10" s="111"/>
-      <c r="O10" s="76"/>
-      <c r="P10" s="76"/>
-      <c r="Q10" s="76"/>
-      <c r="R10" s="76"/>
-      <c r="S10" s="76"/>
-      <c r="T10" s="76"/>
-      <c r="U10" s="76"/>
-      <c r="V10" s="76"/>
-      <c r="W10" s="76"/>
-      <c r="X10" s="76"/>
-      <c r="Y10" s="76"/>
-      <c r="Z10" s="76"/>
-      <c r="AA10" s="76"/>
-      <c r="AB10" s="76"/>
-      <c r="AC10" s="76"/>
-      <c r="AD10" s="76"/>
-      <c r="AE10" s="76"/>
-      <c r="AF10" s="76"/>
-      <c r="AG10" s="76"/>
-      <c r="AH10" s="76"/>
-      <c r="AI10" s="76"/>
-      <c r="AJ10" s="76"/>
-      <c r="AK10" s="76"/>
-      <c r="AL10" s="76"/>
-      <c r="AM10" s="76"/>
-      <c r="AN10" s="76"/>
-      <c r="AO10" s="76"/>
-      <c r="AP10" s="76"/>
-      <c r="AQ10" s="76"/>
-      <c r="AR10" s="76"/>
-      <c r="AS10" s="76"/>
-      <c r="AT10" s="76"/>
-      <c r="AU10" s="76"/>
-      <c r="AV10" s="76"/>
-      <c r="AW10" s="76"/>
-      <c r="AX10" s="76"/>
-      <c r="AY10" s="76"/>
-      <c r="AZ10" s="76"/>
-      <c r="BA10" s="76"/>
-      <c r="BB10" s="76"/>
-      <c r="BC10" s="76"/>
-      <c r="BD10" s="76"/>
-      <c r="BE10" s="76"/>
-      <c r="BF10" s="76"/>
-      <c r="BG10" s="76"/>
-      <c r="BH10" s="76"/>
-      <c r="BI10" s="76"/>
-      <c r="BJ10" s="76"/>
-      <c r="BK10" s="76"/>
-      <c r="BL10" s="76"/>
-      <c r="BM10" s="76"/>
-      <c r="BN10" s="76"/>
-      <c r="BO10" s="76"/>
-      <c r="BP10" s="76"/>
-      <c r="BQ10" s="76"/>
-      <c r="BR10" s="76"/>
-      <c r="BS10" s="76"/>
-      <c r="BT10" s="76"/>
-      <c r="BU10" s="76"/>
-      <c r="BV10" s="76"/>
-      <c r="BW10" s="76"/>
-      <c r="BX10" s="76"/>
-      <c r="BY10" s="76"/>
+      <c r="B10" s="96"/>
+      <c r="C10" s="95"/>
+      <c r="D10" s="95"/>
+      <c r="E10" s="95"/>
+      <c r="F10" s="95"/>
+      <c r="G10" s="95"/>
+      <c r="H10" s="95"/>
+      <c r="I10" s="97"/>
+      <c r="J10" s="95"/>
+      <c r="K10" s="108"/>
+      <c r="L10" s="109"/>
+      <c r="M10" s="101"/>
+      <c r="N10" s="110"/>
+      <c r="O10" s="75"/>
+      <c r="P10" s="75"/>
+      <c r="Q10" s="75"/>
+      <c r="R10" s="75"/>
+      <c r="S10" s="75"/>
+      <c r="T10" s="75"/>
+      <c r="U10" s="75"/>
+      <c r="V10" s="75"/>
+      <c r="W10" s="75"/>
+      <c r="X10" s="75"/>
+      <c r="Y10" s="75"/>
+      <c r="Z10" s="75"/>
+      <c r="AA10" s="75"/>
+      <c r="AB10" s="75"/>
+      <c r="AC10" s="75"/>
+      <c r="AD10" s="75"/>
+      <c r="AE10" s="75"/>
+      <c r="AF10" s="75"/>
+      <c r="AG10" s="75"/>
+      <c r="AH10" s="75"/>
+      <c r="AI10" s="75"/>
+      <c r="AJ10" s="75"/>
+      <c r="AK10" s="75"/>
+      <c r="AL10" s="75"/>
+      <c r="AM10" s="75"/>
+      <c r="AN10" s="75"/>
+      <c r="AO10" s="75"/>
+      <c r="AP10" s="75"/>
+      <c r="AQ10" s="75"/>
+      <c r="AR10" s="75"/>
+      <c r="AS10" s="75"/>
+      <c r="AT10" s="75"/>
+      <c r="AU10" s="75"/>
+      <c r="AV10" s="75"/>
+      <c r="AW10" s="75"/>
+      <c r="AX10" s="75"/>
+      <c r="AY10" s="75"/>
+      <c r="AZ10" s="75"/>
+      <c r="BA10" s="75"/>
+      <c r="BB10" s="75"/>
+      <c r="BC10" s="75"/>
+      <c r="BD10" s="75"/>
+      <c r="BE10" s="75"/>
+      <c r="BF10" s="75"/>
+      <c r="BG10" s="75"/>
+      <c r="BH10" s="75"/>
+      <c r="BI10" s="75"/>
+      <c r="BJ10" s="75"/>
+      <c r="BK10" s="75"/>
+      <c r="BL10" s="75"/>
+      <c r="BM10" s="75"/>
+      <c r="BN10" s="75"/>
+      <c r="BO10" s="75"/>
+      <c r="BP10" s="75"/>
+      <c r="BQ10" s="75"/>
+      <c r="BR10" s="75"/>
+      <c r="BS10" s="75"/>
+      <c r="BT10" s="75"/>
+      <c r="BU10" s="75"/>
+      <c r="BV10" s="75"/>
+      <c r="BW10" s="75"/>
+      <c r="BX10" s="75"/>
+      <c r="BY10" s="75"/>
     </row>
     <row r="11" spans="1:77" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="144"/>
-      <c r="C11" s="145"/>
-      <c r="D11" s="145"/>
-      <c r="E11" s="145"/>
-      <c r="F11" s="145"/>
-      <c r="G11" s="145"/>
-      <c r="H11" s="145"/>
-      <c r="I11" s="145"/>
-      <c r="J11" s="145"/>
-      <c r="K11" s="145"/>
-      <c r="L11" s="145"/>
-      <c r="M11" s="145"/>
-      <c r="N11" s="145"/>
-      <c r="O11" s="76"/>
-      <c r="P11" s="76"/>
-      <c r="Q11" s="76"/>
-      <c r="R11" s="76"/>
-      <c r="S11" s="76"/>
-      <c r="T11" s="76"/>
-      <c r="U11" s="76"/>
-      <c r="V11" s="76"/>
-      <c r="W11" s="76"/>
-      <c r="X11" s="76"/>
-      <c r="Y11" s="76"/>
-      <c r="Z11" s="76"/>
-      <c r="AA11" s="76"/>
-      <c r="AB11" s="76"/>
-      <c r="AC11" s="76"/>
-      <c r="AD11" s="76"/>
-      <c r="AE11" s="76"/>
-      <c r="AF11" s="76"/>
-      <c r="AG11" s="76"/>
-      <c r="AH11" s="76"/>
-      <c r="AI11" s="76"/>
-      <c r="AJ11" s="76"/>
-      <c r="AK11" s="76"/>
-      <c r="AL11" s="76"/>
-      <c r="AM11" s="76"/>
-      <c r="AN11" s="76"/>
-      <c r="AO11" s="76"/>
-      <c r="AP11" s="76"/>
-      <c r="AQ11" s="76"/>
-      <c r="AR11" s="76"/>
-      <c r="AS11" s="76"/>
-      <c r="AT11" s="76"/>
-      <c r="AU11" s="76"/>
-      <c r="AV11" s="76"/>
-      <c r="AW11" s="76"/>
-      <c r="AX11" s="76"/>
-      <c r="AY11" s="76"/>
-      <c r="AZ11" s="76"/>
-      <c r="BA11" s="76"/>
-      <c r="BB11" s="76"/>
-      <c r="BC11" s="76"/>
-      <c r="BD11" s="76"/>
-      <c r="BE11" s="76"/>
-      <c r="BF11" s="76"/>
-      <c r="BG11" s="76"/>
-      <c r="BH11" s="76"/>
-      <c r="BI11" s="76"/>
-      <c r="BJ11" s="76"/>
-      <c r="BK11" s="76"/>
-      <c r="BL11" s="76"/>
-      <c r="BM11" s="76"/>
-      <c r="BN11" s="76"/>
-      <c r="BO11" s="76"/>
-      <c r="BP11" s="76"/>
-      <c r="BQ11" s="76"/>
-      <c r="BR11" s="76"/>
-      <c r="BS11" s="76"/>
-      <c r="BT11" s="76"/>
-      <c r="BU11" s="76"/>
-      <c r="BV11" s="76"/>
-      <c r="BW11" s="76"/>
-      <c r="BX11" s="76"/>
-      <c r="BY11" s="76"/>
-    </row>
-    <row r="12" spans="1:77" s="76" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="112" t="s">
+      <c r="B11" s="145"/>
+      <c r="C11" s="146"/>
+      <c r="D11" s="146"/>
+      <c r="E11" s="146"/>
+      <c r="F11" s="146"/>
+      <c r="G11" s="146"/>
+      <c r="H11" s="146"/>
+      <c r="I11" s="146"/>
+      <c r="J11" s="146"/>
+      <c r="K11" s="146"/>
+      <c r="L11" s="146"/>
+      <c r="M11" s="146"/>
+      <c r="N11" s="146"/>
+      <c r="O11" s="75"/>
+      <c r="P11" s="75"/>
+      <c r="Q11" s="75"/>
+      <c r="R11" s="75"/>
+      <c r="S11" s="75"/>
+      <c r="T11" s="75"/>
+      <c r="U11" s="75"/>
+      <c r="V11" s="75"/>
+      <c r="W11" s="75"/>
+      <c r="X11" s="75"/>
+      <c r="Y11" s="75"/>
+      <c r="Z11" s="75"/>
+      <c r="AA11" s="75"/>
+      <c r="AB11" s="75"/>
+      <c r="AC11" s="75"/>
+      <c r="AD11" s="75"/>
+      <c r="AE11" s="75"/>
+      <c r="AF11" s="75"/>
+      <c r="AG11" s="75"/>
+      <c r="AH11" s="75"/>
+      <c r="AI11" s="75"/>
+      <c r="AJ11" s="75"/>
+      <c r="AK11" s="75"/>
+      <c r="AL11" s="75"/>
+      <c r="AM11" s="75"/>
+      <c r="AN11" s="75"/>
+      <c r="AO11" s="75"/>
+      <c r="AP11" s="75"/>
+      <c r="AQ11" s="75"/>
+      <c r="AR11" s="75"/>
+      <c r="AS11" s="75"/>
+      <c r="AT11" s="75"/>
+      <c r="AU11" s="75"/>
+      <c r="AV11" s="75"/>
+      <c r="AW11" s="75"/>
+      <c r="AX11" s="75"/>
+      <c r="AY11" s="75"/>
+      <c r="AZ11" s="75"/>
+      <c r="BA11" s="75"/>
+      <c r="BB11" s="75"/>
+      <c r="BC11" s="75"/>
+      <c r="BD11" s="75"/>
+      <c r="BE11" s="75"/>
+      <c r="BF11" s="75"/>
+      <c r="BG11" s="75"/>
+      <c r="BH11" s="75"/>
+      <c r="BI11" s="75"/>
+      <c r="BJ11" s="75"/>
+      <c r="BK11" s="75"/>
+      <c r="BL11" s="75"/>
+      <c r="BM11" s="75"/>
+      <c r="BN11" s="75"/>
+      <c r="BO11" s="75"/>
+      <c r="BP11" s="75"/>
+      <c r="BQ11" s="75"/>
+      <c r="BR11" s="75"/>
+      <c r="BS11" s="75"/>
+      <c r="BT11" s="75"/>
+      <c r="BU11" s="75"/>
+      <c r="BV11" s="75"/>
+      <c r="BW11" s="75"/>
+      <c r="BX11" s="75"/>
+      <c r="BY11" s="75"/>
+    </row>
+    <row r="12" spans="1:77" s="75" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="111" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="77" t="s">
+      <c r="C12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="74"/>
-      <c r="I12" s="75"/>
-      <c r="J12" s="77" t="s">
+      <c r="G12" s="73"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="K12" s="74"/>
-      <c r="L12" s="68" t="s">
+      <c r="K12" s="73"/>
+      <c r="L12" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="M12" s="74"/>
-      <c r="N12" s="112" t="s">
+      <c r="M12" s="73"/>
+      <c r="N12" s="111" t="s">
         <v>17</v>
       </c>
-      <c r="O12" s="92"/>
-      <c r="P12" s="92"/>
-      <c r="Q12" s="92"/>
-      <c r="R12" s="92"/>
-      <c r="S12" s="92"/>
-      <c r="T12" s="92"/>
-      <c r="U12" s="92"/>
-      <c r="V12" s="92"/>
-      <c r="W12" s="92"/>
-      <c r="X12" s="92"/>
-      <c r="Y12" s="92"/>
-      <c r="Z12" s="92"/>
-      <c r="AA12" s="92"/>
-      <c r="AB12" s="92"/>
-      <c r="AC12" s="92"/>
-      <c r="AD12" s="92"/>
-      <c r="AE12" s="92"/>
-      <c r="AF12" s="92"/>
-      <c r="AG12" s="92"/>
-      <c r="AH12" s="92"/>
-      <c r="AI12" s="92"/>
-      <c r="AJ12" s="92"/>
-      <c r="AK12" s="92"/>
-      <c r="AL12" s="92"/>
-      <c r="AM12" s="92"/>
-      <c r="AN12" s="92"/>
-      <c r="AO12" s="92"/>
-      <c r="AP12" s="92"/>
-      <c r="AQ12" s="92"/>
-      <c r="AR12" s="92"/>
-      <c r="AS12" s="92"/>
-      <c r="AT12" s="92"/>
-      <c r="AU12" s="92"/>
-      <c r="AV12" s="92"/>
-      <c r="AW12" s="92"/>
-      <c r="AX12" s="92"/>
-      <c r="AY12" s="92"/>
-      <c r="AZ12" s="92"/>
-      <c r="BA12" s="92"/>
-      <c r="BB12" s="92"/>
-      <c r="BC12" s="92"/>
-      <c r="BD12" s="92"/>
-      <c r="BE12" s="92"/>
-      <c r="BF12" s="92"/>
-      <c r="BG12" s="92"/>
-      <c r="BH12" s="92"/>
-      <c r="BI12" s="92"/>
-      <c r="BJ12" s="92"/>
-      <c r="BK12" s="92"/>
-      <c r="BL12" s="92"/>
-      <c r="BM12" s="92"/>
-      <c r="BN12" s="92"/>
-      <c r="BO12" s="92"/>
-      <c r="BP12" s="92"/>
-      <c r="BQ12" s="92"/>
-      <c r="BR12" s="92"/>
-      <c r="BS12" s="92"/>
-      <c r="BT12" s="92"/>
-      <c r="BU12" s="92"/>
-      <c r="BV12" s="92"/>
-      <c r="BW12" s="92"/>
-      <c r="BX12" s="92"/>
-      <c r="BY12" s="92"/>
-    </row>
-    <row r="13" spans="1:77" s="76" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="74"/>
-      <c r="C13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="74"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="77"/>
-      <c r="K13" s="74"/>
-      <c r="L13" s="68"/>
-      <c r="M13" s="74"/>
-      <c r="N13" s="113"/>
-      <c r="O13" s="92"/>
-      <c r="P13" s="92"/>
-      <c r="Q13" s="92"/>
-      <c r="R13" s="92"/>
-      <c r="S13" s="92"/>
-      <c r="T13" s="92"/>
-      <c r="U13" s="92"/>
-      <c r="V13" s="92"/>
-      <c r="W13" s="92"/>
-      <c r="X13" s="92"/>
-      <c r="Y13" s="92"/>
-      <c r="Z13" s="92"/>
-      <c r="AA13" s="92"/>
-      <c r="AB13" s="92"/>
-      <c r="AC13" s="92"/>
-      <c r="AD13" s="92"/>
-      <c r="AE13" s="92"/>
-      <c r="AF13" s="92"/>
-      <c r="AG13" s="92"/>
-      <c r="AH13" s="92"/>
-      <c r="AI13" s="92"/>
-      <c r="AJ13" s="92"/>
-      <c r="AK13" s="92"/>
-      <c r="AL13" s="92"/>
-      <c r="AM13" s="92"/>
-      <c r="AN13" s="92"/>
-      <c r="AO13" s="92"/>
-      <c r="AP13" s="92"/>
-      <c r="AQ13" s="92"/>
-      <c r="AR13" s="92"/>
-      <c r="AS13" s="92"/>
-      <c r="AT13" s="92"/>
-      <c r="AU13" s="92"/>
-      <c r="AV13" s="92"/>
-      <c r="AW13" s="92"/>
-      <c r="AX13" s="92"/>
-      <c r="AY13" s="92"/>
-      <c r="AZ13" s="92"/>
-      <c r="BA13" s="92"/>
-      <c r="BB13" s="92"/>
-      <c r="BC13" s="92"/>
-      <c r="BD13" s="92"/>
-      <c r="BE13" s="92"/>
-      <c r="BF13" s="92"/>
-      <c r="BG13" s="92"/>
-      <c r="BH13" s="92"/>
-      <c r="BI13" s="92"/>
-      <c r="BJ13" s="92"/>
-      <c r="BK13" s="92"/>
-      <c r="BL13" s="92"/>
-      <c r="BM13" s="92"/>
-      <c r="BN13" s="92"/>
-      <c r="BO13" s="92"/>
-      <c r="BP13" s="92"/>
-      <c r="BQ13" s="92"/>
-      <c r="BR13" s="92"/>
-      <c r="BS13" s="92"/>
-      <c r="BT13" s="92"/>
-      <c r="BU13" s="92"/>
-      <c r="BV13" s="92"/>
-      <c r="BW13" s="92"/>
-      <c r="BX13" s="92"/>
-      <c r="BY13" s="92"/>
-    </row>
-    <row r="14" spans="1:77" s="76" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="74"/>
-      <c r="C14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="77" t="s">
+      <c r="O12" s="91"/>
+      <c r="P12" s="91"/>
+      <c r="Q12" s="91"/>
+      <c r="R12" s="91"/>
+      <c r="S12" s="91"/>
+      <c r="T12" s="91"/>
+      <c r="U12" s="91"/>
+      <c r="V12" s="91"/>
+      <c r="W12" s="91"/>
+      <c r="X12" s="91"/>
+      <c r="Y12" s="91"/>
+      <c r="Z12" s="91"/>
+      <c r="AA12" s="91"/>
+      <c r="AB12" s="91"/>
+      <c r="AC12" s="91"/>
+      <c r="AD12" s="91"/>
+      <c r="AE12" s="91"/>
+      <c r="AF12" s="91"/>
+      <c r="AG12" s="91"/>
+      <c r="AH12" s="91"/>
+      <c r="AI12" s="91"/>
+      <c r="AJ12" s="91"/>
+      <c r="AK12" s="91"/>
+      <c r="AL12" s="91"/>
+      <c r="AM12" s="91"/>
+      <c r="AN12" s="91"/>
+      <c r="AO12" s="91"/>
+      <c r="AP12" s="91"/>
+      <c r="AQ12" s="91"/>
+      <c r="AR12" s="91"/>
+      <c r="AS12" s="91"/>
+      <c r="AT12" s="91"/>
+      <c r="AU12" s="91"/>
+      <c r="AV12" s="91"/>
+      <c r="AW12" s="91"/>
+      <c r="AX12" s="91"/>
+      <c r="AY12" s="91"/>
+      <c r="AZ12" s="91"/>
+      <c r="BA12" s="91"/>
+      <c r="BB12" s="91"/>
+      <c r="BC12" s="91"/>
+      <c r="BD12" s="91"/>
+      <c r="BE12" s="91"/>
+      <c r="BF12" s="91"/>
+      <c r="BG12" s="91"/>
+      <c r="BH12" s="91"/>
+      <c r="BI12" s="91"/>
+      <c r="BJ12" s="91"/>
+      <c r="BK12" s="91"/>
+      <c r="BL12" s="91"/>
+      <c r="BM12" s="91"/>
+      <c r="BN12" s="91"/>
+      <c r="BO12" s="91"/>
+      <c r="BP12" s="91"/>
+      <c r="BQ12" s="91"/>
+      <c r="BR12" s="91"/>
+      <c r="BS12" s="91"/>
+      <c r="BT12" s="91"/>
+      <c r="BU12" s="91"/>
+      <c r="BV12" s="91"/>
+      <c r="BW12" s="91"/>
+      <c r="BX12" s="91"/>
+      <c r="BY12" s="91"/>
+    </row>
+    <row r="13" spans="1:77" s="75" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="73"/>
+      <c r="C13" s="73"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="73"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="76"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="67"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="112"/>
+      <c r="O13" s="91"/>
+      <c r="P13" s="91"/>
+      <c r="Q13" s="91"/>
+      <c r="R13" s="91"/>
+      <c r="S13" s="91"/>
+      <c r="T13" s="91"/>
+      <c r="U13" s="91"/>
+      <c r="V13" s="91"/>
+      <c r="W13" s="91"/>
+      <c r="X13" s="91"/>
+      <c r="Y13" s="91"/>
+      <c r="Z13" s="91"/>
+      <c r="AA13" s="91"/>
+      <c r="AB13" s="91"/>
+      <c r="AC13" s="91"/>
+      <c r="AD13" s="91"/>
+      <c r="AE13" s="91"/>
+      <c r="AF13" s="91"/>
+      <c r="AG13" s="91"/>
+      <c r="AH13" s="91"/>
+      <c r="AI13" s="91"/>
+      <c r="AJ13" s="91"/>
+      <c r="AK13" s="91"/>
+      <c r="AL13" s="91"/>
+      <c r="AM13" s="91"/>
+      <c r="AN13" s="91"/>
+      <c r="AO13" s="91"/>
+      <c r="AP13" s="91"/>
+      <c r="AQ13" s="91"/>
+      <c r="AR13" s="91"/>
+      <c r="AS13" s="91"/>
+      <c r="AT13" s="91"/>
+      <c r="AU13" s="91"/>
+      <c r="AV13" s="91"/>
+      <c r="AW13" s="91"/>
+      <c r="AX13" s="91"/>
+      <c r="AY13" s="91"/>
+      <c r="AZ13" s="91"/>
+      <c r="BA13" s="91"/>
+      <c r="BB13" s="91"/>
+      <c r="BC13" s="91"/>
+      <c r="BD13" s="91"/>
+      <c r="BE13" s="91"/>
+      <c r="BF13" s="91"/>
+      <c r="BG13" s="91"/>
+      <c r="BH13" s="91"/>
+      <c r="BI13" s="91"/>
+      <c r="BJ13" s="91"/>
+      <c r="BK13" s="91"/>
+      <c r="BL13" s="91"/>
+      <c r="BM13" s="91"/>
+      <c r="BN13" s="91"/>
+      <c r="BO13" s="91"/>
+      <c r="BP13" s="91"/>
+      <c r="BQ13" s="91"/>
+      <c r="BR13" s="91"/>
+      <c r="BS13" s="91"/>
+      <c r="BT13" s="91"/>
+      <c r="BU13" s="91"/>
+      <c r="BV13" s="91"/>
+      <c r="BW13" s="91"/>
+      <c r="BX13" s="91"/>
+      <c r="BY13" s="91"/>
+    </row>
+    <row r="14" spans="1:77" s="75" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="74"/>
-      <c r="I14" s="75"/>
-      <c r="J14" s="77" t="s">
+      <c r="G14" s="73"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="K14" s="74"/>
-      <c r="L14" s="68" t="s">
+      <c r="K14" s="73"/>
+      <c r="L14" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="M14" s="74"/>
-      <c r="N14" s="113"/>
-      <c r="O14" s="92"/>
-      <c r="P14" s="92"/>
-      <c r="Q14" s="92"/>
-      <c r="R14" s="92"/>
-      <c r="S14" s="92"/>
-      <c r="T14" s="92"/>
-      <c r="U14" s="92"/>
-      <c r="V14" s="92"/>
-      <c r="W14" s="92"/>
-      <c r="X14" s="92"/>
-      <c r="Y14" s="92"/>
-      <c r="Z14" s="92"/>
-      <c r="AA14" s="92"/>
-      <c r="AB14" s="92"/>
-      <c r="AC14" s="92"/>
-      <c r="AD14" s="92"/>
-      <c r="AE14" s="92"/>
-      <c r="AF14" s="92"/>
-      <c r="AG14" s="92"/>
-      <c r="AH14" s="92"/>
-      <c r="AI14" s="92"/>
-      <c r="AJ14" s="92"/>
-      <c r="AK14" s="92"/>
-      <c r="AL14" s="92"/>
-      <c r="AM14" s="92"/>
-      <c r="AN14" s="92"/>
-      <c r="AO14" s="92"/>
-      <c r="AP14" s="92"/>
-      <c r="AQ14" s="92"/>
-      <c r="AR14" s="92"/>
-      <c r="AS14" s="92"/>
-      <c r="AT14" s="92"/>
-      <c r="AU14" s="92"/>
-      <c r="AV14" s="92"/>
-      <c r="AW14" s="92"/>
-      <c r="AX14" s="92"/>
-      <c r="AY14" s="92"/>
-      <c r="AZ14" s="92"/>
-      <c r="BA14" s="92"/>
-      <c r="BB14" s="92"/>
-      <c r="BC14" s="92"/>
-      <c r="BD14" s="92"/>
-      <c r="BE14" s="92"/>
-      <c r="BF14" s="92"/>
-      <c r="BG14" s="92"/>
-      <c r="BH14" s="92"/>
-      <c r="BI14" s="92"/>
-      <c r="BJ14" s="92"/>
-      <c r="BK14" s="92"/>
-      <c r="BL14" s="92"/>
-      <c r="BM14" s="92"/>
-      <c r="BN14" s="92"/>
-      <c r="BO14" s="92"/>
-      <c r="BP14" s="92"/>
-      <c r="BQ14" s="92"/>
-      <c r="BR14" s="92"/>
-      <c r="BS14" s="92"/>
-      <c r="BT14" s="92"/>
-      <c r="BU14" s="92"/>
-      <c r="BV14" s="92"/>
-      <c r="BW14" s="92"/>
-      <c r="BX14" s="92"/>
-      <c r="BY14" s="92"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="91"/>
+      <c r="P14" s="91"/>
+      <c r="Q14" s="91"/>
+      <c r="R14" s="91"/>
+      <c r="S14" s="91"/>
+      <c r="T14" s="91"/>
+      <c r="U14" s="91"/>
+      <c r="V14" s="91"/>
+      <c r="W14" s="91"/>
+      <c r="X14" s="91"/>
+      <c r="Y14" s="91"/>
+      <c r="Z14" s="91"/>
+      <c r="AA14" s="91"/>
+      <c r="AB14" s="91"/>
+      <c r="AC14" s="91"/>
+      <c r="AD14" s="91"/>
+      <c r="AE14" s="91"/>
+      <c r="AF14" s="91"/>
+      <c r="AG14" s="91"/>
+      <c r="AH14" s="91"/>
+      <c r="AI14" s="91"/>
+      <c r="AJ14" s="91"/>
+      <c r="AK14" s="91"/>
+      <c r="AL14" s="91"/>
+      <c r="AM14" s="91"/>
+      <c r="AN14" s="91"/>
+      <c r="AO14" s="91"/>
+      <c r="AP14" s="91"/>
+      <c r="AQ14" s="91"/>
+      <c r="AR14" s="91"/>
+      <c r="AS14" s="91"/>
+      <c r="AT14" s="91"/>
+      <c r="AU14" s="91"/>
+      <c r="AV14" s="91"/>
+      <c r="AW14" s="91"/>
+      <c r="AX14" s="91"/>
+      <c r="AY14" s="91"/>
+      <c r="AZ14" s="91"/>
+      <c r="BA14" s="91"/>
+      <c r="BB14" s="91"/>
+      <c r="BC14" s="91"/>
+      <c r="BD14" s="91"/>
+      <c r="BE14" s="91"/>
+      <c r="BF14" s="91"/>
+      <c r="BG14" s="91"/>
+      <c r="BH14" s="91"/>
+      <c r="BI14" s="91"/>
+      <c r="BJ14" s="91"/>
+      <c r="BK14" s="91"/>
+      <c r="BL14" s="91"/>
+      <c r="BM14" s="91"/>
+      <c r="BN14" s="91"/>
+      <c r="BO14" s="91"/>
+      <c r="BP14" s="91"/>
+      <c r="BQ14" s="91"/>
+      <c r="BR14" s="91"/>
+      <c r="BS14" s="91"/>
+      <c r="BT14" s="91"/>
+      <c r="BU14" s="91"/>
+      <c r="BV14" s="91"/>
+      <c r="BW14" s="91"/>
+      <c r="BX14" s="91"/>
+      <c r="BY14" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2310,379 +2309,379 @@
   <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.5" style="35" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="10.25" style="79" customWidth="1"/>
-    <col min="3" max="3" width="9.625" style="80" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="81" customWidth="1"/>
-    <col min="5" max="5" width="6.5" style="35" customWidth="1"/>
-    <col min="6" max="6" width="13.375" style="35" customWidth="1"/>
-    <col min="7" max="7" width="5.125" style="35" customWidth="1"/>
-    <col min="8" max="8" width="19.125" style="82" customWidth="1"/>
-    <col min="9" max="9" width="61.25" style="83" customWidth="1"/>
-    <col min="10" max="10" width="5.5" style="36" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.125" style="36" hidden="1" customWidth="1"/>
-    <col min="12" max="13" width="5.125" style="36" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="1.75" style="36" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="36"/>
+    <col min="1" max="1" width="5.5" style="34" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="10.25" style="78" customWidth="1"/>
+    <col min="3" max="3" width="9.625" style="79" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="80" customWidth="1"/>
+    <col min="5" max="5" width="6.5" style="34" customWidth="1"/>
+    <col min="6" max="6" width="13.375" style="34" customWidth="1"/>
+    <col min="7" max="7" width="5.125" style="34" customWidth="1"/>
+    <col min="8" max="8" width="19.125" style="81" customWidth="1"/>
+    <col min="9" max="9" width="61.25" style="82" customWidth="1"/>
+    <col min="10" max="10" width="5.5" style="35" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.125" style="35" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="5.125" style="35" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="1.75" style="35" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="35"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="35" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="139" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="37"/>
+    <row r="1" spans="1:17" s="34" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="140" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
     </row>
     <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="39" t="s">
+      <c r="A2" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="F2" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="121" t="s">
+      <c r="G2" s="120" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="41" t="s">
+      <c r="H2" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="39" t="s">
+      <c r="I2" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="43" t="s">
+      <c r="K2" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="44" t="s">
+      <c r="L2" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="45" t="s">
+      <c r="M2" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="43" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="46"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="49"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="51"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="48"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="50"/>
     </row>
     <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="46"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="48">
+      <c r="A4" s="45"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="47">
         <f t="shared" ref="F4:F13" si="0">D4*E4</f>
         <v>0</v>
       </c>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48">
+      <c r="G4" s="47"/>
+      <c r="H4" s="47">
         <f t="shared" ref="H4:H13" si="1">F4</f>
         <v>0</v>
       </c>
-      <c r="I4" s="49"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="51"/>
+      <c r="I4" s="48"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="50"/>
     </row>
     <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="46"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="48">
+      <c r="A5" s="45"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="47">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48">
+      <c r="G5" s="47"/>
+      <c r="H5" s="47">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I5" s="49"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="51"/>
+      <c r="I5" s="48"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="51"/>
+      <c r="N5" s="50"/>
     </row>
     <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="46"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="48">
+      <c r="A6" s="45"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="47">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48">
+      <c r="G6" s="47"/>
+      <c r="H6" s="47">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I6" s="49"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="51"/>
+      <c r="I6" s="48"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="50"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="50"/>
     </row>
     <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="46"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="48">
+      <c r="A7" s="45"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="47">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48">
+      <c r="G7" s="47"/>
+      <c r="H7" s="47">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I7" s="49"/>
-      <c r="K7" s="50"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="52"/>
-      <c r="N7" s="51"/>
+      <c r="I7" s="48"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="50"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="50"/>
     </row>
     <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="46"/>
-      <c r="B8" s="40"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="49"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="52"/>
-      <c r="N8" s="51"/>
+      <c r="A8" s="45"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="47"/>
+      <c r="G8" s="47"/>
+      <c r="H8" s="47"/>
+      <c r="I8" s="48"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="50"/>
+      <c r="M8" s="51"/>
+      <c r="N8" s="50"/>
     </row>
     <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="46"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="48">
+      <c r="A9" s="45"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="47">
         <f t="shared" ref="F9:F12" si="2">D9*E9</f>
         <v>0</v>
       </c>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48">
+      <c r="G9" s="47"/>
+      <c r="H9" s="47">
         <f t="shared" ref="H9:H12" si="3">F9</f>
         <v>0</v>
       </c>
-      <c r="I9" s="49"/>
-      <c r="K9" s="50"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="52"/>
-      <c r="N9" s="51"/>
+      <c r="I9" s="48"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="50"/>
+      <c r="M9" s="51"/>
+      <c r="N9" s="50"/>
     </row>
     <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="46"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="48">
+      <c r="A10" s="45"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48">
+      <c r="G10" s="47"/>
+      <c r="H10" s="47">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I10" s="49"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="51"/>
-      <c r="M10" s="52"/>
-      <c r="N10" s="51"/>
+      <c r="I10" s="48"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="50"/>
+      <c r="M10" s="51"/>
+      <c r="N10" s="50"/>
     </row>
     <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="46"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="48">
+      <c r="A11" s="45"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48">
+      <c r="G11" s="47"/>
+      <c r="H11" s="47">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I11" s="49"/>
-      <c r="K11" s="50"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="52"/>
-      <c r="N11" s="51"/>
+      <c r="I11" s="48"/>
+      <c r="K11" s="49"/>
+      <c r="L11" s="50"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="50"/>
     </row>
     <row r="12" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="46"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="48">
+      <c r="A12" s="45"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48">
+      <c r="G12" s="47"/>
+      <c r="H12" s="47">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I12" s="49"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="51"/>
-      <c r="M12" s="52"/>
-      <c r="N12" s="51"/>
+      <c r="I12" s="48"/>
+      <c r="K12" s="49"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="50"/>
     </row>
     <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="46"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="48">
+      <c r="A13" s="45"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="47">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48">
+      <c r="G13" s="47"/>
+      <c r="H13" s="47">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I13" s="49"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="51"/>
-      <c r="M13" s="52"/>
-      <c r="N13" s="51"/>
+      <c r="I13" s="48"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="50"/>
+      <c r="M13" s="51"/>
+      <c r="N13" s="50"/>
     </row>
     <row r="14" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="53"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="49"/>
-    </row>
-    <row r="15" spans="1:17" s="58" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="59" t="s">
+      <c r="B14" s="52"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="48"/>
+    </row>
+    <row r="15" spans="1:17" s="57" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="60"/>
-      <c r="D15" s="61" t="s">
+      <c r="C15" s="59"/>
+      <c r="D15" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="62"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="62" t="s">
+      <c r="E15" s="61"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="H15" s="61"/>
-      <c r="I15" s="64" t="s">
+      <c r="H15" s="60"/>
+      <c r="I15" s="63" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="58" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="59"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="63"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="64"/>
-    </row>
-    <row r="17" spans="2:9" s="58" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="59"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="63"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="61"/>
-      <c r="I17" s="65"/>
-    </row>
-    <row r="18" spans="2:9" s="58" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="66"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="61" t="s">
+    <row r="16" spans="1:17" s="57" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="58"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="62"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="63"/>
+    </row>
+    <row r="17" spans="2:9" s="57" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="58"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="64"/>
+    </row>
+    <row r="18" spans="2:9" s="57" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="65"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="62"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="62" t="s">
+      <c r="E18" s="61"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="61"/>
-      <c r="I18" s="64" t="s">
+      <c r="H18" s="60"/>
+      <c r="I18" s="63" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="67"/>
-      <c r="C19" s="68"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="70"/>
-      <c r="G19" s="70"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="72"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="71"/>
     </row>
     <row r="20" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="73"/>
-      <c r="C20" s="74"/>
-      <c r="D20" s="75"/>
-      <c r="E20" s="76"/>
-      <c r="F20" s="76"/>
-      <c r="G20" s="76"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="78"/>
+      <c r="B20" s="72"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="75"/>
+      <c r="F20" s="75"/>
+      <c r="G20" s="75"/>
+      <c r="H20" s="76"/>
+      <c r="I20" s="77"/>
     </row>
     <row r="21" spans="2:9" ht="11.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="2:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2699,37 +2698,35 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E98D86-3BBD-4165-99BF-0B3AF952A4EF}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15" style="28" customWidth="1"/>
-    <col min="2" max="2" width="18.375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="17.625" style="20" customWidth="1"/>
-    <col min="4" max="4" width="20" style="30" customWidth="1"/>
-    <col min="5" max="5" width="5.375" style="28" customWidth="1"/>
-    <col min="6" max="6" width="9.25" style="15" customWidth="1"/>
-    <col min="7" max="7" width="8.75" style="15" customWidth="1"/>
+    <col min="1" max="1" width="15" style="27" customWidth="1"/>
+    <col min="2" max="2" width="18.375" style="27" customWidth="1"/>
+    <col min="3" max="3" width="17.625" style="19" customWidth="1"/>
+    <col min="4" max="4" width="20" style="29" customWidth="1"/>
+    <col min="5" max="5" width="5.375" style="27" customWidth="1"/>
+    <col min="6" max="6" width="10.25" style="15" customWidth="1"/>
+    <col min="7" max="7" width="11" style="15" customWidth="1"/>
     <col min="8" max="8" width="13.75" style="16" customWidth="1"/>
-    <col min="9" max="9" width="18.25" style="28" customWidth="1"/>
-    <col min="10" max="10" width="17.625" style="20" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="20"/>
+    <col min="9" max="9" width="36.25" style="27" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-    </row>
-    <row r="2" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="138" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+    </row>
+    <row r="2" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>33</v>
       </c>
@@ -2742,262 +2739,239 @@
       <c r="D2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>37</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H2" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="J2" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I2" s="22" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
       <c r="F3" s="13"/>
       <c r="G3" s="12"/>
-      <c r="H3" s="25"/>
+      <c r="H3" s="24"/>
       <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-    </row>
-    <row r="4" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:9" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
       <c r="F4" s="13"/>
       <c r="G4" s="12"/>
-      <c r="H4" s="25"/>
+      <c r="H4" s="24"/>
       <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:9" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12"/>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
       <c r="F5" s="13"/>
       <c r="G5" s="12"/>
-      <c r="H5" s="25"/>
+      <c r="H5" s="24"/>
       <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:9" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
       <c r="F6" s="13"/>
       <c r="G6" s="12"/>
-      <c r="H6" s="25"/>
+      <c r="H6" s="24"/>
       <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:9" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
       <c r="F7" s="13"/>
       <c r="G7" s="12"/>
-      <c r="H7" s="25"/>
+      <c r="H7" s="24"/>
       <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:9" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
       <c r="F8" s="13"/>
       <c r="G8" s="12"/>
-      <c r="H8" s="25"/>
+      <c r="H8" s="24"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-    </row>
-    <row r="9" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:9" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
       <c r="F9" s="13"/>
       <c r="G9" s="12"/>
-      <c r="H9" s="25"/>
+      <c r="H9" s="24"/>
       <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-    </row>
-    <row r="10" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:9" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
       <c r="F10" s="13"/>
       <c r="G10" s="12"/>
-      <c r="H10" s="25"/>
+      <c r="H10" s="24"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-    </row>
-    <row r="11" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:9" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
       <c r="F11" s="13"/>
       <c r="G11" s="12"/>
-      <c r="H11" s="25"/>
+      <c r="H11" s="24"/>
       <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:9" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
       <c r="F12" s="13"/>
       <c r="G12" s="12"/>
-      <c r="H12" s="25"/>
+      <c r="H12" s="24"/>
       <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:9" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
       <c r="F13" s="13"/>
       <c r="G13" s="12"/>
-      <c r="H13" s="25"/>
+      <c r="H13" s="24"/>
       <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-    </row>
-    <row r="14" spans="1:10" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:9" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
-      <c r="F14" s="26"/>
+      <c r="F14" s="25"/>
       <c r="G14" s="13"/>
       <c r="H14" s="14"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I14" s="26"/>
+    </row>
+    <row r="15" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="28"/>
+        <v>38</v>
+      </c>
+      <c r="C15" s="27"/>
       <c r="D15" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="G15" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="I15" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="J15" s="17"/>
-    </row>
-    <row r="16" spans="1:10" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G15" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
-      <c r="C16" s="28"/>
+      <c r="C16" s="27"/>
       <c r="D16" s="17"/>
-      <c r="G16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="28"/>
-    </row>
-    <row r="17" spans="1:10" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="29"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="J17" s="28"/>
-    </row>
-    <row r="18" spans="1:10" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G16" s="28"/>
+      <c r="I16" s="28"/>
+    </row>
+    <row r="17" spans="1:9" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="28"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+    </row>
+    <row r="18" spans="1:9" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="28"/>
+      <c r="C18" s="27"/>
       <c r="D18" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="G18" s="29" t="s">
-        <v>43</v>
+      <c r="G18" s="28" t="s">
+        <v>41</v>
       </c>
       <c r="I18" s="15"/>
-      <c r="J18" s="28"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="20"/>
-      <c r="B19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="20"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="20"/>
-      <c r="B20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="20"/>
-    </row>
-    <row r="21" spans="1:10" s="28" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="20"/>
-      <c r="D21" s="30"/>
-      <c r="H21" s="34"/>
-      <c r="J21" s="20"/>
-    </row>
-    <row r="22" spans="1:10" s="28" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="20"/>
-      <c r="D22" s="30"/>
-      <c r="H22" s="34"/>
-      <c r="J22" s="20"/>
-    </row>
-    <row r="23" spans="1:10" s="28" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="20"/>
-      <c r="D23" s="30"/>
-      <c r="H23" s="34"/>
-      <c r="J23" s="20"/>
-    </row>
-    <row r="24" spans="1:10" s="28" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="20"/>
-      <c r="D24" s="30"/>
-      <c r="H24" s="34"/>
-      <c r="J24" s="20"/>
+    </row>
+    <row r="19" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="19"/>
+    </row>
+    <row r="20" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="19"/>
+    </row>
+    <row r="21" spans="1:9" s="27" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C21" s="19"/>
+      <c r="D21" s="29"/>
+      <c r="H21" s="33"/>
+    </row>
+    <row r="22" spans="1:9" s="27" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="19"/>
+      <c r="D22" s="29"/>
+      <c r="H22" s="33"/>
+    </row>
+    <row r="23" spans="1:9" s="27" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="19"/>
+      <c r="D23" s="29"/>
+      <c r="H23" s="33"/>
+    </row>
+    <row r="24" spans="1:9" s="27" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="19"/>
+      <c r="D24" s="29"/>
+      <c r="H24" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3006,7 +2980,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D6224E1-2B9C-43DA-8D8F-272D7D48239E}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" style="6" customWidth="1"/>
@@ -3016,27 +2990,25 @@
     <col min="5" max="5" width="8" style="6" customWidth="1"/>
     <col min="6" max="6" width="11.875" style="6" customWidth="1"/>
     <col min="7" max="7" width="7.375" style="6" customWidth="1"/>
-    <col min="8" max="8" width="9.625" style="19" customWidth="1"/>
-    <col min="9" max="9" width="12.5" style="6" customWidth="1"/>
-    <col min="10" max="10" width="17.5" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="6"/>
+    <col min="8" max="8" width="9.625" style="18" customWidth="1"/>
+    <col min="9" max="9" width="42.75" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="149" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-    </row>
-    <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="148" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+    </row>
+    <row r="2" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>33</v>
       </c>
@@ -3047,13 +3019,13 @@
         <v>35</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>5</v>
@@ -3062,109 +3034,98 @@
         <v>6</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
-      <c r="C3" s="138"/>
+      <c r="C3" s="137"/>
       <c r="D3" s="8"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="9"/>
       <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-    </row>
-    <row r="4" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="8"/>
-      <c r="C4" s="138"/>
+      <c r="C4" s="137"/>
       <c r="D4" s="8"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="9"/>
       <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-    </row>
-    <row r="5" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="138"/>
+      <c r="C5" s="137"/>
       <c r="D5" s="8"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="9"/>
       <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-    </row>
-    <row r="6" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="8"/>
-      <c r="C6" s="138"/>
+      <c r="C6" s="137"/>
       <c r="D6" s="8"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="9"/>
       <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-    </row>
-    <row r="7" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="8"/>
-      <c r="C7" s="138"/>
+      <c r="C7" s="137"/>
       <c r="D7" s="8"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="9"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-    </row>
-    <row r="8" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="8"/>
-      <c r="C8" s="138"/>
+      <c r="C8" s="137"/>
       <c r="D8" s="8"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="9"/>
       <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-    </row>
-    <row r="9" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="8"/>
-      <c r="C9" s="138"/>
+      <c r="C9" s="137"/>
       <c r="D9" s="8"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="9"/>
       <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-    </row>
-    <row r="10" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="8"/>
-      <c r="C10" s="138"/>
+      <c r="C10" s="137"/>
       <c r="D10" s="8"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="9"/>
       <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-    </row>
-    <row r="11" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -3174,14 +3135,13 @@
       <c r="G11" s="13"/>
       <c r="H11" s="14"/>
       <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-    </row>
-    <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="15" t="s">
@@ -3189,15 +3149,14 @@
       </c>
       <c r="F12" s="15"/>
       <c r="G12" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H12" s="16"/>
       <c r="I12" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" s="18"/>
-    </row>
-    <row r="13" spans="1:10" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="D13" s="15"/>
@@ -3206,12 +3165,11 @@
       <c r="G13" s="15"/>
       <c r="H13" s="16"/>
       <c r="I13" s="15"/>
-      <c r="J13" s="18"/>
-    </row>
-    <row r="14" spans="1:10" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:9" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15"/>
       <c r="B14" s="15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="15" t="s">
@@ -3219,15 +3177,14 @@
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H14" s="16"/>
       <c r="I14" s="15"/>
-      <c r="J14" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3239,379 +3196,379 @@
   <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.5" style="35" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="10.25" style="79" customWidth="1"/>
-    <col min="3" max="3" width="9.625" style="80" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="81" customWidth="1"/>
-    <col min="5" max="5" width="6.5" style="35" customWidth="1"/>
-    <col min="6" max="6" width="13.375" style="35" customWidth="1"/>
-    <col min="7" max="7" width="5.125" style="35" customWidth="1"/>
-    <col min="8" max="8" width="19.125" style="82" customWidth="1"/>
-    <col min="9" max="9" width="61.25" style="83" customWidth="1"/>
-    <col min="10" max="10" width="5.5" style="36" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.125" style="36" hidden="1" customWidth="1"/>
-    <col min="12" max="13" width="5.125" style="36" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="1.75" style="36" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="36"/>
+    <col min="1" max="1" width="5.5" style="34" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="10.25" style="78" customWidth="1"/>
+    <col min="3" max="3" width="9.625" style="79" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="80" customWidth="1"/>
+    <col min="5" max="5" width="6.5" style="34" customWidth="1"/>
+    <col min="6" max="6" width="13.375" style="34" customWidth="1"/>
+    <col min="7" max="7" width="5.125" style="34" customWidth="1"/>
+    <col min="8" max="8" width="19.125" style="81" customWidth="1"/>
+    <col min="9" max="9" width="61.25" style="82" customWidth="1"/>
+    <col min="10" max="10" width="5.5" style="35" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.125" style="35" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="5.125" style="35" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="1.75" style="35" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="35"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="35" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="139" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="37"/>
+    <row r="1" spans="1:17" s="34" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="140" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
     </row>
     <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="39" t="s">
+      <c r="A2" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="F2" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="121" t="s">
+      <c r="G2" s="120" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="41" t="s">
+      <c r="H2" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="39" t="s">
+      <c r="I2" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="43" t="s">
+      <c r="K2" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="44" t="s">
+      <c r="L2" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="45" t="s">
+      <c r="M2" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="43" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="46"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="49"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="51"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="48"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="50"/>
     </row>
     <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="46"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="48">
+      <c r="A4" s="45"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="47">
         <f t="shared" ref="F4:F13" si="0">D4*E4</f>
         <v>0</v>
       </c>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48">
+      <c r="G4" s="47"/>
+      <c r="H4" s="47">
         <f t="shared" ref="H4:H13" si="1">F4</f>
         <v>0</v>
       </c>
-      <c r="I4" s="49"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="51"/>
+      <c r="I4" s="48"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="50"/>
     </row>
     <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="46"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="48">
+      <c r="A5" s="45"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="47">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48">
+      <c r="G5" s="47"/>
+      <c r="H5" s="47">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I5" s="49"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="51"/>
+      <c r="I5" s="48"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="51"/>
+      <c r="N5" s="50"/>
     </row>
     <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="46"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="48">
+      <c r="A6" s="45"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="47">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48">
+      <c r="G6" s="47"/>
+      <c r="H6" s="47">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I6" s="49"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="51"/>
+      <c r="I6" s="48"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="50"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="50"/>
     </row>
     <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="46"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="48">
+      <c r="A7" s="45"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="47">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48">
+      <c r="G7" s="47"/>
+      <c r="H7" s="47">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I7" s="49"/>
-      <c r="K7" s="50"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="52"/>
-      <c r="N7" s="51"/>
+      <c r="I7" s="48"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="50"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="50"/>
     </row>
     <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="46"/>
-      <c r="B8" s="40"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="49"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="52"/>
-      <c r="N8" s="51"/>
+      <c r="A8" s="45"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="47"/>
+      <c r="G8" s="47"/>
+      <c r="H8" s="47"/>
+      <c r="I8" s="48"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="50"/>
+      <c r="M8" s="51"/>
+      <c r="N8" s="50"/>
     </row>
     <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="46"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="48">
+      <c r="A9" s="45"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="47">
         <f t="shared" ref="F9:F12" si="2">D9*E9</f>
         <v>0</v>
       </c>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48">
+      <c r="G9" s="47"/>
+      <c r="H9" s="47">
         <f t="shared" ref="H9:H12" si="3">F9</f>
         <v>0</v>
       </c>
-      <c r="I9" s="49"/>
-      <c r="K9" s="50"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="52"/>
-      <c r="N9" s="51"/>
+      <c r="I9" s="48"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="50"/>
+      <c r="M9" s="51"/>
+      <c r="N9" s="50"/>
     </row>
     <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="46"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="48">
+      <c r="A10" s="45"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48">
+      <c r="G10" s="47"/>
+      <c r="H10" s="47">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I10" s="49"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="51"/>
-      <c r="M10" s="52"/>
-      <c r="N10" s="51"/>
+      <c r="I10" s="48"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="50"/>
+      <c r="M10" s="51"/>
+      <c r="N10" s="50"/>
     </row>
     <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="46"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="48">
+      <c r="A11" s="45"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48">
+      <c r="G11" s="47"/>
+      <c r="H11" s="47">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I11" s="49"/>
-      <c r="K11" s="50"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="52"/>
-      <c r="N11" s="51"/>
+      <c r="I11" s="48"/>
+      <c r="K11" s="49"/>
+      <c r="L11" s="50"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="50"/>
     </row>
     <row r="12" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="46"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="48">
+      <c r="A12" s="45"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48">
+      <c r="G12" s="47"/>
+      <c r="H12" s="47">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I12" s="49"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="51"/>
-      <c r="M12" s="52"/>
-      <c r="N12" s="51"/>
+      <c r="I12" s="48"/>
+      <c r="K12" s="49"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="50"/>
     </row>
     <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="46"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="48">
+      <c r="A13" s="45"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="47">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48">
+      <c r="G13" s="47"/>
+      <c r="H13" s="47">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I13" s="49"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="51"/>
-      <c r="M13" s="52"/>
-      <c r="N13" s="51"/>
+      <c r="I13" s="48"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="50"/>
+      <c r="M13" s="51"/>
+      <c r="N13" s="50"/>
     </row>
     <row r="14" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="53"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="49"/>
-    </row>
-    <row r="15" spans="1:17" s="58" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="59" t="s">
+      <c r="B14" s="52"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="48"/>
+    </row>
+    <row r="15" spans="1:17" s="57" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="60"/>
-      <c r="D15" s="61" t="s">
+      <c r="C15" s="59"/>
+      <c r="D15" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="62"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="62" t="s">
+      <c r="E15" s="61"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="H15" s="61"/>
-      <c r="I15" s="64" t="s">
+      <c r="H15" s="60"/>
+      <c r="I15" s="63" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="58" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="59"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="63"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="64"/>
-    </row>
-    <row r="17" spans="2:9" s="58" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="59"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="63"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="61"/>
-      <c r="I17" s="65"/>
-    </row>
-    <row r="18" spans="2:9" s="58" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="66"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="61" t="s">
+    <row r="16" spans="1:17" s="57" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="58"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="62"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="63"/>
+    </row>
+    <row r="17" spans="2:9" s="57" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="58"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="64"/>
+    </row>
+    <row r="18" spans="2:9" s="57" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="65"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="62"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="62" t="s">
+      <c r="E18" s="61"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="61"/>
-      <c r="I18" s="64" t="s">
+      <c r="H18" s="60"/>
+      <c r="I18" s="63" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="67"/>
-      <c r="C19" s="68"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="70"/>
-      <c r="G19" s="70"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="72"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="71"/>
     </row>
     <row r="20" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="73"/>
-      <c r="C20" s="74"/>
-      <c r="D20" s="75"/>
-      <c r="E20" s="76"/>
-      <c r="F20" s="76"/>
-      <c r="G20" s="76"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="78"/>
+      <c r="B20" s="72"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="75"/>
+      <c r="F20" s="75"/>
+      <c r="G20" s="75"/>
+      <c r="H20" s="76"/>
+      <c r="I20" s="77"/>
     </row>
     <row r="21" spans="2:9" ht="11.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="2:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/templates/accounting-template.xlsx
+++ b/templates/accounting-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\school-substitution-sys\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A15601-6E41-47AE-9A73-9C2DA5B16823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D6D0B9-2C0E-47C4-BA98-3830521FD62E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="66">
   <si>
     <t>編號</t>
   </si>
@@ -252,6 +252,16 @@
   </si>
   <si>
     <t>備註</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>鐘點費
+單價</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>鐘點費
+單價</t>
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
 </sst>
@@ -541,7 +551,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -956,41 +966,44 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2714,17 +2727,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="148" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
     </row>
     <row r="2" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -2989,24 +3002,24 @@
     <col min="4" max="4" width="7.25" style="6" customWidth="1"/>
     <col min="5" max="5" width="8" style="6" customWidth="1"/>
     <col min="6" max="6" width="11.875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="7.375" style="6" customWidth="1"/>
+    <col min="7" max="7" width="8.75" style="6" customWidth="1"/>
     <col min="8" max="8" width="9.625" style="18" customWidth="1"/>
     <col min="9" max="9" width="42.75" style="6" customWidth="1"/>
     <col min="10" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="138" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="149"/>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="149"/>
-      <c r="G1" s="149"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="149"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -3027,8 +3040,8 @@
       <c r="F2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>5</v>
+      <c r="G2" s="150" t="s">
+        <v>65</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>6</v>
@@ -3226,7 +3239,7 @@
       <c r="P1" s="35"/>
       <c r="Q1" s="36"/>
     </row>
-    <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="37" t="s">
         <v>0</v>
       </c>
@@ -3240,7 +3253,7 @@
         <v>26</v>
       </c>
       <c r="E2" s="39" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="F2" s="40" t="s">
         <v>6</v>
